--- a/NBFC-MF/LoanPortfolio.xlsx
+++ b/NBFC-MF/LoanPortfolio.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3600" windowWidth="15360" windowHeight="4410"/>
+    <workbookView xWindow="0" yWindow="3600" windowWidth="15360" windowHeight="4410" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="7" r:id="rId1"/>
     <sheet name="Tracker" sheetId="8" r:id="rId2"/>
+    <sheet name="LoaneeList" sheetId="9" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
@@ -39,13 +39,14 @@
     <externalReference r:id="rId28"/>
     <externalReference r:id="rId29"/>
     <externalReference r:id="rId30"/>
+    <externalReference r:id="rId31"/>
   </externalReferences>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="69">
   <si>
     <t>Code</t>
   </si>
@@ -153,6 +154,105 @@
   </si>
   <si>
     <t>UPI</t>
+  </si>
+  <si>
+    <t>`</t>
+  </si>
+  <si>
+    <t>600 fish</t>
+  </si>
+  <si>
+    <t>loan sanarei 180000, lanchenbi ranibala 10000</t>
+  </si>
+  <si>
+    <t>loan samila 10000, sandhyarani 20000</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>A Ranjit</t>
+  </si>
+  <si>
+    <t>Angom Bijenti</t>
+  </si>
+  <si>
+    <t>Bidyabati</t>
+  </si>
+  <si>
+    <t>Bidyarani</t>
+  </si>
+  <si>
+    <t>Ibeyaima</t>
+  </si>
+  <si>
+    <t>Inaobi</t>
+  </si>
+  <si>
+    <t>Kamala</t>
+  </si>
+  <si>
+    <t>L Gomti</t>
+  </si>
+  <si>
+    <t>Lanchenbi Ibeyaima</t>
+  </si>
+  <si>
+    <t>Lanchenbi Ranibala</t>
+  </si>
+  <si>
+    <t>Lanchenbi Samila</t>
+  </si>
+  <si>
+    <t>Miranrani</t>
+  </si>
+  <si>
+    <t>Mutum Sandhyarani</t>
+  </si>
+  <si>
+    <t>Pratima</t>
+  </si>
+  <si>
+    <t>Reena</t>
+  </si>
+  <si>
+    <t>Renita</t>
+  </si>
+  <si>
+    <t>Romila</t>
+  </si>
+  <si>
+    <t>Ronel</t>
+  </si>
+  <si>
+    <t>Salam Bidyalaxmi</t>
+  </si>
+  <si>
+    <t>Salam Echan</t>
+  </si>
+  <si>
+    <t>Sanarei Group</t>
+  </si>
+  <si>
+    <t>Sanasam Sonia</t>
+  </si>
+  <si>
+    <t>Sudhana</t>
+  </si>
+  <si>
+    <t>The Memcha</t>
+  </si>
+  <si>
+    <t>Thasana</t>
+  </si>
+  <si>
+    <t>Thnogam Bala</t>
+  </si>
+  <si>
+    <t>Y Seema</t>
+  </si>
+  <si>
+    <t>Collection Day</t>
   </si>
 </sst>
 </file>
@@ -536,7 +636,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
@@ -720,6 +820,40 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -746,18 +880,6 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -864,6 +986,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Loan1"/>
+      <sheetName val="198"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -894,22 +1017,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>11</v>
+            <v>17</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>4200</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>3920.3194223714245</v>
+            <v>4.5668002712773159E-10</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>6079.6805776285755</v>
+            <v>9999.9999999995434</v>
           </cell>
         </row>
         <row r="16">
@@ -920,6 +1043,63 @@
         <row r="17">
           <cell r="K17">
             <v>46248</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="K2" t="str">
+            <v>L20000W17-Mutum_Sandhyarani-N198</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="K3" t="str">
+            <v>Mutum_Sandhyarani</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="K7">
+            <v>20000</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="K9">
+            <v>1400</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="K10">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>23800</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="K14">
+            <v>23800</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="K15">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="K16" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="K17" t="str">
+            <v/>
           </cell>
         </row>
       </sheetData>
@@ -1033,22 +1213,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>8</v>
+            <v>12</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>12600</v>
+            <v>7000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>11424.319854722999</v>
+            <v>6597.85590128073</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>8575.6801452770014</v>
+            <v>13402.144098719269</v>
           </cell>
         </row>
         <row r="16">
@@ -1090,22 +1270,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>2</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>10500</v>
+            <v>9800</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>8991.0157995515765</v>
+            <v>8471.2997110135693</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>1008.9842004484235</v>
+            <v>1528.7002889864307</v>
           </cell>
         </row>
         <row r="16">
@@ -1160,22 +1340,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>7</v>
+            <v>12</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>10000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>9179.6248403282825</v>
+            <v>6.2391336541622877E-10</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>10820.375159671717</v>
+            <v>19999.999999999374</v>
           </cell>
         </row>
         <row r="16">
@@ -1217,22 +1397,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>1</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>11000</v>
+            <v>10000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>9292.2854076913736</v>
+            <v>8563.885350568542</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>707.71459230862638</v>
+            <v>1436.114649431458</v>
           </cell>
         </row>
         <row r="16">
@@ -1287,22 +1467,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>30</v>
+            <v>35</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>9000</v>
+            <v>8500</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>7838.2053538107648</v>
+            <v>7457.891976879012</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>2161.7946461892352</v>
+            <v>2542.108023120988</v>
           </cell>
         </row>
         <row r="16">
@@ -1344,22 +1524,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>23</v>
+            <v>28</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>9700</v>
+            <v>9200</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>8360.8080101606047</v>
+            <v>7988.68287277732</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>1639.1919898393953</v>
+            <v>2011.31712722268</v>
           </cell>
         </row>
         <row r="16">
@@ -1383,6 +1563,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Loan1"/>
+      <sheetName val="196"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -1413,22 +1594,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>13</v>
+            <v>17</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>5600</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>5330.1532184765038</v>
+            <v>9.1336005425546318E-10</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>14669.846781523496</v>
+            <v>19999.999999999087</v>
           </cell>
         </row>
         <row r="16">
@@ -1439,6 +1620,63 @@
         <row r="17">
           <cell r="K17">
             <v>46220</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="K2" t="str">
+            <v>L10000W17-Lanchenbi_Ranibala-N196</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="K3" t="str">
+            <v>Lanchenbi_Ranibala</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="K7">
+            <v>10000</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="K9">
+            <v>700</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="K10">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>11900</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="K14">
+            <v>11900</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="K15">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="K16" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="K17" t="str">
+            <v/>
           </cell>
         </row>
       </sheetData>
@@ -1452,6 +1690,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Loan1"/>
+      <sheetName val="197"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -1482,22 +1721,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>13</v>
+            <v>17</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>5600</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>5330.1532184765038</v>
+            <v>9.1336005425546318E-10</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>14669.846781523496</v>
+            <v>19999.999999999087</v>
           </cell>
         </row>
         <row r="16">
@@ -1508,6 +1747,63 @@
         <row r="17">
           <cell r="K17">
             <v>46220</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="K2" t="str">
+            <v>L10000W17-Lanchenbi_Samila-N197</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="K3" t="str">
+            <v>Lanchenbi_Samila</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="K7">
+            <v>10000</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="K9">
+            <v>700</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="K10">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>11900</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="K14">
+            <v>11900</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="K15">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="K16" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="K17" t="str">
+            <v/>
           </cell>
         </row>
       </sheetData>
@@ -1551,22 +1847,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>5</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>25200</v>
+            <v>27300</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>22201.185647927028</v>
+            <v>23823.487509187638</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>7798.8143520729718</v>
+            <v>6176.5124908123616</v>
           </cell>
         </row>
         <row r="16">
@@ -1620,22 +1916,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>5</v>
+            <v>80</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>7500</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>6615.6271011002946</v>
+            <v>-1.2721557141048834E-10</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>384.37289889970543</v>
+            <v>7000.0000000001273</v>
           </cell>
         </row>
         <row r="16">
@@ -1689,22 +1985,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>10</v>
+            <v>33</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>19800</v>
+            <v>15660</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>16743.038328281105</v>
+            <v>13699.308972116984</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>1256.9616717188946</v>
+            <v>4300.6910278830164</v>
           </cell>
         </row>
         <row r="16">
@@ -1758,22 +2054,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>15</v>
+            <v>17</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>4200</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>4076.9698450221713</v>
+            <v>1.2778400559909642E-9</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>25923.030154977831</v>
+            <v>29999.999999998723</v>
           </cell>
         </row>
         <row r="16">
@@ -1827,22 +2123,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>7</v>
+            <v>30</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>20340</v>
+            <v>16200</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>17124.239007894535</v>
+            <v>14108.769636859435</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>875.76099210546454</v>
+            <v>3891.2303631405648</v>
           </cell>
         </row>
         <row r="16">
@@ -1896,22 +2192,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>19</v>
+            <v>24</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>10100</v>
+            <v>9600</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>8654.3706289841193</v>
+            <v>8286.8450875198287</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>1345.6293710158807</v>
+            <v>1713.1549124801713</v>
           </cell>
         </row>
         <row r="16">
@@ -2034,22 +2330,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>2</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>10500</v>
+            <v>9800</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>8991.0157995515765</v>
+            <v>8471.2997110135693</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>1008.9842004484235</v>
+            <v>1528.7002889864307</v>
           </cell>
         </row>
         <row r="16">
@@ -2103,32 +2399,32 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>35700</v>
+            <v>33600</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>35700</v>
+            <v>28501.546862383388</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>0</v>
+            <v>1498.4531376166124</v>
           </cell>
         </row>
         <row r="16">
-          <cell r="K16" t="str">
-            <v/>
+          <cell r="K16">
+            <v>46201</v>
           </cell>
         </row>
         <row r="17">
-          <cell r="K17" t="str">
-            <v/>
+          <cell r="K17">
+            <v>46320</v>
           </cell>
         </row>
       </sheetData>
@@ -2241,32 +2537,32 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>23800</v>
+            <v>22400</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>23800</v>
+            <v>19001.031241588931</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>0</v>
+            <v>998.96875841106885</v>
           </cell>
         </row>
         <row r="16">
-          <cell r="K16" t="str">
-            <v/>
+          <cell r="K16">
+            <v>46204</v>
           </cell>
         </row>
         <row r="17">
-          <cell r="K17" t="str">
-            <v/>
+          <cell r="K17">
+            <v>46323</v>
           </cell>
         </row>
       </sheetData>
@@ -2310,32 +2606,32 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>23800</v>
+            <v>22400</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>23800</v>
+            <v>19001.031241588931</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>0</v>
+            <v>998.96875841106885</v>
           </cell>
         </row>
         <row r="16">
-          <cell r="K16" t="str">
-            <v/>
+          <cell r="K16">
+            <v>46202</v>
           </cell>
         </row>
         <row r="17">
-          <cell r="K17" t="str">
-            <v/>
+          <cell r="K17">
+            <v>46321</v>
           </cell>
         </row>
       </sheetData>
@@ -2531,9 +2827,15 @@
           </cell>
         </row>
         <row r="17">
-          <cell r="A17"/>
-          <cell r="C17"/>
-          <cell r="E17"/>
+          <cell r="A17">
+            <v>46202</v>
+          </cell>
+          <cell r="C17" t="str">
+            <v>Borrowing</v>
+          </cell>
+          <cell r="E17">
+            <v>160000</v>
+          </cell>
         </row>
         <row r="18">
           <cell r="A18"/>
@@ -2541,12 +2843,20 @@
           <cell r="E18"/>
         </row>
         <row r="19">
-          <cell r="A19" t="str">
-            <v>TOTAL</v>
-          </cell>
+          <cell r="A19"/>
           <cell r="C19"/>
-          <cell r="E19">
-            <v>288580</v>
+          <cell r="E19"/>
+        </row>
+        <row r="20">
+          <cell r="A20"/>
+          <cell r="C20"/>
+          <cell r="E20"/>
+        </row>
+        <row r="21">
+          <cell r="A21"/>
+          <cell r="C21"/>
+          <cell r="E21">
+            <v>448580</v>
           </cell>
         </row>
       </sheetData>
@@ -2730,22 +3040,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>37</v>
+            <v>40</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>41500</v>
+            <v>40000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>36520.516756917001</v>
+            <v>35358.098881814622</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>13479.483243082999</v>
+            <v>14641.901118185378</v>
           </cell>
         </row>
         <row r="16">
@@ -2857,22 +3167,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>11</v>
+            <v>17</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>43600</v>
+            <v>41200</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>36922.620435476056</v>
+            <v>35199.153684934674</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>3077.3795645239443</v>
+            <v>4800.8463150653261</v>
           </cell>
         </row>
         <row r="16">
@@ -2965,6 +3275,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Loan1"/>
+      <sheetName val="195"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -2995,22 +3306,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>15</v>
+            <v>17</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>19600</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>19025.859276770549</v>
+            <v>6.4028427004814148E-9</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>120974.14072322944</v>
+            <v>139999.9999999936</v>
           </cell>
         </row>
         <row r="16">
@@ -3021,6 +3332,63 @@
         <row r="17">
           <cell r="K17">
             <v>46213</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="K2" t="str">
+            <v>L180000W17-Sanarei_Group-N195</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="K3" t="str">
+            <v>Sanarei_Group</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="K7">
+            <v>180000</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="K9">
+            <v>12600</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="K10">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>214200</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="K14">
+            <v>214200</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="K15">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="K16" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="K17" t="str">
+            <v/>
           </cell>
         </row>
       </sheetData>
@@ -3064,22 +3432,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>15</v>
+            <v>16</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>2800</v>
+            <v>1400</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>2717.9798966815056</v>
+            <v>1372.4796393105025</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>17282.020103318493</v>
+            <v>18627.520360689497</v>
           </cell>
         </row>
         <row r="16">
@@ -3202,22 +3570,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>21</v>
+            <v>23</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>2850</v>
+            <v>2550</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>2603.6490690776168</v>
+            <v>2350.4407503985121</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>2396.3509309223832</v>
+            <v>2649.5592496014879</v>
           </cell>
         </row>
         <row r="16">
@@ -3514,53 +3882,53 @@
     <col min="13" max="13" width="13.85546875" style="1" customWidth="1"/>
     <col min="14" max="14" width="15.28515625" style="1" customWidth="1"/>
     <col min="15" max="15" width="1.42578125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="12" style="61" customWidth="1"/>
-    <col min="17" max="17" width="7.5703125" style="61" customWidth="1"/>
-    <col min="18" max="18" width="7.28515625" style="62" customWidth="1"/>
+    <col min="16" max="16" width="12" style="52" customWidth="1"/>
+    <col min="17" max="17" width="7.5703125" style="52" customWidth="1"/>
+    <col min="18" max="18" width="7.28515625" style="53" customWidth="1"/>
     <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="H1" s="56" t="s">
+      <c r="B1" s="62"/>
+      <c r="H1" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="57"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="59">
+      <c r="I1" s="67"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="69">
         <f>SUM(J5:J1000)</f>
-        <v>433390</v>
-      </c>
-      <c r="L1" s="60"/>
-      <c r="N1" s="54" t="s">
+        <v>612310</v>
+      </c>
+      <c r="L1" s="70"/>
+      <c r="N1" s="64" t="s">
         <v>25</v>
       </c>
       <c r="O1" s="10"/>
-      <c r="P1" s="54">
+      <c r="P1" s="64">
         <f>SUM(P5:P1000)</f>
-        <v>48570</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="53"/>
-      <c r="B2" s="53"/>
-      <c r="H2" s="56" t="s">
+      <c r="A2" s="63"/>
+      <c r="B2" s="63"/>
+      <c r="H2" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="57"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="59">
+      <c r="I2" s="67"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="69">
         <f>SUM(K5:K1000)</f>
-        <v>393670.49936032121</v>
-      </c>
-      <c r="L2" s="60"/>
+        <v>568559.65147229424</v>
+      </c>
+      <c r="L2" s="70"/>
       <c r="M2" s="2"/>
-      <c r="N2" s="55"/>
+      <c r="N2" s="65"/>
       <c r="O2" s="10"/>
-      <c r="P2" s="55"/>
+      <c r="P2" s="65"/>
     </row>
     <row r="3" spans="1:18" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3"/>
@@ -3616,7 +3984,7 @@
       <c r="N4" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="R4" s="61">
+      <c r="R4" s="52">
         <f>SUM(R5:R43)</f>
         <v>258000</v>
       </c>
@@ -3676,67 +4044,69 @@
         <f>[1]Loan1!$K$17</f>
         <v>46020</v>
       </c>
-      <c r="R5" s="61"/>
+      <c r="P5" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="R5" s="52"/>
     </row>
     <row r="6" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="39">
+      <c r="A6" s="44">
         <v>161</v>
       </c>
-      <c r="B6" s="39" t="str">
+      <c r="B6" s="44" t="str">
         <f>[2]Loan1!$K$3</f>
         <v>Ibeyaima</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="41" t="str">
+      <c r="D6" s="45" t="str">
         <f>[2]Loan1!$K$2</f>
         <v>L30000W17-Ibeyaima-NLoan1</v>
       </c>
-      <c r="E6" s="42">
+      <c r="E6" s="46">
         <f>[2]Loan1!$K$7</f>
         <v>30000</v>
       </c>
-      <c r="F6" s="39">
+      <c r="F6" s="44">
         <f>[2]Loan1!$K$9</f>
         <v>2100</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="47">
         <f>IF(H6,H6-I6,"")</f>
-        <v>2</v>
-      </c>
-      <c r="H6" s="39">
+        <v>0</v>
+      </c>
+      <c r="H6" s="44">
         <f>[2]Loan1!$K$10</f>
         <v>17</v>
       </c>
-      <c r="I6" s="39">
+      <c r="I6" s="44">
         <f>[2]Loan1!$K$12</f>
-        <v>15</v>
-      </c>
-      <c r="J6" s="42">
+        <v>17</v>
+      </c>
+      <c r="J6" s="46">
         <f>[2]Loan1!$K$13</f>
-        <v>4200</v>
-      </c>
-      <c r="K6" s="42">
+        <v>0</v>
+      </c>
+      <c r="K6" s="46">
         <f>[2]Loan1!$K$14</f>
-        <v>4076.9698450221713</v>
-      </c>
-      <c r="L6" s="43">
+        <v>1.2778400559909642E-9</v>
+      </c>
+      <c r="L6" s="48">
         <f>[2]Loan1!$K$15</f>
-        <v>25923.030154977831</v>
-      </c>
-      <c r="M6" s="23">
+        <v>29999.999999998723</v>
+      </c>
+      <c r="M6" s="49">
         <f>[2]Loan1!$K$16</f>
         <v>46089</v>
       </c>
-      <c r="N6" s="24">
+      <c r="N6" s="50">
         <f>[2]Loan1!$K$17</f>
         <v>46208</v>
       </c>
-      <c r="P6" s="61">
-        <v>2100</v>
-      </c>
-      <c r="R6" s="61"/>
+      <c r="O6" s="51"/>
+      <c r="P6" s="54"/>
+      <c r="R6" s="52"/>
     </row>
     <row r="7" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="36">
@@ -3764,7 +4134,7 @@
       </c>
       <c r="G7" s="22">
         <f t="shared" ref="G7:G17" si="0">IF(H7,H7-I7,"")</f>
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H7" s="36">
         <f>[3]Loan1!$K$10</f>
@@ -3772,19 +4142,19 @@
       </c>
       <c r="I7" s="36">
         <f>[3]Loan1!$K$12</f>
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J7" s="38">
         <f>[3]Loan1!$K$13</f>
-        <v>41500</v>
+        <v>40000</v>
       </c>
       <c r="K7" s="38">
         <f>[3]Loan1!$K$14</f>
-        <v>36520.516756917001</v>
+        <v>35358.098881814622</v>
       </c>
       <c r="L7" s="40">
         <f>[3]Loan1!$K$15</f>
-        <v>13479.483243082999</v>
+        <v>14641.901118185378</v>
       </c>
       <c r="M7" s="25">
         <f>[3]Loan1!$K$16</f>
@@ -3794,14 +4164,14 @@
         <f>[3]Loan1!$K$17</f>
         <v>46209</v>
       </c>
-      <c r="P7" s="64">
+      <c r="P7" s="55">
         <f>7*500</f>
         <v>3500</v>
       </c>
-      <c r="Q7" s="64" t="s">
+      <c r="Q7" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="R7" s="64">
+      <c r="R7" s="55">
         <v>30000</v>
       </c>
     </row>
@@ -3862,8 +4232,8 @@
         <v>46212</v>
       </c>
       <c r="O8" s="51"/>
-      <c r="P8" s="63"/>
-      <c r="R8" s="61"/>
+      <c r="P8" s="54"/>
+      <c r="R8" s="52"/>
     </row>
     <row r="9" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="36">
@@ -3921,77 +4291,76 @@
         <f>[5]Loan1!$K$17</f>
         <v>46212</v>
       </c>
-      <c r="P9" s="64">
+      <c r="P9" s="55">
         <f>7*200</f>
         <v>1400</v>
       </c>
-      <c r="Q9" s="64" t="s">
+      <c r="Q9" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="R9" s="64">
+      <c r="R9" s="55">
         <v>40000</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="39">
+      <c r="A10" s="44">
         <f t="shared" si="1"/>
         <v>165</v>
       </c>
-      <c r="B10" s="39" t="str">
+      <c r="B10" s="44" t="str">
         <f>[6]Loan1!$K$3</f>
         <v>Sanarei_Group</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="41" t="str">
+      <c r="D10" s="45" t="str">
         <f>[6]Loan1!$K$2</f>
         <v>L140000W17-Sanarei_Group-NLoan1</v>
       </c>
-      <c r="E10" s="42">
+      <c r="E10" s="46">
         <f>[6]Loan1!$K$7</f>
         <v>140000</v>
       </c>
-      <c r="F10" s="39">
+      <c r="F10" s="44">
         <f>[6]Loan1!$K$9</f>
         <v>9800</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="47">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H10" s="39">
+        <v>0</v>
+      </c>
+      <c r="H10" s="44">
         <f>[6]Loan1!$K$10</f>
         <v>17</v>
       </c>
-      <c r="I10" s="39">
+      <c r="I10" s="44">
         <f>[6]Loan1!$K$12</f>
-        <v>15</v>
-      </c>
-      <c r="J10" s="42">
+        <v>17</v>
+      </c>
+      <c r="J10" s="46">
         <f>[6]Loan1!$K$13</f>
-        <v>19600</v>
-      </c>
-      <c r="K10" s="42">
+        <v>0</v>
+      </c>
+      <c r="K10" s="46">
         <f>[6]Loan1!$K$14</f>
-        <v>19025.859276770549</v>
-      </c>
-      <c r="L10" s="43">
+        <v>6.4028427004814148E-9</v>
+      </c>
+      <c r="L10" s="48">
         <f>[6]Loan1!$K$15</f>
-        <v>120974.14072322944</v>
-      </c>
-      <c r="M10" s="23">
+        <v>139999.9999999936</v>
+      </c>
+      <c r="M10" s="49">
         <f>[6]Loan1!$K$16</f>
         <v>46094</v>
       </c>
-      <c r="N10" s="24">
+      <c r="N10" s="50">
         <f>[6]Loan1!$K$17</f>
         <v>46213</v>
       </c>
-      <c r="P10" s="61">
-        <v>9800</v>
-      </c>
-      <c r="R10" s="61"/>
+      <c r="O10" s="51"/>
+      <c r="P10" s="54"/>
+      <c r="R10" s="52"/>
     </row>
     <row r="11" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="36">
@@ -4018,7 +4387,7 @@
       </c>
       <c r="G11" s="22">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" s="36">
         <f>[7]Loan1!$K$10</f>
@@ -4026,19 +4395,19 @@
       </c>
       <c r="I11" s="36">
         <f>[7]Loan1!$K$12</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J11" s="38">
         <f>[7]Loan1!$K$13</f>
-        <v>2800</v>
+        <v>1400</v>
       </c>
       <c r="K11" s="38">
         <f>[7]Loan1!$K$14</f>
-        <v>2717.9798966815056</v>
+        <v>1372.4796393105025</v>
       </c>
       <c r="L11" s="40">
         <f>[7]Loan1!$K$15</f>
-        <v>17282.020103318493</v>
+        <v>18627.520360689497</v>
       </c>
       <c r="M11" s="25">
         <f>[7]Loan1!$K$16</f>
@@ -4048,10 +4417,10 @@
         <f>[7]Loan1!$K$17</f>
         <v>46216</v>
       </c>
-      <c r="P11" s="61">
+      <c r="P11" s="52">
         <v>1400</v>
       </c>
-      <c r="R11" s="61"/>
+      <c r="R11" s="52"/>
     </row>
     <row r="12" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="39">
@@ -4108,10 +4477,10 @@
         <f>[8]Loan1!$K$17</f>
         <v>46220</v>
       </c>
-      <c r="P12" s="61">
+      <c r="P12" s="52">
         <v>1400</v>
       </c>
-      <c r="R12" s="61"/>
+      <c r="R12" s="52"/>
     </row>
     <row r="13" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="36">
@@ -4139,7 +4508,7 @@
       </c>
       <c r="G13" s="22">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H13" s="36">
         <f>[9]Loan1!$K$10</f>
@@ -4147,19 +4516,19 @@
       </c>
       <c r="I13" s="36">
         <f>[9]Loan1!$K$12</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J13" s="38">
         <f>[9]Loan1!$K$13</f>
-        <v>2850</v>
+        <v>2550</v>
       </c>
       <c r="K13" s="38">
         <f>[9]Loan1!$K$14</f>
-        <v>2603.6490690776168</v>
+        <v>2350.4407503985121</v>
       </c>
       <c r="L13" s="40">
         <f>[9]Loan1!$K$15</f>
-        <v>2396.3509309223832</v>
+        <v>2649.5592496014879</v>
       </c>
       <c r="M13" s="25">
         <f>[9]Loan1!$K$16</f>
@@ -4169,74 +4538,73 @@
         <f>[9]Loan1!$K$17</f>
         <v>46215</v>
       </c>
-      <c r="P13" s="61">
+      <c r="P13" s="52">
         <f>7*150</f>
         <v>1050</v>
       </c>
-      <c r="R13" s="61"/>
+      <c r="R13" s="52"/>
     </row>
     <row r="14" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="39">
+      <c r="A14" s="44">
         <v>172</v>
       </c>
-      <c r="B14" s="39" t="str">
+      <c r="B14" s="44" t="str">
         <f>[10]Loan1!$K$3</f>
         <v>Mutum_Sandhyarani</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="41" t="str">
+      <c r="D14" s="45" t="str">
         <f>[10]Loan1!$K$2</f>
         <v>L10000W17-Mutum_Sandhyarani-NLoan1</v>
       </c>
-      <c r="E14" s="42">
+      <c r="E14" s="46">
         <f>[10]Loan1!$K$7</f>
         <v>10000</v>
       </c>
-      <c r="F14" s="39">
+      <c r="F14" s="44">
         <f>[10]Loan1!$K$9</f>
         <v>700</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="47">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="H14" s="39">
+        <v>0</v>
+      </c>
+      <c r="H14" s="44">
         <f>[10]Loan1!$K$10</f>
         <v>17</v>
       </c>
-      <c r="I14" s="39">
+      <c r="I14" s="44">
         <f>[10]Loan1!$K$12</f>
-        <v>11</v>
-      </c>
-      <c r="J14" s="42">
+        <v>17</v>
+      </c>
+      <c r="J14" s="46">
         <f>[10]Loan1!$K$13</f>
-        <v>4200</v>
-      </c>
-      <c r="K14" s="42">
+        <v>0</v>
+      </c>
+      <c r="K14" s="46">
         <f>[10]Loan1!$K$14</f>
-        <v>3920.3194223714245</v>
-      </c>
-      <c r="L14" s="43">
+        <v>4.5668002712773159E-10</v>
+      </c>
+      <c r="L14" s="48">
         <f>[10]Loan1!$K$15</f>
-        <v>6079.6805776285755</v>
-      </c>
-      <c r="M14" s="23">
+        <v>9999.9999999995434</v>
+      </c>
+      <c r="M14" s="49">
         <f>[10]Loan1!$K$16</f>
         <v>46129</v>
       </c>
-      <c r="N14" s="24">
+      <c r="N14" s="50">
         <f>[10]Loan1!$K$17</f>
         <v>46248</v>
       </c>
-      <c r="P14" s="64">
-        <v>700</v>
-      </c>
-      <c r="Q14" s="64" t="s">
+      <c r="O14" s="51"/>
+      <c r="P14" s="54"/>
+      <c r="Q14" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="R14" s="64">
+      <c r="R14" s="52">
         <v>5000</v>
       </c>
     </row>
@@ -4296,10 +4664,10 @@
         <f>[11]Loan1!$K$17</f>
         <v>46269</v>
       </c>
-      <c r="P15" s="61">
+      <c r="P15" s="52">
         <v>1400</v>
       </c>
-      <c r="R15" s="61"/>
+      <c r="R15" s="52"/>
     </row>
     <row r="16" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="39">
@@ -4327,7 +4695,7 @@
       </c>
       <c r="G16" s="22">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H16" s="39">
         <f>[12]Loan1!$K$10</f>
@@ -4335,19 +4703,19 @@
       </c>
       <c r="I16" s="39">
         <f>[12]Loan1!$K$12</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J16" s="42">
         <f>[12]Loan1!$K$13</f>
-        <v>12600</v>
+        <v>7000</v>
       </c>
       <c r="K16" s="42">
         <f>[12]Loan1!$K$14</f>
-        <v>11424.319854722999</v>
+        <v>6597.85590128073</v>
       </c>
       <c r="L16" s="43">
         <f>[12]Loan1!$K$15</f>
-        <v>8575.6801452770014</v>
+        <v>13402.144098719269</v>
       </c>
       <c r="M16" s="23">
         <f>[12]Loan1!$K$16</f>
@@ -4357,74 +4725,73 @@
         <f>[12]Loan1!$K$17</f>
         <v>46269</v>
       </c>
-      <c r="P16" s="61">
+      <c r="P16" s="52">
         <v>1400</v>
       </c>
-      <c r="R16" s="61"/>
+      <c r="R16" s="52"/>
     </row>
     <row r="17" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="36">
+      <c r="A17" s="44">
         <f t="shared" si="1"/>
         <v>175</v>
       </c>
-      <c r="B17" s="36" t="str">
+      <c r="B17" s="44" t="str">
         <f>[13]Loan1!$K$3</f>
         <v>Minarani</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="37" t="str">
+      <c r="D17" s="45" t="str">
         <f>[13]Loan1!$K$2</f>
         <v>L20000W12-Minarani-NLoan1</v>
       </c>
-      <c r="E17" s="38">
+      <c r="E17" s="46">
         <f>[13]Loan1!$K$7</f>
         <v>20000</v>
       </c>
-      <c r="F17" s="36">
+      <c r="F17" s="44">
         <f>[13]Loan1!$K$9</f>
         <v>2000</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="47">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="H17" s="36">
+        <v>0</v>
+      </c>
+      <c r="H17" s="44">
         <f>[13]Loan1!$K$10</f>
         <v>12</v>
       </c>
-      <c r="I17" s="36">
+      <c r="I17" s="44">
         <f>[13]Loan1!$K$12</f>
-        <v>7</v>
-      </c>
-      <c r="J17" s="38">
+        <v>12</v>
+      </c>
+      <c r="J17" s="46">
         <f>[13]Loan1!$K$13</f>
-        <v>10000</v>
-      </c>
-      <c r="K17" s="38">
+        <v>0</v>
+      </c>
+      <c r="K17" s="46">
         <f>[13]Loan1!$K$14</f>
-        <v>9179.6248403282825</v>
-      </c>
-      <c r="L17" s="40">
+        <v>6.2391336541622877E-10</v>
+      </c>
+      <c r="L17" s="48">
         <f>[13]Loan1!$K$15</f>
-        <v>10820.375159671717</v>
-      </c>
-      <c r="M17" s="25">
+        <v>19999.999999999374</v>
+      </c>
+      <c r="M17" s="49">
         <f>[13]Loan1!$K$16</f>
         <v>46156</v>
       </c>
-      <c r="N17" s="26">
+      <c r="N17" s="50">
         <f>[13]Loan1!$K$17</f>
         <v>46275</v>
       </c>
-      <c r="P17" s="64">
-        <v>2000</v>
-      </c>
-      <c r="Q17" s="64" t="s">
+      <c r="O17" s="51"/>
+      <c r="P17" s="54"/>
+      <c r="Q17" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="R17" s="64">
+      <c r="R17" s="52">
         <v>20000</v>
       </c>
     </row>
@@ -4454,7 +4821,7 @@
       </c>
       <c r="G18" s="22">
         <f t="shared" ref="G18:G21" si="2">IF(H18,H18-I18,"")</f>
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H18" s="39">
         <f>[14]Loan1!$K$10</f>
@@ -4462,19 +4829,19 @@
       </c>
       <c r="I18" s="39">
         <f>[14]Loan1!$K$12</f>
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J18" s="42">
         <f>[14]Loan1!$K$13</f>
-        <v>9000</v>
+        <v>8500</v>
       </c>
       <c r="K18" s="42">
         <f>[14]Loan1!$K$14</f>
-        <v>7838.2053538107648</v>
+        <v>7457.891976879012</v>
       </c>
       <c r="L18" s="43">
         <f>[14]Loan1!$K$15</f>
-        <v>2161.7946461892352</v>
+        <v>2542.108023120988</v>
       </c>
       <c r="M18" s="23">
         <f>[14]Loan1!$K$16</f>
@@ -4484,137 +4851,135 @@
         <f>[14]Loan1!$K$17</f>
         <v>46290</v>
       </c>
-      <c r="P18" s="64">
+      <c r="P18" s="55">
         <f>7*100</f>
         <v>700</v>
       </c>
-      <c r="Q18" s="64" t="s">
+      <c r="Q18" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="R18" s="64">
+      <c r="R18" s="55">
         <v>20000</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="36">
+      <c r="A19" s="44">
         <v>178</v>
       </c>
-      <c r="B19" s="36" t="str">
+      <c r="B19" s="44" t="str">
         <f>[15]Loan1!$K$3</f>
         <v>Lanchenbi_Ranibala</v>
       </c>
-      <c r="C19" s="36" t="s">
+      <c r="C19" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="37" t="str">
+      <c r="D19" s="45" t="str">
         <f>[15]Loan1!$K$2</f>
         <v>L20000W17-Lanchenbi_Ranibala-NLoan1</v>
       </c>
-      <c r="E19" s="38">
+      <c r="E19" s="46">
         <f>[15]Loan1!$K$7</f>
         <v>20000</v>
       </c>
-      <c r="F19" s="36">
+      <c r="F19" s="44">
         <f>[15]Loan1!$K$9</f>
         <v>1400</v>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="47">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="H19" s="36">
+        <v>0</v>
+      </c>
+      <c r="H19" s="44">
         <f>[15]Loan1!$K$10</f>
         <v>17</v>
       </c>
-      <c r="I19" s="36">
+      <c r="I19" s="44">
         <f>[15]Loan1!$K$12</f>
-        <v>13</v>
-      </c>
-      <c r="J19" s="38">
+        <v>17</v>
+      </c>
+      <c r="J19" s="46">
         <f>[15]Loan1!$K$13</f>
-        <v>5600</v>
-      </c>
-      <c r="K19" s="38">
+        <v>0</v>
+      </c>
+      <c r="K19" s="46">
         <f>[15]Loan1!$K$14</f>
-        <v>5330.1532184765038</v>
-      </c>
-      <c r="L19" s="40">
+        <v>9.1336005425546318E-10</v>
+      </c>
+      <c r="L19" s="48">
         <f>[15]Loan1!$K$15</f>
-        <v>14669.846781523496</v>
-      </c>
-      <c r="M19" s="25">
+        <v>19999.999999999087</v>
+      </c>
+      <c r="M19" s="49">
         <f>[15]Loan1!$K$16</f>
         <v>46101</v>
       </c>
-      <c r="N19" s="26">
+      <c r="N19" s="50">
         <f>[15]Loan1!$K$17</f>
         <v>46220</v>
       </c>
-      <c r="P19" s="61">
-        <v>1400</v>
-      </c>
-      <c r="R19" s="61"/>
+      <c r="O19" s="51"/>
+      <c r="P19" s="54"/>
+      <c r="R19" s="52"/>
     </row>
     <row r="20" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="39">
+      <c r="A20" s="44">
         <f t="shared" si="1"/>
         <v>179</v>
       </c>
-      <c r="B20" s="39" t="str">
+      <c r="B20" s="44" t="str">
         <f>[16]Loan1!$K$3</f>
         <v>Lanchenbi_Samila</v>
       </c>
-      <c r="C20" s="39" t="s">
+      <c r="C20" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="41" t="str">
+      <c r="D20" s="45" t="str">
         <f>[16]Loan1!$K$2</f>
         <v>L20000W17-Lanchenbi_Samila-NLoan1</v>
       </c>
-      <c r="E20" s="42">
+      <c r="E20" s="46">
         <f>[16]Loan1!$K$7</f>
         <v>20000</v>
       </c>
-      <c r="F20" s="39">
+      <c r="F20" s="44">
         <f>[16]Loan1!$K$9</f>
         <v>1400</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="47">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="H20" s="39">
+        <v>0</v>
+      </c>
+      <c r="H20" s="44">
         <f>[16]Loan1!$K$10</f>
         <v>17</v>
       </c>
-      <c r="I20" s="39">
+      <c r="I20" s="44">
         <f>[16]Loan1!$K$12</f>
-        <v>13</v>
-      </c>
-      <c r="J20" s="42">
+        <v>17</v>
+      </c>
+      <c r="J20" s="46">
         <f>[16]Loan1!$K$13</f>
-        <v>5600</v>
-      </c>
-      <c r="K20" s="42">
+        <v>0</v>
+      </c>
+      <c r="K20" s="46">
         <f>[16]Loan1!$K$14</f>
-        <v>5330.1532184765038</v>
-      </c>
-      <c r="L20" s="43">
+        <v>9.1336005425546318E-10</v>
+      </c>
+      <c r="L20" s="48">
         <f>[16]Loan1!$K$15</f>
-        <v>14669.846781523496</v>
-      </c>
-      <c r="M20" s="23">
+        <v>19999.999999999087</v>
+      </c>
+      <c r="M20" s="49">
         <f>[16]Loan1!$K$16</f>
         <v>46101</v>
       </c>
-      <c r="N20" s="24">
+      <c r="N20" s="50">
         <f>[16]Loan1!$K$17</f>
         <v>46220</v>
       </c>
-      <c r="P20" s="61">
-        <v>1400</v>
-      </c>
-      <c r="R20" s="61"/>
+      <c r="O20" s="51"/>
+      <c r="P20" s="54"/>
+      <c r="R20" s="52"/>
     </row>
     <row r="21" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="36">
@@ -4642,7 +5007,7 @@
       </c>
       <c r="G21" s="22">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H21" s="36">
         <f>[17]Loan1!$K$10</f>
@@ -4650,19 +5015,19 @@
       </c>
       <c r="I21" s="36">
         <f>[17]Loan1!$K$12</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J21" s="38">
         <f>[17]Loan1!$K$13</f>
-        <v>25200</v>
+        <v>27300</v>
       </c>
       <c r="K21" s="38">
         <f>[17]Loan1!$K$14</f>
-        <v>22201.185647927028</v>
+        <v>23823.487509187638</v>
       </c>
       <c r="L21" s="40">
         <f>[17]Loan1!$K$15</f>
-        <v>7798.8143520729718</v>
+        <v>6176.5124908123616</v>
       </c>
       <c r="M21" s="25">
         <f>[17]Loan1!$K$16</f>
@@ -4672,72 +5037,70 @@
         <f>[17]Loan1!$K$17</f>
         <v>46297</v>
       </c>
-      <c r="P21" s="61">
+      <c r="P21" s="52">
         <v>2100</v>
       </c>
-      <c r="R21" s="61"/>
+      <c r="R21" s="52"/>
     </row>
     <row r="22" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="39">
+      <c r="A22" s="44">
         <f t="shared" si="1"/>
         <v>181</v>
       </c>
-      <c r="B22" s="39" t="str">
+      <c r="B22" s="44" t="str">
         <f>[18]Loan1!$K$3</f>
         <v>Inaobi</v>
       </c>
-      <c r="C22" s="39" t="s">
+      <c r="C22" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="D22" s="41" t="str">
+      <c r="D22" s="45" t="str">
         <f>[18]Loan1!$K$2</f>
         <v>L7000D80-Inaobi-NLoan1</v>
       </c>
-      <c r="E22" s="42">
+      <c r="E22" s="46">
         <f>[18]Loan1!$K$7</f>
         <v>7000</v>
       </c>
-      <c r="F22" s="39">
+      <c r="F22" s="44">
         <f>[18]Loan1!$K$9</f>
         <v>100</v>
       </c>
-      <c r="G22" s="22">
+      <c r="G22" s="47">
         <f t="shared" ref="G22:G25" si="3">IF(H22,H22-I22,"")</f>
-        <v>75</v>
-      </c>
-      <c r="H22" s="39">
+        <v>0</v>
+      </c>
+      <c r="H22" s="44">
         <f>[18]Loan1!$K$10</f>
         <v>80</v>
       </c>
-      <c r="I22" s="39">
+      <c r="I22" s="44">
         <f>[18]Loan1!$K$12</f>
-        <v>5</v>
-      </c>
-      <c r="J22" s="42">
+        <v>80</v>
+      </c>
+      <c r="J22" s="46">
         <f>[18]Loan1!$K$13</f>
-        <v>7500</v>
-      </c>
-      <c r="K22" s="42">
+        <v>0</v>
+      </c>
+      <c r="K22" s="46">
         <f>[18]Loan1!$K$14</f>
-        <v>6615.6271011002946</v>
-      </c>
-      <c r="L22" s="43">
+        <v>-1.2721557141048834E-10</v>
+      </c>
+      <c r="L22" s="48">
         <f>[18]Loan1!$K$15</f>
-        <v>384.37289889970543</v>
-      </c>
-      <c r="M22" s="23">
+        <v>7000.0000000001273</v>
+      </c>
+      <c r="M22" s="49">
         <f>[18]Loan1!$K$16</f>
         <v>46175</v>
       </c>
-      <c r="N22" s="24">
+      <c r="N22" s="50">
         <f>[18]Loan1!$K$17</f>
         <v>46295</v>
       </c>
-      <c r="P22" s="61">
-        <f>7*100</f>
-        <v>700</v>
-      </c>
-      <c r="R22" s="61"/>
+      <c r="O22" s="51"/>
+      <c r="P22" s="54"/>
+      <c r="R22" s="52"/>
     </row>
     <row r="23" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="36">
@@ -4765,7 +5128,7 @@
       </c>
       <c r="G23" s="22">
         <f t="shared" si="3"/>
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="H23" s="36">
         <f>[19]Loan1!$K$10</f>
@@ -4773,19 +5136,19 @@
       </c>
       <c r="I23" s="36">
         <f>[19]Loan1!$K$12</f>
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="J23" s="38">
         <f>[19]Loan1!$K$13</f>
-        <v>19800</v>
+        <v>15660</v>
       </c>
       <c r="K23" s="38">
         <f>[19]Loan1!$K$14</f>
-        <v>16743.038328281105</v>
+        <v>13699.308972116984</v>
       </c>
       <c r="L23" s="40">
         <f>[19]Loan1!$K$15</f>
-        <v>1256.9616717188946</v>
+        <v>4300.6910278830164</v>
       </c>
       <c r="M23" s="25">
         <f>[19]Loan1!$K$16</f>
@@ -4795,14 +5158,14 @@
         <f>[19]Loan1!$K$17</f>
         <v>46295</v>
       </c>
-      <c r="P23" s="64">
+      <c r="P23" s="55">
         <f>7*180</f>
         <v>1260</v>
       </c>
-      <c r="Q23" s="64" t="s">
+      <c r="Q23" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="R23" s="64">
+      <c r="R23" s="55">
         <v>7000</v>
       </c>
     </row>
@@ -4832,7 +5195,7 @@
       </c>
       <c r="G24" s="22">
         <f t="shared" si="3"/>
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="H24" s="39">
         <f>[20]Loan1!$K$10</f>
@@ -4840,19 +5203,19 @@
       </c>
       <c r="I24" s="39">
         <f>[20]Loan1!$K$12</f>
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="J24" s="42">
         <f>[20]Loan1!$K$13</f>
-        <v>20340</v>
+        <v>16200</v>
       </c>
       <c r="K24" s="42">
         <f>[20]Loan1!$K$14</f>
-        <v>17124.239007894535</v>
+        <v>14108.769636859435</v>
       </c>
       <c r="L24" s="43">
         <f>[20]Loan1!$K$15</f>
-        <v>875.76099210546454</v>
+        <v>3891.2303631405648</v>
       </c>
       <c r="M24" s="23">
         <f>[20]Loan1!$K$16</f>
@@ -4862,14 +5225,14 @@
         <f>[20]Loan1!$K$17</f>
         <v>46295</v>
       </c>
-      <c r="P24" s="64">
+      <c r="P24" s="55">
         <f>7*180</f>
         <v>1260</v>
       </c>
-      <c r="Q24" s="64" t="s">
+      <c r="Q24" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="R24" s="64">
+      <c r="R24" s="55">
         <v>18000</v>
       </c>
     </row>
@@ -4899,7 +5262,7 @@
       </c>
       <c r="G25" s="22">
         <f t="shared" si="3"/>
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="H25" s="36">
         <f>[14]Loan2!$K$10</f>
@@ -4907,19 +5270,19 @@
       </c>
       <c r="I25" s="36">
         <f>[14]Loan2!$K$12</f>
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J25" s="38">
         <f>[14]Loan2!$K$13</f>
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="K25" s="38">
         <f>[14]Loan2!$K$14</f>
-        <v>8360.8080101606047</v>
+        <v>7988.68287277732</v>
       </c>
       <c r="L25" s="40">
         <f>[14]Loan2!$K$15</f>
-        <v>1639.1919898393953</v>
+        <v>2011.31712722268</v>
       </c>
       <c r="M25" s="25">
         <f>[14]Loan2!$K$16</f>
@@ -4929,14 +5292,14 @@
         <f>[14]Loan2!$K$17</f>
         <v>46297</v>
       </c>
-      <c r="P25" s="64">
+      <c r="P25" s="55">
         <f>7*100</f>
         <v>700</v>
       </c>
-      <c r="Q25" s="64" t="s">
+      <c r="Q25" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="R25" s="64">
+      <c r="R25" s="55">
         <v>18000</v>
       </c>
     </row>
@@ -4966,7 +5329,7 @@
       </c>
       <c r="G26" s="22">
         <f t="shared" ref="G26:G89" si="4">IF(H26,H26-I26,"")</f>
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H26" s="39">
         <f>[21]Loan1!$K$10</f>
@@ -4974,19 +5337,19 @@
       </c>
       <c r="I26" s="39">
         <f>[21]Loan1!$K$12</f>
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J26" s="42">
         <f>[21]Loan1!$K$13</f>
-        <v>10100</v>
+        <v>9600</v>
       </c>
       <c r="K26" s="42">
         <f>[21]Loan1!$K$14</f>
-        <v>8654.3706289841193</v>
+        <v>8286.8450875198287</v>
       </c>
       <c r="L26" s="43">
         <f>[21]Loan1!$K$15</f>
-        <v>1345.6293710158807</v>
+        <v>1713.1549124801713</v>
       </c>
       <c r="M26" s="23">
         <f>[21]Loan1!$K$16</f>
@@ -4996,14 +5359,14 @@
         <f>[21]Loan1!$K$17</f>
         <v>46298</v>
       </c>
-      <c r="P26" s="64">
+      <c r="P26" s="55">
         <f>7*100</f>
         <v>700</v>
       </c>
-      <c r="Q26" s="64" t="s">
+      <c r="Q26" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="R26" s="64">
+      <c r="R26" s="55">
         <v>10000</v>
       </c>
     </row>
@@ -5063,13 +5426,13 @@
         <f>[22]Loan1!$K$17</f>
         <v>46304</v>
       </c>
-      <c r="P27" s="64">
+      <c r="P27" s="55">
         <v>1400</v>
       </c>
-      <c r="Q27" s="64" t="s">
+      <c r="Q27" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="R27" s="64">
+      <c r="R27" s="55">
         <v>10000</v>
       </c>
     </row>
@@ -5099,7 +5462,7 @@
       </c>
       <c r="G28" s="22">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H28" s="39">
         <f>[23]Loan1!$K$10</f>
@@ -5107,19 +5470,19 @@
       </c>
       <c r="I28" s="39">
         <f>[23]Loan1!$K$12</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J28" s="42">
         <f>[23]Loan1!$K$13</f>
-        <v>10500</v>
+        <v>9800</v>
       </c>
       <c r="K28" s="42">
         <f>[23]Loan1!$K$14</f>
-        <v>8991.0157995515765</v>
+        <v>8471.2997110135693</v>
       </c>
       <c r="L28" s="43">
         <f>[23]Loan1!$K$15</f>
-        <v>1008.9842004484235</v>
+        <v>1528.7002889864307</v>
       </c>
       <c r="M28" s="23">
         <f>[23]Loan1!$K$16</f>
@@ -5129,10 +5492,10 @@
         <f>[23]Loan1!$K$17</f>
         <v>46309</v>
       </c>
-      <c r="P28" s="61">
+      <c r="P28" s="52">
         <v>700</v>
       </c>
-      <c r="R28" s="61"/>
+      <c r="R28" s="52"/>
     </row>
     <row r="29" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="36">
@@ -5160,7 +5523,7 @@
       </c>
       <c r="G29" s="22">
         <f t="shared" si="4"/>
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H29" s="36">
         <f>'[4]188'!$K$10</f>
@@ -5168,19 +5531,19 @@
       </c>
       <c r="I29" s="36">
         <f>'[4]188'!$K$12</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J29" s="38">
         <f>'[4]188'!$K$13</f>
-        <v>43600</v>
+        <v>41200</v>
       </c>
       <c r="K29" s="38">
         <f>'[4]188'!$K$14</f>
-        <v>36922.620435476056</v>
+        <v>35199.153684934674</v>
       </c>
       <c r="L29" s="40">
         <f>'[4]188'!$K$15</f>
-        <v>3077.3795645239443</v>
+        <v>4800.8463150653261</v>
       </c>
       <c r="M29" s="25">
         <f>'[4]188'!$K$16</f>
@@ -5190,14 +5553,14 @@
         <f>'[4]188'!$K$17</f>
         <v>46310</v>
       </c>
-      <c r="P29" s="64">
+      <c r="P29" s="55">
         <f>400*7</f>
         <v>2800</v>
       </c>
-      <c r="Q29" s="64" t="s">
+      <c r="Q29" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="R29" s="64">
+      <c r="R29" s="55">
         <v>10000</v>
       </c>
     </row>
@@ -5227,7 +5590,7 @@
       </c>
       <c r="G30" s="22">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H30" s="39">
         <f>'[13]189'!$K$10</f>
@@ -5235,19 +5598,19 @@
       </c>
       <c r="I30" s="39">
         <f>'[13]189'!$K$12</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="42">
         <f>'[13]189'!$K$13</f>
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="K30" s="42">
         <f>'[13]189'!$K$14</f>
-        <v>9292.2854076913736</v>
+        <v>8563.885350568542</v>
       </c>
       <c r="L30" s="43">
         <f>'[13]189'!$K$15</f>
-        <v>707.71459230862638</v>
+        <v>1436.114649431458</v>
       </c>
       <c r="M30" s="23">
         <f>'[13]189'!$K$16</f>
@@ -5257,13 +5620,13 @@
         <f>'[13]189'!$K$17</f>
         <v>46312</v>
       </c>
-      <c r="P30" s="64">
+      <c r="P30" s="55">
         <v>1000</v>
       </c>
-      <c r="Q30" s="64" t="s">
+      <c r="Q30" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="R30" s="64">
+      <c r="R30" s="55">
         <v>40000</v>
       </c>
     </row>
@@ -5293,7 +5656,7 @@
       </c>
       <c r="G31" s="22">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H31" s="36">
         <f>'[12]190'!$K$10</f>
@@ -5301,19 +5664,19 @@
       </c>
       <c r="I31" s="36">
         <f>'[12]190'!$K$12</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="38">
         <f>'[12]190'!$K$13</f>
-        <v>10500</v>
+        <v>9800</v>
       </c>
       <c r="K31" s="38">
         <f>'[12]190'!$K$14</f>
-        <v>8991.0157995515765</v>
+        <v>8471.2997110135693</v>
       </c>
       <c r="L31" s="40">
         <f>'[12]190'!$K$15</f>
-        <v>1008.9842004484235</v>
+        <v>1528.7002889864307</v>
       </c>
       <c r="M31" s="25">
         <f>'[12]190'!$K$16</f>
@@ -5323,10 +5686,10 @@
         <f>'[12]190'!$K$17</f>
         <v>46313</v>
       </c>
-      <c r="P31" s="61">
+      <c r="P31" s="52">
         <v>700</v>
       </c>
-      <c r="R31" s="61"/>
+      <c r="R31" s="52"/>
     </row>
     <row r="32" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
@@ -5354,7 +5717,7 @@
       </c>
       <c r="G32" s="22">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H32" s="39">
         <f>'[24]191'!$K$10</f>
@@ -5362,35 +5725,35 @@
       </c>
       <c r="I32" s="39">
         <f>'[24]191'!$K$12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="42">
         <f>'[24]191'!$K$13</f>
-        <v>35700</v>
+        <v>33600</v>
       </c>
       <c r="K32" s="42">
         <f>'[24]191'!$K$14</f>
-        <v>35700</v>
+        <v>28501.546862383388</v>
       </c>
       <c r="L32" s="43">
         <f>'[24]191'!$K$15</f>
-        <v>0</v>
-      </c>
-      <c r="M32" s="23" t="str">
+        <v>1498.4531376166124</v>
+      </c>
+      <c r="M32" s="23">
         <f>'[24]191'!$K$16</f>
-        <v/>
-      </c>
-      <c r="N32" s="24" t="str">
+        <v>46201</v>
+      </c>
+      <c r="N32" s="24">
         <f>'[24]191'!$K$17</f>
-        <v/>
-      </c>
-      <c r="P32" s="64">
+        <v>46320</v>
+      </c>
+      <c r="P32" s="55">
         <v>2100</v>
       </c>
-      <c r="Q32" s="64" t="s">
+      <c r="Q32" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="R32" s="64">
+      <c r="R32" s="55">
         <v>10000</v>
       </c>
     </row>
@@ -5450,10 +5813,10 @@
         <f>'[25]192'!$K$17</f>
         <v/>
       </c>
-      <c r="P33" s="61">
+      <c r="P33" s="52">
         <v>700</v>
       </c>
-      <c r="R33" s="61"/>
+      <c r="R33" s="52"/>
     </row>
     <row r="34" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
@@ -5481,7 +5844,7 @@
       </c>
       <c r="G34" s="22">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H34" s="39">
         <f>'[26]193'!$K$10</f>
@@ -5489,32 +5852,32 @@
       </c>
       <c r="I34" s="39">
         <f>'[26]193'!$K$12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="42">
         <f>'[26]193'!$K$13</f>
-        <v>23800</v>
+        <v>22400</v>
       </c>
       <c r="K34" s="42">
         <f>'[26]193'!$K$14</f>
-        <v>23800</v>
+        <v>19001.031241588931</v>
       </c>
       <c r="L34" s="43">
         <f>'[26]193'!$K$15</f>
-        <v>0</v>
-      </c>
-      <c r="M34" s="23" t="str">
+        <v>998.96875841106885</v>
+      </c>
+      <c r="M34" s="23">
         <f>'[26]193'!$K$16</f>
-        <v/>
-      </c>
-      <c r="N34" s="24" t="str">
+        <v>46204</v>
+      </c>
+      <c r="N34" s="24">
         <f>'[26]193'!$K$17</f>
-        <v/>
-      </c>
-      <c r="P34" s="61">
+        <v>46323</v>
+      </c>
+      <c r="P34" s="52">
         <v>1400</v>
       </c>
-      <c r="R34" s="61"/>
+      <c r="R34" s="52"/>
     </row>
     <row r="35" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="36">
@@ -5542,7 +5905,7 @@
       </c>
       <c r="G35" s="22">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H35" s="36">
         <f>'[27]194'!$K$10</f>
@@ -5550,35 +5913,35 @@
       </c>
       <c r="I35" s="36">
         <f>'[27]194'!$K$12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="38">
         <f>'[27]194'!$K$13</f>
-        <v>23800</v>
+        <v>22400</v>
       </c>
       <c r="K35" s="38">
         <f>'[27]194'!$K$14</f>
-        <v>23800</v>
+        <v>19001.031241588931</v>
       </c>
       <c r="L35" s="40">
         <f>'[27]194'!$K$15</f>
-        <v>0</v>
-      </c>
-      <c r="M35" s="25" t="str">
+        <v>998.96875841106885</v>
+      </c>
+      <c r="M35" s="25">
         <f>'[27]194'!$K$16</f>
-        <v/>
-      </c>
-      <c r="N35" s="26" t="str">
+        <v>46202</v>
+      </c>
+      <c r="N35" s="26">
         <f>'[27]194'!$K$17</f>
-        <v/>
-      </c>
-      <c r="P35" s="64">
+        <v>46321</v>
+      </c>
+      <c r="P35" s="55">
         <v>1400</v>
       </c>
-      <c r="Q35" s="64" t="s">
+      <c r="Q35" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="R35" s="64">
+      <c r="R35" s="55">
         <v>20000</v>
       </c>
     </row>
@@ -5587,89 +5950,241 @@
         <f t="shared" si="1"/>
         <v>195</v>
       </c>
-      <c r="B36" s="39"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="22" t="str">
+      <c r="B36" s="39" t="str">
+        <f>'[6]195'!$K$3</f>
+        <v>Sanarei_Group</v>
+      </c>
+      <c r="C36" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="41" t="str">
+        <f>'[6]195'!$K$2</f>
+        <v>L180000W17-Sanarei_Group-N195</v>
+      </c>
+      <c r="E36" s="42">
+        <f>'[6]195'!$K$7</f>
+        <v>180000</v>
+      </c>
+      <c r="F36" s="39">
+        <f>'[6]195'!$K$9</f>
+        <v>12600</v>
+      </c>
+      <c r="G36" s="22">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H36" s="39"/>
-      <c r="I36" s="39"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="43"/>
-      <c r="M36" s="23"/>
-      <c r="N36" s="24"/>
-      <c r="R36" s="61"/>
+        <v>17</v>
+      </c>
+      <c r="H36" s="39">
+        <f>'[6]195'!$K$10</f>
+        <v>17</v>
+      </c>
+      <c r="I36" s="39">
+        <f>'[6]195'!$K$12</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="42">
+        <f>'[6]195'!$K$13</f>
+        <v>214200</v>
+      </c>
+      <c r="K36" s="42">
+        <f>'[6]195'!$K$14</f>
+        <v>214200</v>
+      </c>
+      <c r="L36" s="43">
+        <f>'[6]195'!$K$15</f>
+        <v>0</v>
+      </c>
+      <c r="M36" s="23" t="str">
+        <f>'[6]195'!$K$16</f>
+        <v/>
+      </c>
+      <c r="N36" s="24" t="str">
+        <f>'[6]195'!$K$17</f>
+        <v/>
+      </c>
+      <c r="P36" s="52">
+        <v>12600</v>
+      </c>
+      <c r="R36" s="52"/>
     </row>
     <row r="37" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="36">
         <f t="shared" si="1"/>
         <v>196</v>
       </c>
-      <c r="B37" s="36"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="37"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="22" t="str">
+      <c r="B37" s="36" t="str">
+        <f>'[15]196'!$K$3</f>
+        <v>Lanchenbi_Ranibala</v>
+      </c>
+      <c r="C37" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="37" t="str">
+        <f>'[15]196'!$K$2</f>
+        <v>L10000W17-Lanchenbi_Ranibala-N196</v>
+      </c>
+      <c r="E37" s="38">
+        <f>'[15]196'!$K$7</f>
+        <v>10000</v>
+      </c>
+      <c r="F37" s="36">
+        <f>'[15]196'!$K$9</f>
+        <v>700</v>
+      </c>
+      <c r="G37" s="22">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H37" s="36"/>
-      <c r="I37" s="36"/>
-      <c r="J37" s="38"/>
-      <c r="K37" s="38"/>
-      <c r="L37" s="40"/>
-      <c r="M37" s="25"/>
-      <c r="N37" s="26"/>
+        <v>17</v>
+      </c>
+      <c r="H37" s="36">
+        <f>'[15]196'!$K$10</f>
+        <v>17</v>
+      </c>
+      <c r="I37" s="36">
+        <f>'[15]196'!$K$12</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="38">
+        <f>'[15]196'!$K$13</f>
+        <v>11900</v>
+      </c>
+      <c r="K37" s="38">
+        <f>'[15]196'!$K$14</f>
+        <v>11900</v>
+      </c>
+      <c r="L37" s="40">
+        <f>'[15]196'!$K$15</f>
+        <v>0</v>
+      </c>
+      <c r="M37" s="25" t="str">
+        <f>'[15]196'!$K$16</f>
+        <v/>
+      </c>
+      <c r="N37" s="26" t="str">
+        <f>'[15]196'!$K$17</f>
+        <v/>
+      </c>
+      <c r="P37" s="52">
+        <v>700</v>
+      </c>
     </row>
     <row r="38" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="39">
         <f t="shared" si="1"/>
         <v>197</v>
       </c>
-      <c r="B38" s="39"/>
-      <c r="C38" s="39"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="42"/>
-      <c r="F38" s="39"/>
-      <c r="G38" s="22" t="str">
+      <c r="B38" s="39" t="str">
+        <f>'[16]197'!$K$3</f>
+        <v>Lanchenbi_Samila</v>
+      </c>
+      <c r="C38" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="41" t="str">
+        <f>'[16]197'!$K$2</f>
+        <v>L10000W17-Lanchenbi_Samila-N197</v>
+      </c>
+      <c r="E38" s="42">
+        <f>'[16]197'!$K$7</f>
+        <v>10000</v>
+      </c>
+      <c r="F38" s="39">
+        <f>'[16]197'!$K$9</f>
+        <v>700</v>
+      </c>
+      <c r="G38" s="22">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H38" s="39"/>
-      <c r="I38" s="39"/>
-      <c r="J38" s="42"/>
-      <c r="K38" s="42"/>
-      <c r="L38" s="43"/>
-      <c r="M38" s="23"/>
-      <c r="N38" s="24"/>
+        <v>17</v>
+      </c>
+      <c r="H38" s="39">
+        <f>'[16]197'!$K$10</f>
+        <v>17</v>
+      </c>
+      <c r="I38" s="39">
+        <f>'[16]197'!$K$12</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="42">
+        <f>'[16]197'!$K$13</f>
+        <v>11900</v>
+      </c>
+      <c r="K38" s="42">
+        <f>'[16]197'!$K$14</f>
+        <v>11900</v>
+      </c>
+      <c r="L38" s="43">
+        <f>'[16]197'!$K$15</f>
+        <v>0</v>
+      </c>
+      <c r="M38" s="23" t="str">
+        <f>'[16]197'!$K$16</f>
+        <v/>
+      </c>
+      <c r="N38" s="24" t="str">
+        <f>'[16]197'!$K$17</f>
+        <v/>
+      </c>
+      <c r="P38" s="52">
+        <v>700</v>
+      </c>
     </row>
     <row r="39" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="36">
         <f t="shared" si="1"/>
         <v>198</v>
       </c>
-      <c r="B39" s="36"/>
-      <c r="C39" s="36"/>
-      <c r="D39" s="37"/>
-      <c r="E39" s="38"/>
-      <c r="F39" s="36"/>
-      <c r="G39" s="22" t="str">
+      <c r="B39" s="36" t="str">
+        <f>'[10]198'!$K$3</f>
+        <v>Mutum_Sandhyarani</v>
+      </c>
+      <c r="C39" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="37" t="str">
+        <f>'[10]198'!$K$2</f>
+        <v>L20000W17-Mutum_Sandhyarani-N198</v>
+      </c>
+      <c r="E39" s="38">
+        <f>'[10]198'!$K$7</f>
+        <v>20000</v>
+      </c>
+      <c r="F39" s="36">
+        <f>'[10]198'!$K$9</f>
+        <v>1400</v>
+      </c>
+      <c r="G39" s="22">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H39" s="36"/>
-      <c r="I39" s="36"/>
-      <c r="J39" s="38"/>
-      <c r="K39" s="38"/>
-      <c r="L39" s="40"/>
-      <c r="M39" s="25"/>
-      <c r="N39" s="26"/>
+        <v>17</v>
+      </c>
+      <c r="H39" s="36">
+        <f>'[10]198'!$K$10</f>
+        <v>17</v>
+      </c>
+      <c r="I39" s="36">
+        <f>'[10]198'!$K$12</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="38">
+        <f>'[10]198'!$K$13</f>
+        <v>23800</v>
+      </c>
+      <c r="K39" s="38">
+        <f>'[10]198'!$K$14</f>
+        <v>23800</v>
+      </c>
+      <c r="L39" s="40">
+        <f>'[10]198'!$K$15</f>
+        <v>0</v>
+      </c>
+      <c r="M39" s="25" t="str">
+        <f>'[10]198'!$K$16</f>
+        <v/>
+      </c>
+      <c r="N39" s="26" t="str">
+        <f>'[10]198'!$K$17</f>
+        <v/>
+      </c>
+      <c r="P39" s="52">
+        <v>1400</v>
+      </c>
     </row>
     <row r="40" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="39">
@@ -5736,6 +6251,7 @@
       <c r="L42" s="43"/>
       <c r="M42" s="23"/>
       <c r="N42" s="24"/>
+      <c r="P42" s="56"/>
     </row>
     <row r="43" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="36">
@@ -15206,7 +15722,7 @@
       <c r="D474" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="GWmLhFTmIlS5K1i0+YCR8d2JhbAItpfzVjbVEbd4N1LJHquon3ZBXQr7eW+bUn2yys5ZXTfcL572gvd7uO/yvQ==" saltValue="ZN0wht6rWA5fV+WPzbY30Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ZsPb2WNZ5bpmVZ80ZAO9lERZw/VTHn+Sl4laUG5TBEw8iy+zjfqj/TR+Sh9JNghhjv9tLejea/knocWpRu1NbQ==" saltValue="fiXaANeEpUju33S6bvWOyA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="7">
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="N1:N2"/>
@@ -15216,7 +15732,7 @@
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="K1:L1"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C472">
       <formula1>"Active, Closed"</formula1>
     </dataValidation>
@@ -15228,7 +15744,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.42578125" style="1" customWidth="1"/>
@@ -15898,165 +16414,211 @@
       <c r="P13" s="9"/>
     </row>
     <row r="14" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="11"/>
-      <c r="B14" s="14" t="str">
+      <c r="A14" s="11">
+        <v>46202</v>
+      </c>
+      <c r="B14" s="14" t="e">
         <f>IF(A14&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A14),
     "")</f>
-        <v/>
-      </c>
-      <c r="C14" s="15" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C14" s="15" t="e">
         <f>IF(A14&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A14),
     "")</f>
-        <v/>
-      </c>
-      <c r="D14" s="15" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D14" s="15" t="e">
         <f>IF(A14&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A14),
     "")</f>
-        <v/>
-      </c>
-      <c r="E14" s="16" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E14" s="16" t="e">
         <f>IF(A14&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A14),
     "")</f>
-        <v/>
-      </c>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="34"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F14" s="29">
+        <v>1044150</v>
+      </c>
+      <c r="G14" s="29">
+        <v>32670</v>
+      </c>
+      <c r="H14" s="29">
+        <v>376330</v>
+      </c>
+      <c r="I14" s="29">
+        <v>333484.34457397927</v>
+      </c>
+      <c r="J14" s="34" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="15" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="17"/>
-      <c r="B15" s="18" t="str">
+      <c r="A15" s="17">
+        <v>46202</v>
+      </c>
+      <c r="B15" s="18" t="e">
         <f>IF(A15&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A15),
     "")</f>
-        <v/>
-      </c>
-      <c r="C15" s="19" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C15" s="19" t="e">
         <f>IF(A15&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A15),
     "")</f>
-        <v/>
-      </c>
-      <c r="D15" s="19" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D15" s="19" t="e">
         <f>IF(A15&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A15),
     "")</f>
-        <v/>
-      </c>
-      <c r="E15" s="20" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E15" s="20" t="e">
         <f>IF(A15&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A15),
     "")</f>
-        <v/>
-      </c>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F15" s="32">
+        <v>1080250</v>
+      </c>
+      <c r="G15" s="32">
+        <v>2670</v>
+      </c>
+      <c r="H15" s="32">
+        <v>602430</v>
+      </c>
+      <c r="I15" s="32">
+        <v>559584.34457397927</v>
+      </c>
+      <c r="J15" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="P15" s="9"/>
     </row>
     <row r="16" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="11"/>
-      <c r="B16" s="14" t="str">
+      <c r="A16" s="11">
+        <v>46204</v>
+      </c>
+      <c r="B16" s="14" t="e">
         <f>IF(A16&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A16),
     "")</f>
-        <v/>
-      </c>
-      <c r="C16" s="15" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C16" s="15" t="e">
         <f>IF(A16&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A16),
     "")</f>
-        <v/>
-      </c>
-      <c r="D16" s="15" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D16" s="15" t="e">
         <f>IF(A16&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A16),
     "")</f>
-        <v/>
-      </c>
-      <c r="E16" s="16" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E16" s="16" t="e">
         <f>IF(A16&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A16),
     "")</f>
-        <v/>
-      </c>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F16" s="29">
+        <v>1080250</v>
+      </c>
+      <c r="G16" s="29">
+        <v>28490</v>
+      </c>
+      <c r="H16" s="29">
+        <v>576610</v>
+      </c>
+      <c r="I16" s="29">
+        <v>532859.65147229424</v>
+      </c>
       <c r="J16" s="34"/>
     </row>
     <row r="17" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="17"/>
-      <c r="B17" s="18" t="str">
+      <c r="A17" s="17">
+        <v>46204</v>
+      </c>
+      <c r="B17" s="18" t="e">
         <f>IF(A17&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A17),
     "")</f>
-        <v/>
-      </c>
-      <c r="C17" s="19" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C17" s="19" t="e">
         <f>IF(A17&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A17),
     "")</f>
-        <v/>
-      </c>
-      <c r="D17" s="19" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D17" s="19" t="e">
         <f>IF(A17&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A17),
     "")</f>
-        <v/>
-      </c>
-      <c r="E17" s="20" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E17" s="20" t="e">
         <f>IF(A17&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A17),
     "")</f>
-        <v/>
-      </c>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F17" s="32">
+        <v>1085950</v>
+      </c>
+      <c r="G17" s="32">
+        <v>-1510</v>
+      </c>
+      <c r="H17" s="32">
+        <v>612310</v>
+      </c>
+      <c r="I17" s="32">
+        <v>568559.65147229424</v>
+      </c>
+      <c r="J17" s="35" t="s">
+        <v>39</v>
+      </c>
       <c r="P17" s="9"/>
     </row>
     <row r="18" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -16140,9 +16702,278 @@
       <c r="J19" s="35"/>
       <c r="P19" s="9"/>
     </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="J20" s="57"/>
+    </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="Pr4ttaMbAD7lulxdoRkM8I5OK0x5TznjcP16kg7dLKVW5k2UUpg7q30kix36rJ5+QbR2M9Otb5eoeHz0IxuVpg==" saltValue="b4mNrdrPjC50AT2lDgxUzw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:C29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="26.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="58">
+        <v>1</v>
+      </c>
+      <c r="B3" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="11"/>
+    </row>
+    <row r="4" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="59">
+        <v>2</v>
+      </c>
+      <c r="B4" s="61" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="17"/>
+    </row>
+    <row r="5" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="58">
+        <v>3</v>
+      </c>
+      <c r="B5" s="60" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="11"/>
+    </row>
+    <row r="6" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="59">
+        <v>4</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="17"/>
+    </row>
+    <row r="7" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="58">
+        <v>5</v>
+      </c>
+      <c r="B7" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="11"/>
+    </row>
+    <row r="8" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="59">
+        <v>6</v>
+      </c>
+      <c r="B8" s="61" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="17"/>
+    </row>
+    <row r="9" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="58">
+        <v>7</v>
+      </c>
+      <c r="B9" s="60" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="11"/>
+    </row>
+    <row r="10" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="59">
+        <v>8</v>
+      </c>
+      <c r="B10" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="17"/>
+    </row>
+    <row r="11" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="58">
+        <v>9</v>
+      </c>
+      <c r="B11" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="11"/>
+    </row>
+    <row r="12" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="59">
+        <v>10</v>
+      </c>
+      <c r="B12" s="61" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="17"/>
+    </row>
+    <row r="13" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="58">
+        <v>11</v>
+      </c>
+      <c r="B13" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="11"/>
+    </row>
+    <row r="14" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="59">
+        <v>12</v>
+      </c>
+      <c r="B14" s="61" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="17"/>
+    </row>
+    <row r="15" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="58">
+        <v>13</v>
+      </c>
+      <c r="B15" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="11"/>
+    </row>
+    <row r="16" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="59">
+        <v>14</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="17"/>
+    </row>
+    <row r="17" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="58">
+        <v>15</v>
+      </c>
+      <c r="B17" s="60" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="11"/>
+    </row>
+    <row r="18" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="59">
+        <v>16</v>
+      </c>
+      <c r="B18" s="61" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="17"/>
+    </row>
+    <row r="19" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="58">
+        <v>17</v>
+      </c>
+      <c r="B19" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="11"/>
+    </row>
+    <row r="20" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="59">
+        <v>18</v>
+      </c>
+      <c r="B20" s="61" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="17"/>
+    </row>
+    <row r="21" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="58">
+        <v>19</v>
+      </c>
+      <c r="B21" s="60" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="11"/>
+    </row>
+    <row r="22" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="59">
+        <v>20</v>
+      </c>
+      <c r="B22" s="61" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="17"/>
+    </row>
+    <row r="23" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="58">
+        <v>21</v>
+      </c>
+      <c r="B23" s="60" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="11"/>
+    </row>
+    <row r="24" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="59">
+        <v>22</v>
+      </c>
+      <c r="B24" s="61" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="17"/>
+    </row>
+    <row r="25" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="58">
+        <v>23</v>
+      </c>
+      <c r="B25" s="60" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="11"/>
+    </row>
+    <row r="26" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="59">
+        <v>24</v>
+      </c>
+      <c r="B26" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="17"/>
+    </row>
+    <row r="27" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="58">
+        <v>25</v>
+      </c>
+      <c r="B27" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="11"/>
+    </row>
+    <row r="28" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="59">
+        <v>26</v>
+      </c>
+      <c r="B28" s="61" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="17"/>
+    </row>
+    <row r="29" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="58">
+        <v>27</v>
+      </c>
+      <c r="B29" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/NBFC-MF/LoanPortfolio.xlsx
+++ b/NBFC-MF/LoanPortfolio.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3600" windowWidth="15360" windowHeight="4410" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="3600" windowWidth="15360" windowHeight="4410"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="7" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
   <si>
     <t>Code</t>
   </si>
@@ -165,13 +165,7 @@
     <t>loan sanarei 180000, lanchenbi ranibala 10000</t>
   </si>
   <si>
-    <t>loan samila 10000, sandhyarani 20000</t>
-  </si>
-  <si>
     <t>Name</t>
-  </si>
-  <si>
-    <t>A Ranjit</t>
   </si>
   <si>
     <t>Angom Bijenti</t>
@@ -181,12 +175,6 @@
   </si>
   <si>
     <t>Bidyarani</t>
-  </si>
-  <si>
-    <t>Ibeyaima</t>
-  </si>
-  <si>
-    <t>Inaobi</t>
   </si>
   <si>
     <t>Kamala</t>
@@ -253,6 +241,87 @@
   </si>
   <si>
     <t>Collection Day</t>
+  </si>
+  <si>
+    <t>loan minarani 199 30000</t>
+  </si>
+  <si>
+    <t>loan samila-197 10000, sandhyarani 20000</t>
+  </si>
+  <si>
+    <t>samila loan 197 aadded 10000 to make 20000</t>
+  </si>
+  <si>
+    <t>expenses veg 520</t>
+  </si>
+  <si>
+    <t>A Ranita</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>mode</t>
+  </si>
+  <si>
+    <t>weekly</t>
+  </si>
+  <si>
+    <t>daily</t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>friday</t>
+  </si>
+  <si>
+    <t>purana rajbari</t>
+  </si>
+  <si>
+    <t>angom leikai</t>
+  </si>
+  <si>
+    <t>soibam leikai</t>
+  </si>
+  <si>
+    <t>ayangpalli</t>
+  </si>
+  <si>
+    <t>kongba</t>
+  </si>
+  <si>
+    <t>keithel ashangbi</t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>Monday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">checkon </t>
+  </si>
+  <si>
+    <t>karong</t>
+  </si>
+  <si>
+    <t>soibam leikai bidyabati group</t>
+  </si>
+  <si>
+    <t>khurai ahongai group</t>
+  </si>
+  <si>
+    <t>kakwa</t>
   </si>
 </sst>
 </file>
@@ -636,7 +705,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
@@ -835,9 +904,6 @@
     <xf numFmtId="164" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="1" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -881,6 +947,18 @@
     <xf numFmtId="164" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="13" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1074,32 +1152,32 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>23800</v>
+            <v>22400</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>23800</v>
+            <v>19001.031241588931</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>0</v>
+            <v>998.96875841106885</v>
           </cell>
         </row>
         <row r="16">
-          <cell r="K16" t="str">
-            <v/>
+          <cell r="K16">
+            <v>46205</v>
           </cell>
         </row>
         <row r="17">
-          <cell r="K17" t="str">
-            <v/>
+          <cell r="K17">
+            <v>46324</v>
           </cell>
         </row>
       </sheetData>
@@ -1143,22 +1221,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>7</v>
+            <v>8</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>14000</v>
+            <v>12600</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>12572.227063286609</v>
+            <v>11424.319854722999</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>7427.7729367133907</v>
+            <v>8575.6801452770014</v>
           </cell>
         </row>
         <row r="16">
@@ -1213,22 +1291,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>12</v>
+            <v>13</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>7000</v>
+            <v>5600</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>6597.85590128073</v>
+            <v>5330.1532184765038</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>13402.144098719269</v>
+            <v>14669.846781523496</v>
           </cell>
         </row>
         <row r="16">
@@ -1310,6 +1388,7 @@
     <sheetNames>
       <sheetName val="Loan1"/>
       <sheetName val="189"/>
+      <sheetName val="199"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -1397,22 +1476,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>2</v>
+            <v>12</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>10000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>8563.885350568542</v>
+            <v>3.1195668270811439E-10</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>1436.114649431458</v>
+            <v>9999.9999999996871</v>
           </cell>
         </row>
         <row r="16">
@@ -1423,6 +1502,63 @@
         <row r="17">
           <cell r="K17">
             <v>46312</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2">
+        <row r="2">
+          <cell r="K2" t="str">
+            <v>L30000W12-Minarani-N199</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="K3" t="str">
+            <v>Minarani</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="K7">
+            <v>30000</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="K9">
+            <v>3000</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="K10">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>36000</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="K14">
+            <v>36000</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="K15">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="K16" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="K17" t="str">
+            <v/>
           </cell>
         </row>
       </sheetData>
@@ -1467,22 +1603,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>35</v>
+            <v>42</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>8500</v>
+            <v>7800</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>7457.891976879012</v>
+            <v>6915.4215609237572</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>2542.108023120988</v>
+            <v>3084.5784390762428</v>
           </cell>
         </row>
         <row r="16">
@@ -1524,22 +1660,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>28</v>
+            <v>35</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>9200</v>
+            <v>8500</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>7988.68287277732</v>
+            <v>7457.891976879012</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>2011.31712722268</v>
+            <v>2542.108023120988</v>
           </cell>
         </row>
         <row r="16">
@@ -1651,32 +1787,32 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>11900</v>
+            <v>11200</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>11900</v>
+            <v>9500.5156207944656</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>0</v>
+            <v>499.48437920553442</v>
           </cell>
         </row>
         <row r="16">
-          <cell r="K16" t="str">
-            <v/>
+          <cell r="K16">
+            <v>46206</v>
           </cell>
         </row>
         <row r="17">
-          <cell r="K17" t="str">
-            <v/>
+          <cell r="K17">
+            <v>46325</v>
           </cell>
         </row>
       </sheetData>
@@ -1753,7 +1889,7 @@
       <sheetData sheetId="1">
         <row r="2">
           <cell r="K2" t="str">
-            <v>L10000W17-Lanchenbi_Samila-N197</v>
+            <v>L20000W17-Lanchenbi_Samila-N197</v>
           </cell>
         </row>
         <row r="3">
@@ -1763,12 +1899,12 @@
         </row>
         <row r="7">
           <cell r="K7">
-            <v>10000</v>
+            <v>20000</v>
           </cell>
         </row>
         <row r="9">
           <cell r="K9">
-            <v>700</v>
+            <v>1400</v>
           </cell>
         </row>
         <row r="10">
@@ -1778,32 +1914,32 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>11900</v>
+            <v>22400</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>11900</v>
+            <v>19001.031241588931</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>0</v>
+            <v>998.96875841106885</v>
           </cell>
         </row>
         <row r="16">
-          <cell r="K16" t="str">
-            <v/>
+          <cell r="K16">
+            <v>46209</v>
           </cell>
         </row>
         <row r="17">
-          <cell r="K17" t="str">
-            <v/>
+          <cell r="K17">
+            <v>46328</v>
           </cell>
         </row>
       </sheetData>
@@ -1847,22 +1983,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>4</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>27300</v>
+            <v>25200</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>23823.487509187638</v>
+            <v>22201.185647927028</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>6176.5124908123616</v>
+            <v>7798.8143520729718</v>
           </cell>
         </row>
         <row r="16">
@@ -1985,22 +2121,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>33</v>
+            <v>34</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>15660</v>
+            <v>15480</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>13699.308972116984</v>
+            <v>13561.971112790645</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>4300.6910278830164</v>
+            <v>4438.0288872093552</v>
           </cell>
         </row>
         <row r="16">
@@ -2192,22 +2328,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>24</v>
+            <v>29</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>9600</v>
+            <v>9100</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>8286.8450875198287</v>
+            <v>7913.561084752052</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>1713.1549124801713</v>
+            <v>2086.438915247948</v>
           </cell>
         </row>
         <row r="16">
@@ -2261,22 +2397,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>3</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>19600</v>
+            <v>18200</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>16942.599422027139</v>
+            <v>15882.325006125111</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>3057.4005779728614</v>
+            <v>4117.674993874889</v>
           </cell>
         </row>
         <row r="16">
@@ -2330,22 +2466,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>3</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>9800</v>
+            <v>9100</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>8471.2997110135693</v>
+            <v>7941.1625030625555</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>1528.7002889864307</v>
+            <v>2058.8374969374445</v>
           </cell>
         </row>
         <row r="16">
@@ -2399,22 +2535,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>1</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>33600</v>
+            <v>31500</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>28501.546862383388</v>
+            <v>26973.047398654715</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>1498.4531376166124</v>
+            <v>3026.9526013452851</v>
           </cell>
         </row>
         <row r="16">
@@ -2468,32 +2604,32 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>11900</v>
+            <v>11200</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>11900</v>
+            <v>9500.5156207944656</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>0</v>
+            <v>499.48437920553442</v>
           </cell>
         </row>
         <row r="16">
-          <cell r="K16" t="str">
-            <v/>
+          <cell r="K16">
+            <v>46206</v>
           </cell>
         </row>
         <row r="17">
-          <cell r="K17" t="str">
-            <v/>
+          <cell r="K17">
+            <v>46325</v>
           </cell>
         </row>
       </sheetData>
@@ -2537,22 +2673,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>1</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>22400</v>
+            <v>21000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>19001.031241588931</v>
+            <v>17982.031599103153</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>998.96875841106885</v>
+            <v>2017.968400896847</v>
           </cell>
         </row>
         <row r="16">
@@ -2606,22 +2742,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>1</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>22400</v>
+            <v>21000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>19001.031241588931</v>
+            <v>17982.031599103153</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>998.96875841106885</v>
+            <v>2017.968400896847</v>
           </cell>
         </row>
         <row r="16">
@@ -3040,22 +3176,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>40</v>
+            <v>41</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>40000</v>
+            <v>39500</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>35358.098881814622</v>
+            <v>34968.21043499728</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>14641.901118185378</v>
+            <v>15031.78956500272</v>
           </cell>
         </row>
         <row r="16">
@@ -3167,22 +3303,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>17</v>
+            <v>23</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>41200</v>
+            <v>38800</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>35199.153684934674</v>
+            <v>33443.232040642419</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>4800.8463150653261</v>
+            <v>6556.7679593575813</v>
           </cell>
         </row>
         <row r="16">
@@ -3363,32 +3499,32 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>214200</v>
+            <v>201600</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>214200</v>
+            <v>171009.28117430035</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>0</v>
+            <v>8990.7188256996451</v>
           </cell>
         </row>
         <row r="16">
-          <cell r="K16" t="str">
-            <v/>
+          <cell r="K16">
+            <v>46206</v>
           </cell>
         </row>
         <row r="17">
-          <cell r="K17" t="str">
-            <v/>
+          <cell r="K17">
+            <v>46325</v>
           </cell>
         </row>
       </sheetData>
@@ -3432,22 +3568,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>16</v>
+            <v>17</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>1400</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>1372.4796393105025</v>
+            <v>9.1336005425546318E-10</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>18627.520360689497</v>
+            <v>19999.999999999087</v>
           </cell>
         </row>
         <row r="16">
@@ -3501,22 +3637,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>15</v>
+            <v>16</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>2800</v>
+            <v>1400</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>2717.9798966815056</v>
+            <v>1372.4796393105025</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>17282.020103318493</v>
+            <v>18627.520360689497</v>
           </cell>
         </row>
         <row r="16">
@@ -3570,22 +3706,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>23</v>
+            <v>26</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>2550</v>
+            <v>2100</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>2350.4407503985121</v>
+            <v>1961.8170859013758</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>2649.5592496014879</v>
+            <v>3038.1829140986242</v>
           </cell>
         </row>
         <row r="16">
@@ -3889,46 +4025,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="H1" s="66" t="s">
+      <c r="B1" s="61"/>
+      <c r="H1" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="67"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="69">
+      <c r="I1" s="66"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="68">
         <f>SUM(J5:J1000)</f>
-        <v>612310</v>
-      </c>
-      <c r="L1" s="70"/>
-      <c r="N1" s="64" t="s">
+        <v>613280</v>
+      </c>
+      <c r="L1" s="69"/>
+      <c r="N1" s="63" t="s">
         <v>25</v>
       </c>
       <c r="O1" s="10"/>
-      <c r="P1" s="64">
+      <c r="P1" s="63">
         <f>SUM(P5:P1000)</f>
-        <v>45870</v>
+        <v>47870</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="63"/>
-      <c r="B2" s="63"/>
-      <c r="H2" s="66" t="s">
+      <c r="A2" s="62"/>
+      <c r="B2" s="62"/>
+      <c r="H2" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="67"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="69">
+      <c r="I2" s="66"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="68">
         <f>SUM(K5:K1000)</f>
-        <v>568559.65147229424</v>
-      </c>
-      <c r="L2" s="70"/>
+        <v>534277.02206937643</v>
+      </c>
+      <c r="L2" s="69"/>
       <c r="M2" s="2"/>
-      <c r="N2" s="65"/>
+      <c r="N2" s="64"/>
       <c r="O2" s="10"/>
-      <c r="P2" s="65"/>
+      <c r="P2" s="64"/>
     </row>
     <row r="3" spans="1:18" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3"/>
@@ -4134,7 +4270,7 @@
       </c>
       <c r="G7" s="22">
         <f t="shared" ref="G7:G17" si="0">IF(H7,H7-I7,"")</f>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H7" s="36">
         <f>[3]Loan1!$K$10</f>
@@ -4142,19 +4278,19 @@
       </c>
       <c r="I7" s="36">
         <f>[3]Loan1!$K$12</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J7" s="38">
         <f>[3]Loan1!$K$13</f>
-        <v>40000</v>
+        <v>39500</v>
       </c>
       <c r="K7" s="38">
         <f>[3]Loan1!$K$14</f>
-        <v>35358.098881814622</v>
+        <v>34968.21043499728</v>
       </c>
       <c r="L7" s="40">
         <f>[3]Loan1!$K$15</f>
-        <v>14641.901118185378</v>
+        <v>15031.78956500272</v>
       </c>
       <c r="M7" s="25">
         <f>[3]Loan1!$K$16</f>
@@ -4387,7 +4523,7 @@
       </c>
       <c r="G11" s="22">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="36">
         <f>[7]Loan1!$K$10</f>
@@ -4395,19 +4531,19 @@
       </c>
       <c r="I11" s="36">
         <f>[7]Loan1!$K$12</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J11" s="38">
         <f>[7]Loan1!$K$13</f>
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="K11" s="38">
         <f>[7]Loan1!$K$14</f>
-        <v>1372.4796393105025</v>
+        <v>9.1336005425546318E-10</v>
       </c>
       <c r="L11" s="40">
         <f>[7]Loan1!$K$15</f>
-        <v>18627.520360689497</v>
+        <v>19999.999999999087</v>
       </c>
       <c r="M11" s="25">
         <f>[7]Loan1!$K$16</f>
@@ -4447,7 +4583,7 @@
       </c>
       <c r="G12" s="22">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="39">
         <f>[8]Loan1!$K$10</f>
@@ -4455,19 +4591,19 @@
       </c>
       <c r="I12" s="39">
         <f>[8]Loan1!$K$12</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J12" s="42">
         <f>[8]Loan1!$K$13</f>
-        <v>2800</v>
+        <v>1400</v>
       </c>
       <c r="K12" s="42">
         <f>[8]Loan1!$K$14</f>
-        <v>2717.9798966815056</v>
+        <v>1372.4796393105025</v>
       </c>
       <c r="L12" s="43">
         <f>[8]Loan1!$K$15</f>
-        <v>17282.020103318493</v>
+        <v>18627.520360689497</v>
       </c>
       <c r="M12" s="23">
         <f>[8]Loan1!$K$16</f>
@@ -4508,7 +4644,7 @@
       </c>
       <c r="G13" s="22">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H13" s="36">
         <f>[9]Loan1!$K$10</f>
@@ -4516,19 +4652,19 @@
       </c>
       <c r="I13" s="36">
         <f>[9]Loan1!$K$12</f>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J13" s="38">
         <f>[9]Loan1!$K$13</f>
-        <v>2550</v>
+        <v>2100</v>
       </c>
       <c r="K13" s="38">
         <f>[9]Loan1!$K$14</f>
-        <v>2350.4407503985121</v>
+        <v>1961.8170859013758</v>
       </c>
       <c r="L13" s="40">
         <f>[9]Loan1!$K$15</f>
-        <v>2649.5592496014879</v>
+        <v>3038.1829140986242</v>
       </c>
       <c r="M13" s="25">
         <f>[9]Loan1!$K$16</f>
@@ -4634,7 +4770,7 @@
       </c>
       <c r="G15" s="22">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H15" s="36">
         <f>[11]Loan1!$K$10</f>
@@ -4642,19 +4778,19 @@
       </c>
       <c r="I15" s="36">
         <f>[11]Loan1!$K$12</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="38">
         <f>[11]Loan1!$K$13</f>
-        <v>14000</v>
+        <v>12600</v>
       </c>
       <c r="K15" s="38">
         <f>[11]Loan1!$K$14</f>
-        <v>12572.227063286609</v>
+        <v>11424.319854722999</v>
       </c>
       <c r="L15" s="40">
         <f>[11]Loan1!$K$15</f>
-        <v>7427.7729367133907</v>
+        <v>8575.6801452770014</v>
       </c>
       <c r="M15" s="25">
         <f>[11]Loan1!$K$16</f>
@@ -4695,7 +4831,7 @@
       </c>
       <c r="G16" s="22">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H16" s="39">
         <f>[12]Loan1!$K$10</f>
@@ -4703,19 +4839,19 @@
       </c>
       <c r="I16" s="39">
         <f>[12]Loan1!$K$12</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J16" s="42">
         <f>[12]Loan1!$K$13</f>
-        <v>7000</v>
+        <v>5600</v>
       </c>
       <c r="K16" s="42">
         <f>[12]Loan1!$K$14</f>
-        <v>6597.85590128073</v>
+        <v>5330.1532184765038</v>
       </c>
       <c r="L16" s="43">
         <f>[12]Loan1!$K$15</f>
-        <v>13402.144098719269</v>
+        <v>14669.846781523496</v>
       </c>
       <c r="M16" s="23">
         <f>[12]Loan1!$K$16</f>
@@ -4821,7 +4957,7 @@
       </c>
       <c r="G18" s="22">
         <f t="shared" ref="G18:G21" si="2">IF(H18,H18-I18,"")</f>
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H18" s="39">
         <f>[14]Loan1!$K$10</f>
@@ -4829,19 +4965,19 @@
       </c>
       <c r="I18" s="39">
         <f>[14]Loan1!$K$12</f>
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J18" s="42">
         <f>[14]Loan1!$K$13</f>
-        <v>8500</v>
+        <v>7800</v>
       </c>
       <c r="K18" s="42">
         <f>[14]Loan1!$K$14</f>
-        <v>7457.891976879012</v>
+        <v>6915.4215609237572</v>
       </c>
       <c r="L18" s="43">
         <f>[14]Loan1!$K$15</f>
-        <v>2542.108023120988</v>
+        <v>3084.5784390762428</v>
       </c>
       <c r="M18" s="23">
         <f>[14]Loan1!$K$16</f>
@@ -5007,7 +5143,7 @@
       </c>
       <c r="G21" s="22">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H21" s="36">
         <f>[17]Loan1!$K$10</f>
@@ -5015,19 +5151,19 @@
       </c>
       <c r="I21" s="36">
         <f>[17]Loan1!$K$12</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J21" s="38">
         <f>[17]Loan1!$K$13</f>
-        <v>27300</v>
+        <v>25200</v>
       </c>
       <c r="K21" s="38">
         <f>[17]Loan1!$K$14</f>
-        <v>23823.487509187638</v>
+        <v>22201.185647927028</v>
       </c>
       <c r="L21" s="40">
         <f>[17]Loan1!$K$15</f>
-        <v>6176.5124908123616</v>
+        <v>7798.8143520729718</v>
       </c>
       <c r="M21" s="25">
         <f>[17]Loan1!$K$16</f>
@@ -5128,7 +5264,7 @@
       </c>
       <c r="G23" s="22">
         <f t="shared" si="3"/>
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H23" s="36">
         <f>[19]Loan1!$K$10</f>
@@ -5136,19 +5272,19 @@
       </c>
       <c r="I23" s="36">
         <f>[19]Loan1!$K$12</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J23" s="38">
         <f>[19]Loan1!$K$13</f>
-        <v>15660</v>
+        <v>15480</v>
       </c>
       <c r="K23" s="38">
         <f>[19]Loan1!$K$14</f>
-        <v>13699.308972116984</v>
+        <v>13561.971112790645</v>
       </c>
       <c r="L23" s="40">
         <f>[19]Loan1!$K$15</f>
-        <v>4300.6910278830164</v>
+        <v>4438.0288872093552</v>
       </c>
       <c r="M23" s="25">
         <f>[19]Loan1!$K$16</f>
@@ -5262,7 +5398,7 @@
       </c>
       <c r="G25" s="22">
         <f t="shared" si="3"/>
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H25" s="36">
         <f>[14]Loan2!$K$10</f>
@@ -5270,19 +5406,19 @@
       </c>
       <c r="I25" s="36">
         <f>[14]Loan2!$K$12</f>
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="J25" s="38">
         <f>[14]Loan2!$K$13</f>
-        <v>9200</v>
+        <v>8500</v>
       </c>
       <c r="K25" s="38">
         <f>[14]Loan2!$K$14</f>
-        <v>7988.68287277732</v>
+        <v>7457.891976879012</v>
       </c>
       <c r="L25" s="40">
         <f>[14]Loan2!$K$15</f>
-        <v>2011.31712722268</v>
+        <v>2542.108023120988</v>
       </c>
       <c r="M25" s="25">
         <f>[14]Loan2!$K$16</f>
@@ -5329,7 +5465,7 @@
       </c>
       <c r="G26" s="22">
         <f t="shared" ref="G26:G89" si="4">IF(H26,H26-I26,"")</f>
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="H26" s="39">
         <f>[21]Loan1!$K$10</f>
@@ -5337,19 +5473,19 @@
       </c>
       <c r="I26" s="39">
         <f>[21]Loan1!$K$12</f>
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J26" s="42">
         <f>[21]Loan1!$K$13</f>
-        <v>9600</v>
+        <v>9100</v>
       </c>
       <c r="K26" s="42">
         <f>[21]Loan1!$K$14</f>
-        <v>8286.8450875198287</v>
+        <v>7913.561084752052</v>
       </c>
       <c r="L26" s="43">
         <f>[21]Loan1!$K$15</f>
-        <v>1713.1549124801713</v>
+        <v>2086.438915247948</v>
       </c>
       <c r="M26" s="23">
         <f>[21]Loan1!$K$16</f>
@@ -5396,7 +5532,7 @@
       </c>
       <c r="G27" s="22">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H27" s="36">
         <f>[22]Loan1!$K$10</f>
@@ -5404,19 +5540,19 @@
       </c>
       <c r="I27" s="36">
         <f>[22]Loan1!$K$12</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="38">
         <f>[22]Loan1!$K$13</f>
-        <v>19600</v>
+        <v>18200</v>
       </c>
       <c r="K27" s="38">
         <f>[22]Loan1!$K$14</f>
-        <v>16942.599422027139</v>
+        <v>15882.325006125111</v>
       </c>
       <c r="L27" s="40">
         <f>[22]Loan1!$K$15</f>
-        <v>3057.4005779728614</v>
+        <v>4117.674993874889</v>
       </c>
       <c r="M27" s="25">
         <f>[22]Loan1!$K$16</f>
@@ -5462,7 +5598,7 @@
       </c>
       <c r="G28" s="22">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H28" s="39">
         <f>[23]Loan1!$K$10</f>
@@ -5470,19 +5606,19 @@
       </c>
       <c r="I28" s="39">
         <f>[23]Loan1!$K$12</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J28" s="42">
         <f>[23]Loan1!$K$13</f>
-        <v>9800</v>
+        <v>9100</v>
       </c>
       <c r="K28" s="42">
         <f>[23]Loan1!$K$14</f>
-        <v>8471.2997110135693</v>
+        <v>7941.1625030625555</v>
       </c>
       <c r="L28" s="43">
         <f>[23]Loan1!$K$15</f>
-        <v>1528.7002889864307</v>
+        <v>2058.8374969374445</v>
       </c>
       <c r="M28" s="23">
         <f>[23]Loan1!$K$16</f>
@@ -5523,7 +5659,7 @@
       </c>
       <c r="G29" s="22">
         <f t="shared" si="4"/>
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="H29" s="36">
         <f>'[4]188'!$K$10</f>
@@ -5531,19 +5667,19 @@
       </c>
       <c r="I29" s="36">
         <f>'[4]188'!$K$12</f>
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J29" s="38">
         <f>'[4]188'!$K$13</f>
-        <v>41200</v>
+        <v>38800</v>
       </c>
       <c r="K29" s="38">
         <f>'[4]188'!$K$14</f>
-        <v>35199.153684934674</v>
+        <v>33443.232040642419</v>
       </c>
       <c r="L29" s="40">
         <f>'[4]188'!$K$15</f>
-        <v>4800.8463150653261</v>
+        <v>6556.7679593575813</v>
       </c>
       <c r="M29" s="25">
         <f>'[4]188'!$K$16</f>
@@ -5565,68 +5701,67 @@
       </c>
     </row>
     <row r="30" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="39">
+      <c r="A30" s="44">
         <f t="shared" si="1"/>
         <v>189</v>
       </c>
-      <c r="B30" s="39" t="str">
+      <c r="B30" s="44" t="str">
         <f>'[13]189'!$K$3</f>
         <v>Minarani</v>
       </c>
-      <c r="C30" s="39" t="s">
+      <c r="C30" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="D30" s="41" t="str">
+      <c r="D30" s="45" t="str">
         <f>'[13]189'!$K$2</f>
         <v>L10000W12-Minarani-N189</v>
       </c>
-      <c r="E30" s="42">
+      <c r="E30" s="46">
         <f>'[13]189'!$K$7</f>
         <v>10000</v>
       </c>
-      <c r="F30" s="39">
+      <c r="F30" s="44">
         <f>'[13]189'!$K$9</f>
         <v>1000</v>
       </c>
-      <c r="G30" s="22">
+      <c r="G30" s="47">
         <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="H30" s="39">
+        <v>0</v>
+      </c>
+      <c r="H30" s="44">
         <f>'[13]189'!$K$10</f>
         <v>12</v>
       </c>
-      <c r="I30" s="39">
+      <c r="I30" s="44">
         <f>'[13]189'!$K$12</f>
-        <v>2</v>
-      </c>
-      <c r="J30" s="42">
+        <v>12</v>
+      </c>
+      <c r="J30" s="46">
         <f>'[13]189'!$K$13</f>
-        <v>10000</v>
-      </c>
-      <c r="K30" s="42">
+        <v>0</v>
+      </c>
+      <c r="K30" s="46">
         <f>'[13]189'!$K$14</f>
-        <v>8563.885350568542</v>
-      </c>
-      <c r="L30" s="43">
+        <v>3.1195668270811439E-10</v>
+      </c>
+      <c r="L30" s="48">
         <f>'[13]189'!$K$15</f>
-        <v>1436.114649431458</v>
-      </c>
-      <c r="M30" s="23">
+        <v>9999.9999999996871</v>
+      </c>
+      <c r="M30" s="49">
         <f>'[13]189'!$K$16</f>
         <v>46193</v>
       </c>
-      <c r="N30" s="24">
+      <c r="N30" s="50">
         <f>'[13]189'!$K$17</f>
         <v>46312</v>
       </c>
-      <c r="P30" s="55">
-        <v>1000</v>
-      </c>
-      <c r="Q30" s="55" t="s">
+      <c r="O30" s="51"/>
+      <c r="P30" s="54"/>
+      <c r="Q30" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="R30" s="55">
+      <c r="R30" s="52">
         <v>40000</v>
       </c>
     </row>
@@ -5717,7 +5852,7 @@
       </c>
       <c r="G32" s="22">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H32" s="39">
         <f>'[24]191'!$K$10</f>
@@ -5725,19 +5860,19 @@
       </c>
       <c r="I32" s="39">
         <f>'[24]191'!$K$12</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J32" s="42">
         <f>'[24]191'!$K$13</f>
-        <v>33600</v>
+        <v>31500</v>
       </c>
       <c r="K32" s="42">
         <f>'[24]191'!$K$14</f>
-        <v>28501.546862383388</v>
+        <v>26973.047398654715</v>
       </c>
       <c r="L32" s="43">
         <f>'[24]191'!$K$15</f>
-        <v>1498.4531376166124</v>
+        <v>3026.9526013452851</v>
       </c>
       <c r="M32" s="23">
         <f>'[24]191'!$K$16</f>
@@ -5783,7 +5918,7 @@
       </c>
       <c r="G33" s="22">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H33" s="36">
         <f>'[25]192'!$K$10</f>
@@ -5791,27 +5926,27 @@
       </c>
       <c r="I33" s="36">
         <f>'[25]192'!$K$12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" s="38">
         <f>'[25]192'!$K$13</f>
-        <v>11900</v>
+        <v>11200</v>
       </c>
       <c r="K33" s="38">
         <f>'[25]192'!$K$14</f>
-        <v>11900</v>
+        <v>9500.5156207944656</v>
       </c>
       <c r="L33" s="40">
         <f>'[25]192'!$K$15</f>
-        <v>0</v>
-      </c>
-      <c r="M33" s="25" t="str">
+        <v>499.48437920553442</v>
+      </c>
+      <c r="M33" s="25">
         <f>'[25]192'!$K$16</f>
-        <v/>
-      </c>
-      <c r="N33" s="26" t="str">
+        <v>46206</v>
+      </c>
+      <c r="N33" s="26">
         <f>'[25]192'!$K$17</f>
-        <v/>
+        <v>46325</v>
       </c>
       <c r="P33" s="52">
         <v>700</v>
@@ -5844,7 +5979,7 @@
       </c>
       <c r="G34" s="22">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H34" s="39">
         <f>'[26]193'!$K$10</f>
@@ -5852,19 +5987,19 @@
       </c>
       <c r="I34" s="39">
         <f>'[26]193'!$K$12</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" s="42">
         <f>'[26]193'!$K$13</f>
-        <v>22400</v>
+        <v>21000</v>
       </c>
       <c r="K34" s="42">
         <f>'[26]193'!$K$14</f>
-        <v>19001.031241588931</v>
+        <v>17982.031599103153</v>
       </c>
       <c r="L34" s="43">
         <f>'[26]193'!$K$15</f>
-        <v>998.96875841106885</v>
+        <v>2017.968400896847</v>
       </c>
       <c r="M34" s="23">
         <f>'[26]193'!$K$16</f>
@@ -5905,7 +6040,7 @@
       </c>
       <c r="G35" s="22">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H35" s="36">
         <f>'[27]194'!$K$10</f>
@@ -5913,19 +6048,19 @@
       </c>
       <c r="I35" s="36">
         <f>'[27]194'!$K$12</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35" s="38">
         <f>'[27]194'!$K$13</f>
-        <v>22400</v>
+        <v>21000</v>
       </c>
       <c r="K35" s="38">
         <f>'[27]194'!$K$14</f>
-        <v>19001.031241588931</v>
+        <v>17982.031599103153</v>
       </c>
       <c r="L35" s="40">
         <f>'[27]194'!$K$15</f>
-        <v>998.96875841106885</v>
+        <v>2017.968400896847</v>
       </c>
       <c r="M35" s="25">
         <f>'[27]194'!$K$16</f>
@@ -5971,7 +6106,7 @@
       </c>
       <c r="G36" s="22">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H36" s="39">
         <f>'[6]195'!$K$10</f>
@@ -5979,27 +6114,27 @@
       </c>
       <c r="I36" s="39">
         <f>'[6]195'!$K$12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" s="42">
         <f>'[6]195'!$K$13</f>
-        <v>214200</v>
+        <v>201600</v>
       </c>
       <c r="K36" s="42">
         <f>'[6]195'!$K$14</f>
-        <v>214200</v>
+        <v>171009.28117430035</v>
       </c>
       <c r="L36" s="43">
         <f>'[6]195'!$K$15</f>
-        <v>0</v>
-      </c>
-      <c r="M36" s="23" t="str">
+        <v>8990.7188256996451</v>
+      </c>
+      <c r="M36" s="23">
         <f>'[6]195'!$K$16</f>
-        <v/>
-      </c>
-      <c r="N36" s="24" t="str">
+        <v>46206</v>
+      </c>
+      <c r="N36" s="24">
         <f>'[6]195'!$K$17</f>
-        <v/>
+        <v>46325</v>
       </c>
       <c r="P36" s="52">
         <v>12600</v>
@@ -6032,7 +6167,7 @@
       </c>
       <c r="G37" s="22">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H37" s="36">
         <f>'[15]196'!$K$10</f>
@@ -6040,27 +6175,27 @@
       </c>
       <c r="I37" s="36">
         <f>'[15]196'!$K$12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" s="38">
         <f>'[15]196'!$K$13</f>
-        <v>11900</v>
+        <v>11200</v>
       </c>
       <c r="K37" s="38">
         <f>'[15]196'!$K$14</f>
-        <v>11900</v>
+        <v>9500.5156207944656</v>
       </c>
       <c r="L37" s="40">
         <f>'[15]196'!$K$15</f>
-        <v>0</v>
-      </c>
-      <c r="M37" s="25" t="str">
+        <v>499.48437920553442</v>
+      </c>
+      <c r="M37" s="25">
         <f>'[15]196'!$K$16</f>
-        <v/>
-      </c>
-      <c r="N37" s="26" t="str">
+        <v>46206</v>
+      </c>
+      <c r="N37" s="26">
         <f>'[15]196'!$K$17</f>
-        <v/>
+        <v>46325</v>
       </c>
       <c r="P37" s="52">
         <v>700</v>
@@ -6080,19 +6215,19 @@
       </c>
       <c r="D38" s="41" t="str">
         <f>'[16]197'!$K$2</f>
-        <v>L10000W17-Lanchenbi_Samila-N197</v>
+        <v>L20000W17-Lanchenbi_Samila-N197</v>
       </c>
       <c r="E38" s="42">
         <f>'[16]197'!$K$7</f>
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="F38" s="39">
         <f>'[16]197'!$K$9</f>
-        <v>700</v>
+        <v>1400</v>
       </c>
       <c r="G38" s="22">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H38" s="39">
         <f>'[16]197'!$K$10</f>
@@ -6100,27 +6235,27 @@
       </c>
       <c r="I38" s="39">
         <f>'[16]197'!$K$12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="42">
         <f>'[16]197'!$K$13</f>
-        <v>11900</v>
+        <v>22400</v>
       </c>
       <c r="K38" s="42">
         <f>'[16]197'!$K$14</f>
-        <v>11900</v>
+        <v>19001.031241588931</v>
       </c>
       <c r="L38" s="43">
         <f>'[16]197'!$K$15</f>
-        <v>0</v>
-      </c>
-      <c r="M38" s="23" t="str">
+        <v>998.96875841106885</v>
+      </c>
+      <c r="M38" s="23">
         <f>'[16]197'!$K$16</f>
-        <v/>
-      </c>
-      <c r="N38" s="24" t="str">
+        <v>46209</v>
+      </c>
+      <c r="N38" s="24">
         <f>'[16]197'!$K$17</f>
-        <v/>
+        <v>46328</v>
       </c>
       <c r="P38" s="52">
         <v>700</v>
@@ -6152,7 +6287,7 @@
       </c>
       <c r="G39" s="22">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H39" s="36">
         <f>'[10]198'!$K$10</f>
@@ -6160,27 +6295,27 @@
       </c>
       <c r="I39" s="36">
         <f>'[10]198'!$K$12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="38">
         <f>'[10]198'!$K$13</f>
-        <v>23800</v>
+        <v>22400</v>
       </c>
       <c r="K39" s="38">
         <f>'[10]198'!$K$14</f>
-        <v>23800</v>
+        <v>19001.031241588931</v>
       </c>
       <c r="L39" s="40">
         <f>'[10]198'!$K$15</f>
-        <v>0</v>
-      </c>
-      <c r="M39" s="25" t="str">
+        <v>998.96875841106885</v>
+      </c>
+      <c r="M39" s="25">
         <f>'[10]198'!$K$16</f>
-        <v/>
-      </c>
-      <c r="N39" s="26" t="str">
+        <v>46205</v>
+      </c>
+      <c r="N39" s="26">
         <f>'[10]198'!$K$17</f>
-        <v/>
+        <v>46324</v>
       </c>
       <c r="P39" s="52">
         <v>1400</v>
@@ -6191,22 +6326,60 @@
         <f t="shared" si="1"/>
         <v>199</v>
       </c>
-      <c r="B40" s="39"/>
-      <c r="C40" s="39"/>
-      <c r="D40" s="41"/>
-      <c r="E40" s="42"/>
-      <c r="F40" s="39"/>
-      <c r="G40" s="22" t="str">
+      <c r="B40" s="39" t="str">
+        <f>'[13]199'!$K$3</f>
+        <v>Minarani</v>
+      </c>
+      <c r="C40" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" s="41" t="str">
+        <f>'[13]199'!$K$2</f>
+        <v>L30000W12-Minarani-N199</v>
+      </c>
+      <c r="E40" s="42">
+        <f>'[13]199'!$K$7</f>
+        <v>30000</v>
+      </c>
+      <c r="F40" s="39">
+        <f>'[13]199'!$K$9</f>
+        <v>3000</v>
+      </c>
+      <c r="G40" s="22">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H40" s="39"/>
-      <c r="I40" s="39"/>
-      <c r="J40" s="42"/>
-      <c r="K40" s="42"/>
-      <c r="L40" s="43"/>
-      <c r="M40" s="23"/>
-      <c r="N40" s="24"/>
+        <v>12</v>
+      </c>
+      <c r="H40" s="39">
+        <f>'[13]199'!$K$10</f>
+        <v>12</v>
+      </c>
+      <c r="I40" s="39">
+        <f>'[13]199'!$K$12</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="42">
+        <f>'[13]199'!$K$13</f>
+        <v>36000</v>
+      </c>
+      <c r="K40" s="42">
+        <f>'[13]199'!$K$14</f>
+        <v>36000</v>
+      </c>
+      <c r="L40" s="43">
+        <f>'[13]199'!$K$15</f>
+        <v>0</v>
+      </c>
+      <c r="M40" s="23" t="str">
+        <f>'[13]199'!$K$16</f>
+        <v/>
+      </c>
+      <c r="N40" s="24" t="str">
+        <f>'[13]199'!$K$17</f>
+        <v/>
+      </c>
+      <c r="P40" s="52">
+        <v>3000</v>
+      </c>
     </row>
     <row r="41" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="36">
@@ -15722,7 +15895,7 @@
       <c r="D474" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ZsPb2WNZ5bpmVZ80ZAO9lERZw/VTHn+Sl4laUG5TBEw8iy+zjfqj/TR+Sh9JNghhjv9tLejea/knocWpRu1NbQ==" saltValue="fiXaANeEpUju33S6bvWOyA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ohFLWnyldoB+6ffDCs5PAtq223/9axGP8V5E4EJyGswIVaNCqdFVUdeN1h2icyiEBJ/ZAeKU6xF7UjNwFz0Afw==" saltValue="gj+qv+B48Xwdb3055J6a1A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="7">
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="N1:N2"/>
@@ -15744,7 +15917,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.42578125" style="1" customWidth="1"/>
@@ -16617,96 +16790,1242 @@
         <v>568559.65147229424</v>
       </c>
       <c r="J17" s="35" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="P17" s="9"/>
     </row>
     <row r="18" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="11"/>
-      <c r="B18" s="14" t="str">
+      <c r="A18" s="11">
+        <v>46206</v>
+      </c>
+      <c r="B18" s="14" t="e">
         <f>IF(A18&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A18),
     "")</f>
-        <v/>
-      </c>
-      <c r="C18" s="15" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C18" s="15" t="e">
         <f>IF(A18&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A18),
     "")</f>
-        <v/>
-      </c>
-      <c r="D18" s="15" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D18" s="15" t="e">
         <f>IF(A18&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A18),
     "")</f>
-        <v/>
-      </c>
-      <c r="E18" s="16" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E18" s="16" t="e">
         <f>IF(A18&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A18),
     "")</f>
-        <v/>
-      </c>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F18" s="29">
+        <v>1085950</v>
+      </c>
+      <c r="G18" s="29">
+        <v>32970</v>
+      </c>
+      <c r="H18" s="29">
+        <v>577830</v>
+      </c>
+      <c r="I18" s="29">
+        <v>497848.14171366976</v>
+      </c>
       <c r="J18" s="34"/>
     </row>
     <row r="19" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="17"/>
-      <c r="B19" s="18" t="str">
+      <c r="A19" s="17">
+        <v>46206</v>
+      </c>
+      <c r="B19" s="18" t="e">
         <f>IF(A19&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A19),
     "")</f>
-        <v/>
-      </c>
-      <c r="C19" s="19" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C19" s="19" t="e">
         <f>IF(A19&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A19),
     "")</f>
-        <v/>
-      </c>
-      <c r="D19" s="19" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D19" s="19" t="e">
         <f>IF(A19&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A19),
     "")</f>
-        <v/>
-      </c>
-      <c r="E19" s="20" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E19" s="20" t="e">
         <f>IF(A19&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A19),
     "")</f>
-        <v/>
-      </c>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F19" s="32">
+        <v>1091950</v>
+      </c>
+      <c r="G19" s="32">
+        <v>2970</v>
+      </c>
+      <c r="H19" s="32">
+        <v>613830</v>
+      </c>
+      <c r="I19" s="32">
+        <v>533848.14171366976</v>
+      </c>
+      <c r="J19" s="35" t="s">
+        <v>65</v>
+      </c>
       <c r="P19" s="9"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="J20" s="57"/>
+    <row r="20" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="11">
+        <v>46209</v>
+      </c>
+      <c r="B20" s="14" t="e">
+        <f>IF(A20&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A20),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C20" s="15" t="e">
+        <f>IF(A20&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A20),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D20" s="15" t="e">
+        <f>IF(A20&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A20),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E20" s="16" t="e">
+        <f>IF(A20&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A20),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F20" s="29">
+        <v>1091950</v>
+      </c>
+      <c r="G20" s="29">
+        <v>12820</v>
+      </c>
+      <c r="H20" s="29">
+        <v>603980</v>
+      </c>
+      <c r="I20" s="29">
+        <v>526200.29871109314</v>
+      </c>
+      <c r="J20" s="34"/>
+    </row>
+    <row r="21" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="17">
+        <v>46209</v>
+      </c>
+      <c r="B21" s="18" t="e">
+        <f>IF(A21&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A21),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C21" s="19" t="e">
+        <f>IF(A21&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A21),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D21" s="19" t="e">
+        <f>IF(A21&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A21),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E21" s="20" t="e">
+        <f>IF(A21&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A21),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F21" s="32">
+        <v>1093850</v>
+      </c>
+      <c r="G21" s="32">
+        <v>2820</v>
+      </c>
+      <c r="H21" s="32">
+        <v>615880</v>
+      </c>
+      <c r="I21" s="32">
+        <v>536210.3141531304</v>
+      </c>
+      <c r="J21" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="P21" s="9"/>
+    </row>
+    <row r="22" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="11">
+        <v>46211</v>
+      </c>
+      <c r="B22" s="14" t="e">
+        <f>IF(A22&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A22),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C22" s="15" t="e">
+        <f>IF(A22&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A22),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D22" s="15" t="e">
+        <f>IF(A22&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A22),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E22" s="16" t="e">
+        <f>IF(A22&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A22),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F22" s="29">
+        <v>1093330</v>
+      </c>
+      <c r="G22" s="29">
+        <v>4900</v>
+      </c>
+      <c r="H22" s="29">
+        <v>613280</v>
+      </c>
+      <c r="I22" s="29">
+        <v>534277.02206937643</v>
+      </c>
+      <c r="J22" s="34" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="17"/>
+      <c r="B23" s="18" t="str">
+        <f>IF(A23&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A23),
+    "")</f>
+        <v/>
+      </c>
+      <c r="C23" s="19" t="str">
+        <f>IF(A23&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A23),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D23" s="19" t="str">
+        <f>IF(A23&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A23),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E23" s="20" t="str">
+        <f>IF(A23&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A23),
+    "")</f>
+        <v/>
+      </c>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="35"/>
+      <c r="P23" s="9"/>
+    </row>
+    <row r="24" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="11"/>
+      <c r="B24" s="14" t="str">
+        <f>IF(A24&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A24),
+    "")</f>
+        <v/>
+      </c>
+      <c r="C24" s="15" t="str">
+        <f>IF(A24&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A24),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D24" s="15" t="str">
+        <f>IF(A24&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A24),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E24" s="16" t="str">
+        <f>IF(A24&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A24),
+    "")</f>
+        <v/>
+      </c>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="34"/>
+    </row>
+    <row r="25" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="17"/>
+      <c r="B25" s="18" t="str">
+        <f>IF(A25&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A25),
+    "")</f>
+        <v/>
+      </c>
+      <c r="C25" s="19" t="str">
+        <f>IF(A25&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A25),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D25" s="19" t="str">
+        <f>IF(A25&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A25),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E25" s="20" t="str">
+        <f>IF(A25&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A25),
+    "")</f>
+        <v/>
+      </c>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="35"/>
+      <c r="P25" s="9"/>
+    </row>
+    <row r="26" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="11"/>
+      <c r="B26" s="14" t="str">
+        <f>IF(A26&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A26),
+    "")</f>
+        <v/>
+      </c>
+      <c r="C26" s="15" t="str">
+        <f>IF(A26&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A26),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D26" s="15" t="str">
+        <f>IF(A26&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A26),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E26" s="16" t="str">
+        <f>IF(A26&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A26),
+    "")</f>
+        <v/>
+      </c>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="34"/>
+    </row>
+    <row r="27" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="17"/>
+      <c r="B27" s="18" t="str">
+        <f>IF(A27&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A27),
+    "")</f>
+        <v/>
+      </c>
+      <c r="C27" s="19" t="str">
+        <f>IF(A27&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A27),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D27" s="19" t="str">
+        <f>IF(A27&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A27),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E27" s="20" t="str">
+        <f>IF(A27&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A27),
+    "")</f>
+        <v/>
+      </c>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="35"/>
+      <c r="P27" s="9"/>
+    </row>
+    <row r="28" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="11"/>
+      <c r="B28" s="14" t="str">
+        <f>IF(A28&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A28),
+    "")</f>
+        <v/>
+      </c>
+      <c r="C28" s="15" t="str">
+        <f>IF(A28&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A28),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D28" s="15" t="str">
+        <f>IF(A28&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A28),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E28" s="16" t="str">
+        <f>IF(A28&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A28),
+    "")</f>
+        <v/>
+      </c>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="34"/>
+    </row>
+    <row r="29" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="17"/>
+      <c r="B29" s="18" t="str">
+        <f>IF(A29&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A29),
+    "")</f>
+        <v/>
+      </c>
+      <c r="C29" s="19" t="str">
+        <f>IF(A29&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A29),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D29" s="19" t="str">
+        <f>IF(A29&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A29),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E29" s="20" t="str">
+        <f>IF(A29&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A29),
+    "")</f>
+        <v/>
+      </c>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="35"/>
+      <c r="P29" s="9"/>
+    </row>
+    <row r="30" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="11"/>
+      <c r="B30" s="14" t="str">
+        <f>IF(A30&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A30),
+    "")</f>
+        <v/>
+      </c>
+      <c r="C30" s="15" t="str">
+        <f>IF(A30&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A30),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D30" s="15" t="str">
+        <f>IF(A30&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A30),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E30" s="16" t="str">
+        <f>IF(A30&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A30),
+    "")</f>
+        <v/>
+      </c>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="34"/>
+    </row>
+    <row r="31" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="17"/>
+      <c r="B31" s="18" t="str">
+        <f>IF(A31&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A31),
+    "")</f>
+        <v/>
+      </c>
+      <c r="C31" s="19" t="str">
+        <f>IF(A31&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A31),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D31" s="19" t="str">
+        <f>IF(A31&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A31),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E31" s="20" t="str">
+        <f>IF(A31&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A31),
+    "")</f>
+        <v/>
+      </c>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
+      <c r="J31" s="35"/>
+      <c r="P31" s="9"/>
+    </row>
+    <row r="32" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="11"/>
+      <c r="B32" s="14" t="str">
+        <f>IF(A32&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A32),
+    "")</f>
+        <v/>
+      </c>
+      <c r="C32" s="15" t="str">
+        <f>IF(A32&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A32),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D32" s="15" t="str">
+        <f>IF(A32&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A32),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E32" s="16" t="str">
+        <f>IF(A32&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A32),
+    "")</f>
+        <v/>
+      </c>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="34"/>
+    </row>
+    <row r="33" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="17"/>
+      <c r="B33" s="18" t="str">
+        <f>IF(A33&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A33),
+    "")</f>
+        <v/>
+      </c>
+      <c r="C33" s="19" t="str">
+        <f>IF(A33&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A33),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D33" s="19" t="str">
+        <f>IF(A33&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A33),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E33" s="20" t="str">
+        <f>IF(A33&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A33),
+    "")</f>
+        <v/>
+      </c>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="35"/>
+      <c r="P33" s="9"/>
+    </row>
+    <row r="34" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="11"/>
+      <c r="B34" s="14" t="str">
+        <f>IF(A34&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A34),
+    "")</f>
+        <v/>
+      </c>
+      <c r="C34" s="15" t="str">
+        <f>IF(A34&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A34),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D34" s="15" t="str">
+        <f>IF(A34&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A34),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E34" s="16" t="str">
+        <f>IF(A34&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A34),
+    "")</f>
+        <v/>
+      </c>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="34"/>
+    </row>
+    <row r="35" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="17"/>
+      <c r="B35" s="18" t="str">
+        <f>IF(A35&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A35),
+    "")</f>
+        <v/>
+      </c>
+      <c r="C35" s="19" t="str">
+        <f>IF(A35&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A35),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D35" s="19" t="str">
+        <f>IF(A35&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A35),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E35" s="20" t="str">
+        <f>IF(A35&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A35),
+    "")</f>
+        <v/>
+      </c>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
+      <c r="J35" s="35"/>
+      <c r="P35" s="9"/>
+    </row>
+    <row r="36" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="11"/>
+      <c r="B36" s="14" t="str">
+        <f>IF(A36&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A36),
+    "")</f>
+        <v/>
+      </c>
+      <c r="C36" s="15" t="str">
+        <f>IF(A36&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A36),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D36" s="15" t="str">
+        <f>IF(A36&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A36),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E36" s="16" t="str">
+        <f>IF(A36&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A36),
+    "")</f>
+        <v/>
+      </c>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="34"/>
+    </row>
+    <row r="37" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="17"/>
+      <c r="B37" s="18" t="str">
+        <f>IF(A37&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A37),
+    "")</f>
+        <v/>
+      </c>
+      <c r="C37" s="19" t="str">
+        <f>IF(A37&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A37),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D37" s="19" t="str">
+        <f>IF(A37&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A37),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E37" s="20" t="str">
+        <f>IF(A37&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A37),
+    "")</f>
+        <v/>
+      </c>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="35"/>
+      <c r="P37" s="9"/>
+    </row>
+    <row r="38" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="11"/>
+      <c r="B38" s="14" t="str">
+        <f>IF(A38&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A38),
+    "")</f>
+        <v/>
+      </c>
+      <c r="C38" s="15" t="str">
+        <f>IF(A38&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A38),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D38" s="15" t="str">
+        <f>IF(A38&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A38),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E38" s="16" t="str">
+        <f>IF(A38&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A38),
+    "")</f>
+        <v/>
+      </c>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="34"/>
+    </row>
+    <row r="39" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="17"/>
+      <c r="B39" s="18" t="str">
+        <f>IF(A39&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A39),
+    "")</f>
+        <v/>
+      </c>
+      <c r="C39" s="19" t="str">
+        <f>IF(A39&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A39),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D39" s="19" t="str">
+        <f>IF(A39&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A39),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E39" s="20" t="str">
+        <f>IF(A39&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A39),
+    "")</f>
+        <v/>
+      </c>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="32"/>
+      <c r="J39" s="35"/>
+      <c r="P39" s="9"/>
+    </row>
+    <row r="40" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="11"/>
+      <c r="B40" s="14" t="str">
+        <f>IF(A40&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A40),
+    "")</f>
+        <v/>
+      </c>
+      <c r="C40" s="15" t="str">
+        <f>IF(A40&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A40),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D40" s="15" t="str">
+        <f>IF(A40&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A40),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E40" s="16" t="str">
+        <f>IF(A40&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A40),
+    "")</f>
+        <v/>
+      </c>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="34"/>
+    </row>
+    <row r="41" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="17"/>
+      <c r="B41" s="18" t="str">
+        <f>IF(A41&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A41),
+    "")</f>
+        <v/>
+      </c>
+      <c r="C41" s="19" t="str">
+        <f>IF(A41&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A41),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D41" s="19" t="str">
+        <f>IF(A41&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A41),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E41" s="20" t="str">
+        <f>IF(A41&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A41),
+    "")</f>
+        <v/>
+      </c>
+      <c r="F41" s="32"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="32"/>
+      <c r="J41" s="35"/>
+      <c r="P41" s="9"/>
+    </row>
+    <row r="42" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="11"/>
+      <c r="B42" s="14" t="str">
+        <f>IF(A42&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A42),
+    "")</f>
+        <v/>
+      </c>
+      <c r="C42" s="15" t="str">
+        <f>IF(A42&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A42),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D42" s="15" t="str">
+        <f>IF(A42&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A42),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E42" s="16" t="str">
+        <f>IF(A42&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A42),
+    "")</f>
+        <v/>
+      </c>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
+      <c r="I42" s="29"/>
+      <c r="J42" s="34"/>
+    </row>
+    <row r="43" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="17"/>
+      <c r="B43" s="18" t="str">
+        <f>IF(A43&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A43),
+    "")</f>
+        <v/>
+      </c>
+      <c r="C43" s="19" t="str">
+        <f>IF(A43&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A43),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D43" s="19" t="str">
+        <f>IF(A43&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A43),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E43" s="20" t="str">
+        <f>IF(A43&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A43),
+    "")</f>
+        <v/>
+      </c>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="32"/>
+      <c r="J43" s="35"/>
+      <c r="P43" s="9"/>
+    </row>
+    <row r="44" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="11"/>
+      <c r="B44" s="14" t="str">
+        <f>IF(A44&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A44),
+    "")</f>
+        <v/>
+      </c>
+      <c r="C44" s="15" t="str">
+        <f>IF(A44&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A44),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D44" s="15" t="str">
+        <f>IF(A44&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A44),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E44" s="16" t="str">
+        <f>IF(A44&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A44),
+    "")</f>
+        <v/>
+      </c>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
+      <c r="H44" s="29"/>
+      <c r="I44" s="29"/>
+      <c r="J44" s="34"/>
+    </row>
+    <row r="45" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="17"/>
+      <c r="B45" s="18" t="str">
+        <f>IF(A45&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A45),
+    "")</f>
+        <v/>
+      </c>
+      <c r="C45" s="19" t="str">
+        <f>IF(A45&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A45),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D45" s="19" t="str">
+        <f>IF(A45&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A45),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E45" s="20" t="str">
+        <f>IF(A45&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A45),
+    "")</f>
+        <v/>
+      </c>
+      <c r="F45" s="32"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="32"/>
+      <c r="J45" s="35"/>
+      <c r="P45" s="9"/>
+    </row>
+    <row r="46" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="11"/>
+      <c r="B46" s="14" t="str">
+        <f>IF(A46&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Capital Injection",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A46),
+    "")</f>
+        <v/>
+      </c>
+      <c r="C46" s="15" t="str">
+        <f>IF(A46&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Izra Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A46),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D46" s="15" t="str">
+        <f>IF(A46&lt;&gt;"",
+    SUMIFS([28]InvestingJournal!$F:$F,
+           [28]InvestingJournal!$C:$C,"Loan Advance",
+           [28]InvestingJournal!$A:$A,"&lt;="&amp;A46),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E46" s="16" t="str">
+        <f>IF(A46&lt;&gt;"",
+    SUMIFS([28]FinancingJournal!$E:$E,
+           [28]FinancingJournal!$C:$C,"Borrowing",
+           [28]FinancingJournal!$A:$A,"&lt;="&amp;A46),
+    "")</f>
+        <v/>
+      </c>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="34"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Pr4ttaMbAD7lulxdoRkM8I5OK0x5TznjcP16kg7dLKVW5k2UUpg7q30kix36rJ5+QbR2M9Otb5eoeHz0IxuVpg==" saltValue="b4mNrdrPjC50AT2lDgxUzw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="invEb16H57kvQ4lvUFSyHLh+ofvvU3PkztmZ/1O9RsAyMVJsmlIiM6cBn7jWU58EewmV0kETG9HFxqIlogk64g==" saltValue="tSc9o7ul5Xz1EN/CU9Zfgg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -16714,264 +18033,553 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:C29"/>
+  <dimension ref="A2:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.7109375" customWidth="1"/>
+    <col min="2" max="2" width="31" customWidth="1"/>
     <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" style="73" customWidth="1"/>
+    <col min="5" max="6" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="70" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="12"/>
+    </row>
+    <row r="3" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="57">
+        <v>1</v>
+      </c>
+      <c r="B3" s="59" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="71">
+        <v>2100</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="58">
+        <v>2</v>
+      </c>
+      <c r="B4" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="58">
-        <v>1</v>
-      </c>
-      <c r="B3" s="60" t="s">
+      <c r="C4" s="17"/>
+      <c r="D4" s="72">
+        <v>500</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="57">
+        <v>3</v>
+      </c>
+      <c r="B5" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="11"/>
-    </row>
-    <row r="4" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="59">
-        <v>2</v>
-      </c>
-      <c r="B4" s="61" t="s">
+      <c r="C5" s="11"/>
+      <c r="D5" s="71">
+        <f>100*2</f>
+        <v>200</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="58">
+        <v>4</v>
+      </c>
+      <c r="B6" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="17"/>
-    </row>
-    <row r="5" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="58">
-        <v>3</v>
-      </c>
-      <c r="B5" s="60" t="s">
+      <c r="C6" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="72">
+        <v>1400</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="57">
+        <v>5</v>
+      </c>
+      <c r="B7" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="11"/>
-    </row>
-    <row r="6" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="59">
-        <v>4</v>
-      </c>
-      <c r="B6" s="61" t="s">
+      <c r="C7" s="11"/>
+      <c r="D7" s="71">
+        <v>400</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="58">
+        <v>6</v>
+      </c>
+      <c r="B8" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="17"/>
-    </row>
-    <row r="7" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="58">
-        <v>5</v>
-      </c>
-      <c r="B7" s="60" t="s">
+      <c r="C8" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="72">
+        <v>1400</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="57">
+        <v>7</v>
+      </c>
+      <c r="B9" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="11"/>
-    </row>
-    <row r="8" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="59">
-        <v>6</v>
-      </c>
-      <c r="B8" s="61" t="s">
+      <c r="C9" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" s="71">
+        <v>2100</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="58">
+        <v>8</v>
+      </c>
+      <c r="B10" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="17"/>
-    </row>
-    <row r="9" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="58">
-        <v>7</v>
-      </c>
-      <c r="B9" s="60" t="s">
+      <c r="C10" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="72">
+        <v>700</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="57">
+        <v>9</v>
+      </c>
+      <c r="B11" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="11"/>
-    </row>
-    <row r="10" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="59">
-        <v>8</v>
-      </c>
-      <c r="B10" s="61" t="s">
+      <c r="C11" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="71">
+        <v>1400</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="58">
+        <v>10</v>
+      </c>
+      <c r="B12" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="17"/>
-    </row>
-    <row r="11" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="58">
-        <v>9</v>
-      </c>
-      <c r="B11" s="60" t="s">
+      <c r="C12" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="72">
+        <v>3000</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="57">
+        <v>11</v>
+      </c>
+      <c r="B13" s="59" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="11"/>
-    </row>
-    <row r="12" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="59">
-        <v>10</v>
-      </c>
-      <c r="B12" s="61" t="s">
+      <c r="C13" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="71">
+        <v>1400</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="58">
+        <v>12</v>
+      </c>
+      <c r="B14" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="17"/>
-    </row>
-    <row r="13" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="58">
-        <v>11</v>
-      </c>
-      <c r="B13" s="60" t="s">
+      <c r="C14" s="17"/>
+      <c r="D14" s="72">
+        <v>100</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="57">
+        <v>13</v>
+      </c>
+      <c r="B15" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="11"/>
-    </row>
-    <row r="14" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="59">
-        <v>12</v>
-      </c>
-      <c r="B14" s="61" t="s">
+      <c r="C15" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="71">
+        <v>700</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="58">
+        <v>14</v>
+      </c>
+      <c r="B16" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="17"/>
-    </row>
-    <row r="15" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="58">
-        <v>13</v>
-      </c>
-      <c r="B15" s="60" t="s">
+      <c r="C16" s="17"/>
+      <c r="D16" s="72">
+        <v>180</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="57">
+        <v>15</v>
+      </c>
+      <c r="B17" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="11"/>
-    </row>
-    <row r="16" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="59">
-        <v>14</v>
-      </c>
-      <c r="B16" s="61" t="s">
+      <c r="C17" s="11"/>
+      <c r="D17" s="71">
+        <v>180</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="58">
+        <v>16</v>
+      </c>
+      <c r="B18" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="17"/>
-    </row>
-    <row r="17" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="58">
-        <v>15</v>
-      </c>
-      <c r="B17" s="60" t="s">
+      <c r="C18" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="72">
+        <v>2100</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="57">
+        <v>17</v>
+      </c>
+      <c r="B19" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="11"/>
-    </row>
-    <row r="18" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="59">
-        <v>16</v>
-      </c>
-      <c r="B18" s="61" t="s">
+      <c r="C19" s="11"/>
+      <c r="D19" s="71">
+        <v>150</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="58">
+        <v>18</v>
+      </c>
+      <c r="B20" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="17"/>
-    </row>
-    <row r="19" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="58">
-        <v>17</v>
-      </c>
-      <c r="B19" s="60" t="s">
+      <c r="C20" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="72">
+        <v>1400</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="57">
+        <v>19</v>
+      </c>
+      <c r="B21" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="C19" s="11"/>
-    </row>
-    <row r="20" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="59">
-        <v>18</v>
-      </c>
-      <c r="B20" s="61" t="s">
+      <c r="C21" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="71">
+        <v>12600</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="58">
+        <v>20</v>
+      </c>
+      <c r="B22" s="60" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="17"/>
-    </row>
-    <row r="21" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="58">
-        <v>19</v>
-      </c>
-      <c r="B21" s="60" t="s">
+      <c r="C22" s="17"/>
+      <c r="D22" s="72">
+        <v>200</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="57">
+        <v>21</v>
+      </c>
+      <c r="B23" s="59" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="11"/>
-    </row>
-    <row r="22" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="59">
-        <v>20</v>
-      </c>
-      <c r="B22" s="61" t="s">
+      <c r="C23" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="71">
+        <v>1400</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="58">
+        <v>22</v>
+      </c>
+      <c r="B24" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="17"/>
-    </row>
-    <row r="23" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="58">
-        <v>21</v>
-      </c>
-      <c r="B23" s="60" t="s">
+      <c r="C24" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" s="72">
+        <v>700</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="57">
+        <v>23</v>
+      </c>
+      <c r="B25" s="59" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="11"/>
-    </row>
-    <row r="24" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="59">
-        <v>22</v>
-      </c>
-      <c r="B24" s="61" t="s">
+      <c r="C25" s="11"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+    </row>
+    <row r="26" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="58">
+        <v>24</v>
+      </c>
+      <c r="B26" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="17"/>
-    </row>
-    <row r="25" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="58">
-        <v>23</v>
-      </c>
-      <c r="B25" s="60" t="s">
+      <c r="C26" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="72">
+        <v>1400</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="57">
+        <v>25</v>
+      </c>
+      <c r="B27" s="59" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="11"/>
-    </row>
-    <row r="26" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="59">
-        <v>24</v>
-      </c>
-      <c r="B26" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="17"/>
-    </row>
-    <row r="27" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A27" s="58">
-        <v>25</v>
-      </c>
-      <c r="B27" s="60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" s="11"/>
-    </row>
-    <row r="28" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="59">
+      <c r="C27" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" s="71">
+        <v>1400</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="58">
         <v>26</v>
       </c>
-      <c r="B28" s="61" t="s">
-        <v>66</v>
+      <c r="B28" s="60" t="s">
+        <v>89</v>
       </c>
       <c r="C28" s="17"/>
-    </row>
-    <row r="29" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="58">
+      <c r="D28" s="72"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+    </row>
+    <row r="29" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="57">
         <v>27</v>
       </c>
-      <c r="B29" s="60" t="s">
-        <v>67</v>
+      <c r="B29" s="59" t="s">
+        <v>90</v>
       </c>
       <c r="C29" s="11"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+    </row>
+    <row r="30" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="58">
+        <v>28</v>
+      </c>
+      <c r="B30" s="60" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" s="17"/>
+      <c r="D30" s="72"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+    </row>
+    <row r="31" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A31" s="57">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="58">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/NBFC-MF/LoanPortfolio.xlsx
+++ b/NBFC-MF/LoanPortfolio.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3600" windowWidth="15360" windowHeight="4410"/>
+    <workbookView xWindow="0" yWindow="3600" windowWidth="15360" windowHeight="4410" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="7" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="94">
   <si>
     <t>Code</t>
   </si>
@@ -322,6 +322,12 @@
   </si>
   <si>
     <t>kakwa</t>
+  </si>
+  <si>
+    <t>loan no 200 ronel 30000</t>
+  </si>
+  <si>
+    <t>bomcha marup 16500</t>
   </si>
 </sst>
 </file>
@@ -920,6 +926,18 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="2" fontId="13" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -947,18 +965,6 @@
     <xf numFmtId="164" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="13" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1291,22 +1297,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>13</v>
+            <v>14</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>5600</v>
+            <v>4200</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>5330.1532184765038</v>
+            <v>4037.031116629747</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>14669.846781523496</v>
+            <v>15962.968883370253</v>
           </cell>
         </row>
         <row r="16">
@@ -1533,32 +1539,32 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>36000</v>
+            <v>33000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>36000</v>
+            <v>27876.856223074126</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>0</v>
+            <v>2123.1437769258737</v>
           </cell>
         </row>
         <row r="16">
-          <cell r="K16" t="str">
-            <v/>
+          <cell r="K16">
+            <v>46212</v>
           </cell>
         </row>
         <row r="17">
-          <cell r="K17" t="str">
-            <v/>
+          <cell r="K17">
+            <v>46331</v>
           </cell>
         </row>
       </sheetData>
@@ -1603,22 +1609,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>42</v>
+            <v>47</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>7800</v>
+            <v>7300</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>6915.4215609237572</v>
+            <v>6520.6498289572655</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>3084.5784390762428</v>
+            <v>3479.3501710427345</v>
           </cell>
         </row>
         <row r="16">
@@ -1660,22 +1666,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>35</v>
+            <v>40</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>8500</v>
+            <v>8000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>7457.891976879012</v>
+            <v>7071.6197763630944</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>2542.108023120988</v>
+            <v>2928.3802236369056</v>
           </cell>
         </row>
         <row r="16">
@@ -1787,22 +1793,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>1</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>11200</v>
+            <v>10500</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>9500.5156207944656</v>
+            <v>8991.0157995515765</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>499.48437920553442</v>
+            <v>1008.9842004484235</v>
           </cell>
         </row>
         <row r="16">
@@ -1914,22 +1920,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>1</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>22400</v>
+            <v>21000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>19001.031241588931</v>
+            <v>17982.031599103153</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>998.96875841106885</v>
+            <v>2017.968400896847</v>
           </cell>
         </row>
         <row r="16">
@@ -1983,22 +1989,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>5</v>
+            <v>6</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>25200</v>
+            <v>23100</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>22201.185647927028</v>
+            <v>20546.354100183748</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>7798.8143520729718</v>
+            <v>9453.6458998162525</v>
           </cell>
         </row>
         <row r="16">
@@ -2328,22 +2334,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>29</v>
+            <v>36</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>9100</v>
+            <v>8400</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>7913.561084752052</v>
+            <v>7381.1172094286358</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>2086.438915247948</v>
+            <v>2618.8827905713642</v>
           </cell>
         </row>
         <row r="16">
@@ -2397,22 +2403,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>4</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>18200</v>
+            <v>16800</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>15882.325006125111</v>
+            <v>14800.790431951375</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>4117.674993874889</v>
+            <v>5199.2095680486254</v>
           </cell>
         </row>
         <row r="16">
@@ -2535,22 +2541,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>2</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>31500</v>
+            <v>29400</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>26973.047398654715</v>
+            <v>25413.899133040686</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>3026.9526013452851</v>
+            <v>4586.1008669593139</v>
           </cell>
         </row>
         <row r="16">
@@ -2604,22 +2610,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>1</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>11200</v>
+            <v>10500</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>9500.5156207944656</v>
+            <v>8991.0157995515765</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>499.48437920553442</v>
+            <v>1008.9842004484235</v>
           </cell>
         </row>
         <row r="16">
@@ -2742,22 +2748,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>2</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>21000</v>
+            <v>19600</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>17982.031599103153</v>
+            <v>16942.599422027139</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>2017.968400896847</v>
+            <v>3057.4005779728614</v>
           </cell>
         </row>
         <row r="16">
@@ -2973,24 +2979,7 @@
             <v>160000</v>
           </cell>
         </row>
-        <row r="18">
-          <cell r="A18"/>
-          <cell r="C18"/>
-          <cell r="E18"/>
-        </row>
-        <row r="19">
-          <cell r="A19"/>
-          <cell r="C19"/>
-          <cell r="E19"/>
-        </row>
-        <row r="20">
-          <cell r="A20"/>
-          <cell r="C20"/>
-          <cell r="E20"/>
-        </row>
         <row r="21">
-          <cell r="A21"/>
-          <cell r="C21"/>
           <cell r="E21">
             <v>448580</v>
           </cell>
@@ -3085,57 +3074,16 @@
             <v>10000</v>
           </cell>
         </row>
-        <row r="9">
-          <cell r="A9"/>
-          <cell r="C9"/>
-          <cell r="F9"/>
-        </row>
-        <row r="10">
-          <cell r="A10"/>
-          <cell r="C10"/>
-          <cell r="F10"/>
-        </row>
-        <row r="11">
-          <cell r="A11"/>
-          <cell r="C11"/>
-          <cell r="F11"/>
-        </row>
-        <row r="12">
-          <cell r="A12"/>
-          <cell r="C12"/>
-          <cell r="F12"/>
-        </row>
-        <row r="13">
-          <cell r="A13"/>
-          <cell r="C13"/>
-          <cell r="F13"/>
-        </row>
-        <row r="14">
-          <cell r="A14"/>
-          <cell r="C14"/>
-          <cell r="F14"/>
-        </row>
-        <row r="15">
-          <cell r="A15"/>
-          <cell r="C15"/>
-          <cell r="F15"/>
-        </row>
-        <row r="16">
-          <cell r="A16"/>
-          <cell r="C16"/>
-          <cell r="F16"/>
-        </row>
         <row r="17">
           <cell r="A17" t="str">
             <v>TOTAL</v>
           </cell>
-          <cell r="C17"/>
           <cell r="F17">
             <v>735350</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3176,22 +3124,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>41</v>
+            <v>43</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>39500</v>
+            <v>38500</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>34968.21043499728</v>
+            <v>34184.787209487964</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>15031.78956500272</v>
+            <v>15815.212790512036</v>
           </cell>
         </row>
         <row r="16">
@@ -3303,22 +3251,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>23</v>
+            <v>29</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>38800</v>
+            <v>36400</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>33443.232040642419</v>
+            <v>31654.244339008208</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>6556.7679593575813</v>
+            <v>8345.755660991792</v>
           </cell>
         </row>
         <row r="16">
@@ -3372,22 +3320,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>70</v>
+            <v>95</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>10000</v>
+            <v>5000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>9247.0384022978469</v>
+            <v>4803.13010252807</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>10752.961597702153</v>
+            <v>15196.86989747193</v>
           </cell>
         </row>
         <row r="16">
@@ -3499,22 +3447,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>1</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>201600</v>
+            <v>189000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>171009.28117430035</v>
+            <v>161838.28439192835</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>8990.7188256996451</v>
+            <v>18161.715608071652</v>
           </cell>
         </row>
         <row r="16">
@@ -3538,6 +3486,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Loan1"/>
+      <sheetName val="200"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -3594,6 +3543,63 @@
         <row r="17">
           <cell r="K17">
             <v>46216</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="K2" t="str">
+            <v>L30000W17-Ronel-N200</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="K3" t="str">
+            <v>Ronel</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="K7">
+            <v>30000</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="K9">
+            <v>2100</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="K10">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>35700</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="K14">
+            <v>35700</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="K15">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="K16" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="K17" t="str">
+            <v/>
           </cell>
         </row>
       </sheetData>
@@ -3637,22 +3643,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>16</v>
+            <v>17</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>1400</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>1372.4796393105025</v>
+            <v>9.1336005425546318E-10</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>18627.520360689497</v>
+            <v>19999.999999999087</v>
           </cell>
         </row>
         <row r="16">
@@ -3706,22 +3712,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>26</v>
+            <v>27</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>2100</v>
+            <v>1950</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>1961.8170859013758</v>
+            <v>1829.8827748738483</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>3038.1829140986242</v>
+            <v>3170.1172251261514</v>
           </cell>
         </row>
         <row r="16">
@@ -4025,46 +4031,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="H1" s="65" t="s">
+      <c r="B1" s="65"/>
+      <c r="H1" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="66"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="68">
+      <c r="I1" s="70"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="72">
         <f>SUM(J5:J1000)</f>
-        <v>613280</v>
-      </c>
-      <c r="L1" s="69"/>
-      <c r="N1" s="63" t="s">
+        <v>610530</v>
+      </c>
+      <c r="L1" s="73"/>
+      <c r="N1" s="67" t="s">
         <v>25</v>
       </c>
       <c r="O1" s="10"/>
-      <c r="P1" s="63">
+      <c r="P1" s="67">
         <f>SUM(P5:P1000)</f>
-        <v>47870</v>
+        <v>47170</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="62"/>
-      <c r="B2" s="62"/>
-      <c r="H2" s="65" t="s">
+      <c r="A2" s="66"/>
+      <c r="B2" s="66"/>
+      <c r="H2" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="66"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="68">
+      <c r="I2" s="70"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="72">
         <f>SUM(K5:K1000)</f>
-        <v>534277.02206937643</v>
-      </c>
-      <c r="L2" s="69"/>
+        <v>534182.59257359686</v>
+      </c>
+      <c r="L2" s="73"/>
       <c r="M2" s="2"/>
-      <c r="N2" s="64"/>
+      <c r="N2" s="68"/>
       <c r="O2" s="10"/>
-      <c r="P2" s="64"/>
+      <c r="P2" s="68"/>
     </row>
     <row r="3" spans="1:18" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3"/>
@@ -4270,7 +4276,7 @@
       </c>
       <c r="G7" s="22">
         <f t="shared" ref="G7:G17" si="0">IF(H7,H7-I7,"")</f>
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H7" s="36">
         <f>[3]Loan1!$K$10</f>
@@ -4278,19 +4284,19 @@
       </c>
       <c r="I7" s="36">
         <f>[3]Loan1!$K$12</f>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J7" s="38">
         <f>[3]Loan1!$K$13</f>
-        <v>39500</v>
+        <v>38500</v>
       </c>
       <c r="K7" s="38">
         <f>[3]Loan1!$K$14</f>
-        <v>34968.21043499728</v>
+        <v>34184.787209487964</v>
       </c>
       <c r="L7" s="40">
         <f>[3]Loan1!$K$15</f>
-        <v>15031.78956500272</v>
+        <v>15815.212790512036</v>
       </c>
       <c r="M7" s="25">
         <f>[3]Loan1!$K$16</f>
@@ -4397,7 +4403,7 @@
       </c>
       <c r="G9" s="22">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H9" s="36">
         <f>[5]Loan1!$K$10</f>
@@ -4405,19 +4411,19 @@
       </c>
       <c r="I9" s="36">
         <f>[5]Loan1!$K$12</f>
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="J9" s="38">
         <f>[5]Loan1!$K$13</f>
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K9" s="38">
         <f>[5]Loan1!$K$14</f>
-        <v>9247.0384022978469</v>
+        <v>4803.13010252807</v>
       </c>
       <c r="L9" s="40">
         <f>[5]Loan1!$K$15</f>
-        <v>10752.961597702153</v>
+        <v>15196.86989747193</v>
       </c>
       <c r="M9" s="25">
         <f>[5]Loan1!$K$16</f>
@@ -4499,123 +4505,121 @@
       <c r="R10" s="52"/>
     </row>
     <row r="11" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="36">
+      <c r="A11" s="44">
         <v>167</v>
       </c>
-      <c r="B11" s="36" t="str">
+      <c r="B11" s="44" t="str">
         <f>[7]Loan1!$K$3</f>
         <v>Ronel</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="37" t="str">
-        <f>[7]Loan1!$K$2</f>
+      <c r="D11" s="45" t="str">
+        <f ca="1">[7]Loan1!$K$2</f>
         <v>L20000W17-Ronel-NLoan1</v>
       </c>
-      <c r="E11" s="38">
+      <c r="E11" s="46">
         <f>[7]Loan1!$K$7</f>
         <v>20000</v>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="44">
         <f>[7]Loan1!$K$9</f>
         <v>1400</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="47">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H11" s="36">
+      <c r="H11" s="44">
         <f>[7]Loan1!$K$10</f>
         <v>17</v>
       </c>
-      <c r="I11" s="36">
+      <c r="I11" s="44">
         <f>[7]Loan1!$K$12</f>
         <v>17</v>
       </c>
-      <c r="J11" s="38">
+      <c r="J11" s="46">
         <f>[7]Loan1!$K$13</f>
         <v>0</v>
       </c>
-      <c r="K11" s="38">
+      <c r="K11" s="46">
         <f>[7]Loan1!$K$14</f>
         <v>9.1336005425546318E-10</v>
       </c>
-      <c r="L11" s="40">
+      <c r="L11" s="48">
         <f>[7]Loan1!$K$15</f>
         <v>19999.999999999087</v>
       </c>
-      <c r="M11" s="25">
+      <c r="M11" s="49">
         <f>[7]Loan1!$K$16</f>
         <v>46097</v>
       </c>
-      <c r="N11" s="26">
+      <c r="N11" s="50">
         <f>[7]Loan1!$K$17</f>
         <v>46216</v>
       </c>
-      <c r="P11" s="52">
-        <v>1400</v>
-      </c>
+      <c r="O11" s="51"/>
+      <c r="P11" s="54"/>
       <c r="R11" s="52"/>
     </row>
     <row r="12" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="39">
+      <c r="A12" s="44">
         <v>169</v>
       </c>
-      <c r="B12" s="39" t="str">
+      <c r="B12" s="44" t="str">
         <f>[8]Loan1!$K$3</f>
         <v>Thongam_Bala</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="41" t="str">
+      <c r="D12" s="45" t="str">
         <f>[8]Loan1!$K$2</f>
         <v>L20000W17-Thongam_Bala-NLoan1</v>
       </c>
-      <c r="E12" s="42">
+      <c r="E12" s="46">
         <f>[8]Loan1!$K$7</f>
         <v>20000</v>
       </c>
-      <c r="F12" s="39">
+      <c r="F12" s="44">
         <f>[8]Loan1!$K$9</f>
         <v>1400</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="47">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H12" s="39">
+        <v>0</v>
+      </c>
+      <c r="H12" s="44">
         <f>[8]Loan1!$K$10</f>
         <v>17</v>
       </c>
-      <c r="I12" s="39">
+      <c r="I12" s="44">
         <f>[8]Loan1!$K$12</f>
-        <v>16</v>
-      </c>
-      <c r="J12" s="42">
+        <v>17</v>
+      </c>
+      <c r="J12" s="46">
         <f>[8]Loan1!$K$13</f>
-        <v>1400</v>
-      </c>
-      <c r="K12" s="42">
+        <v>0</v>
+      </c>
+      <c r="K12" s="46">
         <f>[8]Loan1!$K$14</f>
-        <v>1372.4796393105025</v>
-      </c>
-      <c r="L12" s="43">
+        <v>9.1336005425546318E-10</v>
+      </c>
+      <c r="L12" s="48">
         <f>[8]Loan1!$K$15</f>
-        <v>18627.520360689497</v>
-      </c>
-      <c r="M12" s="23">
+        <v>19999.999999999087</v>
+      </c>
+      <c r="M12" s="49">
         <f>[8]Loan1!$K$16</f>
         <v>46101</v>
       </c>
-      <c r="N12" s="24">
+      <c r="N12" s="50">
         <f>[8]Loan1!$K$17</f>
         <v>46220</v>
       </c>
-      <c r="P12" s="52">
-        <v>1400</v>
-      </c>
+      <c r="O12" s="51"/>
+      <c r="P12" s="54"/>
       <c r="R12" s="52"/>
     </row>
     <row r="13" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4644,7 +4648,7 @@
       </c>
       <c r="G13" s="22">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H13" s="36">
         <f>[9]Loan1!$K$10</f>
@@ -4652,19 +4656,19 @@
       </c>
       <c r="I13" s="36">
         <f>[9]Loan1!$K$12</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J13" s="38">
         <f>[9]Loan1!$K$13</f>
-        <v>2100</v>
+        <v>1950</v>
       </c>
       <c r="K13" s="38">
         <f>[9]Loan1!$K$14</f>
-        <v>1961.8170859013758</v>
+        <v>1829.8827748738483</v>
       </c>
       <c r="L13" s="40">
         <f>[9]Loan1!$K$15</f>
-        <v>3038.1829140986242</v>
+        <v>3170.1172251261514</v>
       </c>
       <c r="M13" s="25">
         <f>[9]Loan1!$K$16</f>
@@ -4831,7 +4835,7 @@
       </c>
       <c r="G16" s="22">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H16" s="39">
         <f>[12]Loan1!$K$10</f>
@@ -4839,19 +4843,19 @@
       </c>
       <c r="I16" s="39">
         <f>[12]Loan1!$K$12</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J16" s="42">
         <f>[12]Loan1!$K$13</f>
-        <v>5600</v>
+        <v>4200</v>
       </c>
       <c r="K16" s="42">
         <f>[12]Loan1!$K$14</f>
-        <v>5330.1532184765038</v>
+        <v>4037.031116629747</v>
       </c>
       <c r="L16" s="43">
         <f>[12]Loan1!$K$15</f>
-        <v>14669.846781523496</v>
+        <v>15962.968883370253</v>
       </c>
       <c r="M16" s="23">
         <f>[12]Loan1!$K$16</f>
@@ -4957,7 +4961,7 @@
       </c>
       <c r="G18" s="22">
         <f t="shared" ref="G18:G21" si="2">IF(H18,H18-I18,"")</f>
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H18" s="39">
         <f>[14]Loan1!$K$10</f>
@@ -4965,19 +4969,19 @@
       </c>
       <c r="I18" s="39">
         <f>[14]Loan1!$K$12</f>
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J18" s="42">
         <f>[14]Loan1!$K$13</f>
-        <v>7800</v>
+        <v>7300</v>
       </c>
       <c r="K18" s="42">
         <f>[14]Loan1!$K$14</f>
-        <v>6915.4215609237572</v>
+        <v>6520.6498289572655</v>
       </c>
       <c r="L18" s="43">
         <f>[14]Loan1!$K$15</f>
-        <v>3084.5784390762428</v>
+        <v>3479.3501710427345</v>
       </c>
       <c r="M18" s="23">
         <f>[14]Loan1!$K$16</f>
@@ -5143,7 +5147,7 @@
       </c>
       <c r="G21" s="22">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H21" s="36">
         <f>[17]Loan1!$K$10</f>
@@ -5151,19 +5155,19 @@
       </c>
       <c r="I21" s="36">
         <f>[17]Loan1!$K$12</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J21" s="38">
         <f>[17]Loan1!$K$13</f>
-        <v>25200</v>
+        <v>23100</v>
       </c>
       <c r="K21" s="38">
         <f>[17]Loan1!$K$14</f>
-        <v>22201.185647927028</v>
+        <v>20546.354100183748</v>
       </c>
       <c r="L21" s="40">
         <f>[17]Loan1!$K$15</f>
-        <v>7798.8143520729718</v>
+        <v>9453.6458998162525</v>
       </c>
       <c r="M21" s="25">
         <f>[17]Loan1!$K$16</f>
@@ -5398,7 +5402,7 @@
       </c>
       <c r="G25" s="22">
         <f t="shared" si="3"/>
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H25" s="36">
         <f>[14]Loan2!$K$10</f>
@@ -5406,19 +5410,19 @@
       </c>
       <c r="I25" s="36">
         <f>[14]Loan2!$K$12</f>
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J25" s="38">
         <f>[14]Loan2!$K$13</f>
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="K25" s="38">
         <f>[14]Loan2!$K$14</f>
-        <v>7457.891976879012</v>
+        <v>7071.6197763630944</v>
       </c>
       <c r="L25" s="40">
         <f>[14]Loan2!$K$15</f>
-        <v>2542.108023120988</v>
+        <v>2928.3802236369056</v>
       </c>
       <c r="M25" s="25">
         <f>[14]Loan2!$K$16</f>
@@ -5465,7 +5469,7 @@
       </c>
       <c r="G26" s="22">
         <f t="shared" ref="G26:G89" si="4">IF(H26,H26-I26,"")</f>
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H26" s="39">
         <f>[21]Loan1!$K$10</f>
@@ -5473,19 +5477,19 @@
       </c>
       <c r="I26" s="39">
         <f>[21]Loan1!$K$12</f>
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="J26" s="42">
         <f>[21]Loan1!$K$13</f>
-        <v>9100</v>
+        <v>8400</v>
       </c>
       <c r="K26" s="42">
         <f>[21]Loan1!$K$14</f>
-        <v>7913.561084752052</v>
+        <v>7381.1172094286358</v>
       </c>
       <c r="L26" s="43">
         <f>[21]Loan1!$K$15</f>
-        <v>2086.438915247948</v>
+        <v>2618.8827905713642</v>
       </c>
       <c r="M26" s="23">
         <f>[21]Loan1!$K$16</f>
@@ -5532,7 +5536,7 @@
       </c>
       <c r="G27" s="22">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H27" s="36">
         <f>[22]Loan1!$K$10</f>
@@ -5540,19 +5544,19 @@
       </c>
       <c r="I27" s="36">
         <f>[22]Loan1!$K$12</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="38">
         <f>[22]Loan1!$K$13</f>
-        <v>18200</v>
+        <v>16800</v>
       </c>
       <c r="K27" s="38">
         <f>[22]Loan1!$K$14</f>
-        <v>15882.325006125111</v>
+        <v>14800.790431951375</v>
       </c>
       <c r="L27" s="40">
         <f>[22]Loan1!$K$15</f>
-        <v>4117.674993874889</v>
+        <v>5199.2095680486254</v>
       </c>
       <c r="M27" s="25">
         <f>[22]Loan1!$K$16</f>
@@ -5659,7 +5663,7 @@
       </c>
       <c r="G29" s="22">
         <f t="shared" si="4"/>
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H29" s="36">
         <f>'[4]188'!$K$10</f>
@@ -5667,19 +5671,19 @@
       </c>
       <c r="I29" s="36">
         <f>'[4]188'!$K$12</f>
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J29" s="38">
         <f>'[4]188'!$K$13</f>
-        <v>38800</v>
+        <v>36400</v>
       </c>
       <c r="K29" s="38">
         <f>'[4]188'!$K$14</f>
-        <v>33443.232040642419</v>
+        <v>31654.244339008208</v>
       </c>
       <c r="L29" s="40">
         <f>'[4]188'!$K$15</f>
-        <v>6556.7679593575813</v>
+        <v>8345.755660991792</v>
       </c>
       <c r="M29" s="25">
         <f>'[4]188'!$K$16</f>
@@ -5852,7 +5856,7 @@
       </c>
       <c r="G32" s="22">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H32" s="39">
         <f>'[24]191'!$K$10</f>
@@ -5860,19 +5864,19 @@
       </c>
       <c r="I32" s="39">
         <f>'[24]191'!$K$12</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J32" s="42">
         <f>'[24]191'!$K$13</f>
-        <v>31500</v>
+        <v>29400</v>
       </c>
       <c r="K32" s="42">
         <f>'[24]191'!$K$14</f>
-        <v>26973.047398654715</v>
+        <v>25413.899133040686</v>
       </c>
       <c r="L32" s="43">
         <f>'[24]191'!$K$15</f>
-        <v>3026.9526013452851</v>
+        <v>4586.1008669593139</v>
       </c>
       <c r="M32" s="23">
         <f>'[24]191'!$K$16</f>
@@ -5918,7 +5922,7 @@
       </c>
       <c r="G33" s="22">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H33" s="36">
         <f>'[25]192'!$K$10</f>
@@ -5926,19 +5930,19 @@
       </c>
       <c r="I33" s="36">
         <f>'[25]192'!$K$12</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="38">
         <f>'[25]192'!$K$13</f>
-        <v>11200</v>
+        <v>10500</v>
       </c>
       <c r="K33" s="38">
         <f>'[25]192'!$K$14</f>
-        <v>9500.5156207944656</v>
+        <v>8991.0157995515765</v>
       </c>
       <c r="L33" s="40">
         <f>'[25]192'!$K$15</f>
-        <v>499.48437920553442</v>
+        <v>1008.9842004484235</v>
       </c>
       <c r="M33" s="25">
         <f>'[25]192'!$K$16</f>
@@ -6040,7 +6044,7 @@
       </c>
       <c r="G35" s="22">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H35" s="36">
         <f>'[27]194'!$K$10</f>
@@ -6048,19 +6052,19 @@
       </c>
       <c r="I35" s="36">
         <f>'[27]194'!$K$12</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J35" s="38">
         <f>'[27]194'!$K$13</f>
-        <v>21000</v>
+        <v>19600</v>
       </c>
       <c r="K35" s="38">
         <f>'[27]194'!$K$14</f>
-        <v>17982.031599103153</v>
+        <v>16942.599422027139</v>
       </c>
       <c r="L35" s="40">
         <f>'[27]194'!$K$15</f>
-        <v>2017.968400896847</v>
+        <v>3057.4005779728614</v>
       </c>
       <c r="M35" s="25">
         <f>'[27]194'!$K$16</f>
@@ -6106,7 +6110,7 @@
       </c>
       <c r="G36" s="22">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H36" s="39">
         <f>'[6]195'!$K$10</f>
@@ -6114,19 +6118,19 @@
       </c>
       <c r="I36" s="39">
         <f>'[6]195'!$K$12</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" s="42">
         <f>'[6]195'!$K$13</f>
-        <v>201600</v>
+        <v>189000</v>
       </c>
       <c r="K36" s="42">
         <f>'[6]195'!$K$14</f>
-        <v>171009.28117430035</v>
+        <v>161838.28439192835</v>
       </c>
       <c r="L36" s="43">
         <f>'[6]195'!$K$15</f>
-        <v>8990.7188256996451</v>
+        <v>18161.715608071652</v>
       </c>
       <c r="M36" s="23">
         <f>'[6]195'!$K$16</f>
@@ -6167,7 +6171,7 @@
       </c>
       <c r="G37" s="22">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H37" s="36">
         <f>'[15]196'!$K$10</f>
@@ -6175,19 +6179,19 @@
       </c>
       <c r="I37" s="36">
         <f>'[15]196'!$K$12</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J37" s="38">
         <f>'[15]196'!$K$13</f>
-        <v>11200</v>
+        <v>10500</v>
       </c>
       <c r="K37" s="38">
         <f>'[15]196'!$K$14</f>
-        <v>9500.5156207944656</v>
+        <v>8991.0157995515765</v>
       </c>
       <c r="L37" s="40">
         <f>'[15]196'!$K$15</f>
-        <v>499.48437920553442</v>
+        <v>1008.9842004484235</v>
       </c>
       <c r="M37" s="25">
         <f>'[15]196'!$K$16</f>
@@ -6227,7 +6231,7 @@
       </c>
       <c r="G38" s="22">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H38" s="39">
         <f>'[16]197'!$K$10</f>
@@ -6235,19 +6239,19 @@
       </c>
       <c r="I38" s="39">
         <f>'[16]197'!$K$12</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38" s="42">
         <f>'[16]197'!$K$13</f>
-        <v>22400</v>
+        <v>21000</v>
       </c>
       <c r="K38" s="42">
         <f>'[16]197'!$K$14</f>
-        <v>19001.031241588931</v>
+        <v>17982.031599103153</v>
       </c>
       <c r="L38" s="43">
         <f>'[16]197'!$K$15</f>
-        <v>998.96875841106885</v>
+        <v>2017.968400896847</v>
       </c>
       <c r="M38" s="23">
         <f>'[16]197'!$K$16</f>
@@ -6347,7 +6351,7 @@
       </c>
       <c r="G40" s="22">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H40" s="39">
         <f>'[13]199'!$K$10</f>
@@ -6355,27 +6359,27 @@
       </c>
       <c r="I40" s="39">
         <f>'[13]199'!$K$12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="42">
         <f>'[13]199'!$K$13</f>
-        <v>36000</v>
+        <v>33000</v>
       </c>
       <c r="K40" s="42">
         <f>'[13]199'!$K$14</f>
-        <v>36000</v>
+        <v>27876.856223074126</v>
       </c>
       <c r="L40" s="43">
         <f>'[13]199'!$K$15</f>
-        <v>0</v>
-      </c>
-      <c r="M40" s="23" t="str">
+        <v>2123.1437769258737</v>
+      </c>
+      <c r="M40" s="23">
         <f>'[13]199'!$K$16</f>
-        <v/>
-      </c>
-      <c r="N40" s="24" t="str">
+        <v>46212</v>
+      </c>
+      <c r="N40" s="24">
         <f>'[13]199'!$K$17</f>
-        <v/>
+        <v>46331</v>
       </c>
       <c r="P40" s="52">
         <v>3000</v>
@@ -6386,22 +6390,60 @@
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="B41" s="36"/>
-      <c r="C41" s="36"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="38"/>
-      <c r="F41" s="36"/>
-      <c r="G41" s="22" t="str">
+      <c r="B41" s="36" t="str">
+        <f>'[7]200'!$K$3</f>
+        <v>Ronel</v>
+      </c>
+      <c r="C41" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="37" t="str">
+        <f ca="1">'[7]200'!$K$2</f>
+        <v>L30000W17-Ronel-N200</v>
+      </c>
+      <c r="E41" s="38">
+        <f>'[7]200'!$K$7</f>
+        <v>30000</v>
+      </c>
+      <c r="F41" s="36">
+        <f>'[7]200'!$K$9</f>
+        <v>2100</v>
+      </c>
+      <c r="G41" s="22">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H41" s="36"/>
-      <c r="I41" s="36"/>
-      <c r="J41" s="38"/>
-      <c r="K41" s="38"/>
-      <c r="L41" s="40"/>
-      <c r="M41" s="25"/>
-      <c r="N41" s="26"/>
+        <v>17</v>
+      </c>
+      <c r="H41" s="36">
+        <f>'[7]200'!$K$10</f>
+        <v>17</v>
+      </c>
+      <c r="I41" s="36">
+        <f>'[7]200'!$K$12</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="38">
+        <f>'[7]200'!$K$13</f>
+        <v>35700</v>
+      </c>
+      <c r="K41" s="38">
+        <f>'[7]200'!$K$14</f>
+        <v>35700</v>
+      </c>
+      <c r="L41" s="40">
+        <f>'[7]200'!$K$15</f>
+        <v>0</v>
+      </c>
+      <c r="M41" s="25" t="str">
+        <f>'[7]200'!$K$16</f>
+        <v/>
+      </c>
+      <c r="N41" s="26" t="str">
+        <f>'[7]200'!$K$17</f>
+        <v/>
+      </c>
+      <c r="P41" s="52">
+        <v>2100</v>
+      </c>
     </row>
     <row r="42" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="39">
@@ -15895,7 +15937,7 @@
       <c r="D474" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ohFLWnyldoB+6ffDCs5PAtq223/9axGP8V5E4EJyGswIVaNCqdFVUdeN1h2icyiEBJ/ZAeKU6xF7UjNwFz0Afw==" saltValue="gj+qv+B48Xwdb3055J6a1A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="wIeoUT3QNI9pZrLWjd5fVR7oSO82NAqxGcaRD33dq/3AHU7EW6xYA2WVGB+eYYhtZGemxrOALDTeFKOUHTTRjA==" saltValue="cH41hDeuVuw+fTPcwvGSAw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="7">
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="N1:N2"/>
@@ -15967,37 +16009,37 @@
       <c r="A2" s="11">
         <v>46193</v>
       </c>
-      <c r="B2" s="14" t="e">
+      <c r="B2" s="14">
         <f>IF(A2&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A2),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C2" s="15" t="e">
+        <v>188380</v>
+      </c>
+      <c r="C2" s="15">
         <f>IF(A2&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A2),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D2" s="15" t="e">
+        <v>105350</v>
+      </c>
+      <c r="D2" s="15">
         <f>IF(A2&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A2),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E2" s="16" t="e">
+        <v>630000</v>
+      </c>
+      <c r="E2" s="16">
         <f>IF(A2&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A2),
     "")</f>
-        <v>#VALUE!</v>
+        <v>100200</v>
       </c>
       <c r="F2" s="29">
         <v>1035150</v>
@@ -16017,37 +16059,37 @@
       <c r="A3" s="17">
         <v>46185</v>
       </c>
-      <c r="B3" s="18" t="e">
+      <c r="B3" s="18">
         <f>IF(A3&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A3),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C3" s="19" t="e">
+        <v>188380</v>
+      </c>
+      <c r="C3" s="19">
         <f>IF(A3&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A3),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D3" s="19" t="e">
+        <v>105350</v>
+      </c>
+      <c r="D3" s="19">
         <f>IF(A3&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A3),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E3" s="20" t="e">
+        <v>630000</v>
+      </c>
+      <c r="E3" s="20">
         <f>IF(A3&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A3),
     "")</f>
-        <v>#VALUE!</v>
+        <v>100200</v>
       </c>
       <c r="F3" s="32">
         <v>1035150</v>
@@ -16068,37 +16110,37 @@
       <c r="A4" s="11">
         <v>46185</v>
       </c>
-      <c r="B4" s="14" t="e">
+      <c r="B4" s="14">
         <f>IF(A4&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A4),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C4" s="15" t="e">
+        <v>188380</v>
+      </c>
+      <c r="C4" s="15">
         <f>IF(A4&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A4),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D4" s="15" t="e">
+        <v>105350</v>
+      </c>
+      <c r="D4" s="15">
         <f>IF(A4&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A4),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E4" s="16" t="e">
+        <v>630000</v>
+      </c>
+      <c r="E4" s="16">
         <f>IF(A4&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A4),
     "")</f>
-        <v>#VALUE!</v>
+        <v>100200</v>
       </c>
       <c r="F4" s="29">
         <v>1045150</v>
@@ -16120,37 +16162,37 @@
       <c r="A5" s="17">
         <v>46192</v>
       </c>
-      <c r="B5" s="18" t="e">
+      <c r="B5" s="18">
         <f>IF(A5&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A5),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C5" s="19" t="e">
+        <v>188380</v>
+      </c>
+      <c r="C5" s="19">
         <f>IF(A5&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A5),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D5" s="19" t="e">
+        <v>105350</v>
+      </c>
+      <c r="D5" s="19">
         <f>IF(A5&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A5),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E5" s="20" t="e">
+        <v>630000</v>
+      </c>
+      <c r="E5" s="20">
         <f>IF(A5&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A5),
     "")</f>
-        <v>#VALUE!</v>
+        <v>100200</v>
       </c>
       <c r="F5" s="32">
         <v>1045150</v>
@@ -16171,37 +16213,37 @@
       <c r="A6" s="11">
         <v>46192</v>
       </c>
-      <c r="B6" s="14" t="e">
+      <c r="B6" s="14">
         <f>IF(A6&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A6),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C6" s="15" t="e">
+        <v>188380</v>
+      </c>
+      <c r="C6" s="15">
         <f>IF(A6&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A6),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D6" s="15" t="e">
+        <v>105350</v>
+      </c>
+      <c r="D6" s="15">
         <f>IF(A6&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A6),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E6" s="16" t="e">
+        <v>630000</v>
+      </c>
+      <c r="E6" s="16">
         <f>IF(A6&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A6),
     "")</f>
-        <v>#VALUE!</v>
+        <v>100200</v>
       </c>
       <c r="F6" s="29">
         <v>1047050</v>
@@ -16223,37 +16265,37 @@
       <c r="A7" s="17">
         <v>46193</v>
       </c>
-      <c r="B7" s="18" t="e">
+      <c r="B7" s="18">
         <f>IF(A7&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A7),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C7" s="19" t="e">
+        <v>188380</v>
+      </c>
+      <c r="C7" s="19">
         <f>IF(A7&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A7),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D7" s="19" t="e">
+        <v>105350</v>
+      </c>
+      <c r="D7" s="19">
         <f>IF(A7&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A7),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E7" s="20" t="e">
+        <v>630000</v>
+      </c>
+      <c r="E7" s="20">
         <f>IF(A7&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A7),
     "")</f>
-        <v>#VALUE!</v>
+        <v>100200</v>
       </c>
       <c r="F7" s="32">
         <v>1029550</v>
@@ -16276,37 +16318,37 @@
       <c r="A8" s="11">
         <v>46194</v>
       </c>
-      <c r="B8" s="14" t="e">
+      <c r="B8" s="14">
         <f>IF(A8&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A8),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C8" s="15" t="e">
+        <v>188380</v>
+      </c>
+      <c r="C8" s="15">
         <f>IF(A8&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A8),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D8" s="15" t="e">
+        <v>105350</v>
+      </c>
+      <c r="D8" s="15">
         <f>IF(A8&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A8),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E8" s="16" t="e">
+        <v>630000</v>
+      </c>
+      <c r="E8" s="16">
         <f>IF(A8&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A8),
     "")</f>
-        <v>#VALUE!</v>
+        <v>100200</v>
       </c>
       <c r="F8" s="29">
         <v>1029550</v>
@@ -16326,37 +16368,37 @@
       <c r="A9" s="17">
         <v>46194</v>
       </c>
-      <c r="B9" s="18" t="e">
+      <c r="B9" s="18">
         <f>IF(A9&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A9),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C9" s="19" t="e">
+        <v>188380</v>
+      </c>
+      <c r="C9" s="19">
         <f>IF(A9&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A9),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D9" s="19" t="e">
+        <v>105350</v>
+      </c>
+      <c r="D9" s="19">
         <f>IF(A9&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A9),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E9" s="20" t="e">
+        <v>630000</v>
+      </c>
+      <c r="E9" s="20">
         <f>IF(A9&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A9),
     "")</f>
-        <v>#VALUE!</v>
+        <v>100200</v>
       </c>
       <c r="F9" s="32">
         <v>1035250</v>
@@ -16380,37 +16422,37 @@
       <c r="A10" s="11">
         <v>46197</v>
       </c>
-      <c r="B10" s="14" t="e">
+      <c r="B10" s="14">
         <f>IF(A10&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A10),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C10" s="15" t="e">
+        <v>188380</v>
+      </c>
+      <c r="C10" s="15">
         <f>IF(A10&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A10),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D10" s="15" t="e">
+        <v>105350</v>
+      </c>
+      <c r="D10" s="15">
         <f>IF(A10&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A10),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E10" s="16" t="e">
+        <v>630000</v>
+      </c>
+      <c r="E10" s="16">
         <f>IF(A10&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A10),
     "")</f>
-        <v>#VALUE!</v>
+        <v>100200</v>
       </c>
       <c r="F10" s="29">
         <v>1035250</v>
@@ -16432,37 +16474,37 @@
       <c r="A11" s="17">
         <v>46197</v>
       </c>
-      <c r="B11" s="18" t="e">
+      <c r="B11" s="18">
         <f>IF(A11&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A11),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C11" s="19" t="e">
+        <v>188380</v>
+      </c>
+      <c r="C11" s="19">
         <f>IF(A11&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A11),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D11" s="19" t="e">
+        <v>105350</v>
+      </c>
+      <c r="D11" s="19">
         <f>IF(A11&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A11),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E11" s="20" t="e">
+        <v>630000</v>
+      </c>
+      <c r="E11" s="20">
         <f>IF(A11&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A11),
     "")</f>
-        <v>#VALUE!</v>
+        <v>100200</v>
       </c>
       <c r="F11" s="32">
         <v>1040950</v>
@@ -16485,37 +16527,37 @@
       <c r="A12" s="11">
         <v>46199</v>
       </c>
-      <c r="B12" s="14" t="e">
+      <c r="B12" s="14">
         <f>IF(A12&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A12),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C12" s="15" t="e">
+        <v>188380</v>
+      </c>
+      <c r="C12" s="15">
         <f>IF(A12&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A12),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D12" s="15" t="e">
+        <v>105350</v>
+      </c>
+      <c r="D12" s="15">
         <f>IF(A12&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A12),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E12" s="16" t="e">
+        <v>630000</v>
+      </c>
+      <c r="E12" s="16">
         <f>IF(A12&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A12),
     "")</f>
-        <v>#VALUE!</v>
+        <v>100200</v>
       </c>
       <c r="F12" s="29">
         <v>1040950</v>
@@ -16537,37 +16579,37 @@
       <c r="A13" s="17">
         <v>46199</v>
       </c>
-      <c r="B13" s="18" t="e">
+      <c r="B13" s="18">
         <f>IF(A13&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A13),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C13" s="19" t="e">
+        <v>188380</v>
+      </c>
+      <c r="C13" s="19">
         <f>IF(A13&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A13),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D13" s="19" t="e">
+        <v>105350</v>
+      </c>
+      <c r="D13" s="19">
         <f>IF(A13&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A13),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E13" s="20" t="e">
+        <v>630000</v>
+      </c>
+      <c r="E13" s="20">
         <f>IF(A13&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A13),
     "")</f>
-        <v>#VALUE!</v>
+        <v>100200</v>
       </c>
       <c r="F13" s="32">
         <v>1044750</v>
@@ -16590,37 +16632,37 @@
       <c r="A14" s="11">
         <v>46202</v>
       </c>
-      <c r="B14" s="14" t="e">
+      <c r="B14" s="14">
         <f>IF(A14&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A14),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C14" s="15" t="e">
+        <v>188380</v>
+      </c>
+      <c r="C14" s="15">
         <f>IF(A14&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A14),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D14" s="15" t="e">
+        <v>105350</v>
+      </c>
+      <c r="D14" s="15">
         <f>IF(A14&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A14),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E14" s="16" t="e">
+        <v>630000</v>
+      </c>
+      <c r="E14" s="16">
         <f>IF(A14&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A14),
     "")</f>
-        <v>#VALUE!</v>
+        <v>260200</v>
       </c>
       <c r="F14" s="29">
         <v>1044150</v>
@@ -16642,37 +16684,37 @@
       <c r="A15" s="17">
         <v>46202</v>
       </c>
-      <c r="B15" s="18" t="e">
+      <c r="B15" s="18">
         <f>IF(A15&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A15),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C15" s="19" t="e">
+        <v>188380</v>
+      </c>
+      <c r="C15" s="19">
         <f>IF(A15&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A15),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D15" s="19" t="e">
+        <v>105350</v>
+      </c>
+      <c r="D15" s="19">
         <f>IF(A15&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A15),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E15" s="20" t="e">
+        <v>630000</v>
+      </c>
+      <c r="E15" s="20">
         <f>IF(A15&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A15),
     "")</f>
-        <v>#VALUE!</v>
+        <v>260200</v>
       </c>
       <c r="F15" s="32">
         <v>1080250</v>
@@ -16695,37 +16737,37 @@
       <c r="A16" s="11">
         <v>46204</v>
       </c>
-      <c r="B16" s="14" t="e">
+      <c r="B16" s="14">
         <f>IF(A16&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A16),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C16" s="15" t="e">
+        <v>188380</v>
+      </c>
+      <c r="C16" s="15">
         <f>IF(A16&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A16),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D16" s="15" t="e">
+        <v>105350</v>
+      </c>
+      <c r="D16" s="15">
         <f>IF(A16&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A16),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E16" s="16" t="e">
+        <v>630000</v>
+      </c>
+      <c r="E16" s="16">
         <f>IF(A16&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A16),
     "")</f>
-        <v>#VALUE!</v>
+        <v>260200</v>
       </c>
       <c r="F16" s="29">
         <v>1080250</v>
@@ -16745,37 +16787,37 @@
       <c r="A17" s="17">
         <v>46204</v>
       </c>
-      <c r="B17" s="18" t="e">
+      <c r="B17" s="18">
         <f>IF(A17&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A17),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C17" s="19" t="e">
+        <v>188380</v>
+      </c>
+      <c r="C17" s="19">
         <f>IF(A17&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A17),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D17" s="19" t="e">
+        <v>105350</v>
+      </c>
+      <c r="D17" s="19">
         <f>IF(A17&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A17),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E17" s="20" t="e">
+        <v>630000</v>
+      </c>
+      <c r="E17" s="20">
         <f>IF(A17&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A17),
     "")</f>
-        <v>#VALUE!</v>
+        <v>260200</v>
       </c>
       <c r="F17" s="32">
         <v>1085950</v>
@@ -16798,37 +16840,37 @@
       <c r="A18" s="11">
         <v>46206</v>
       </c>
-      <c r="B18" s="14" t="e">
+      <c r="B18" s="14">
         <f>IF(A18&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A18),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C18" s="15" t="e">
+        <v>188380</v>
+      </c>
+      <c r="C18" s="15">
         <f>IF(A18&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A18),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D18" s="15" t="e">
+        <v>105350</v>
+      </c>
+      <c r="D18" s="15">
         <f>IF(A18&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A18),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E18" s="16" t="e">
+        <v>630000</v>
+      </c>
+      <c r="E18" s="16">
         <f>IF(A18&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A18),
     "")</f>
-        <v>#VALUE!</v>
+        <v>260200</v>
       </c>
       <c r="F18" s="29">
         <v>1085950</v>
@@ -16848,37 +16890,37 @@
       <c r="A19" s="17">
         <v>46206</v>
       </c>
-      <c r="B19" s="18" t="e">
+      <c r="B19" s="18">
         <f>IF(A19&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A19),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C19" s="19" t="e">
+        <v>188380</v>
+      </c>
+      <c r="C19" s="19">
         <f>IF(A19&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A19),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D19" s="19" t="e">
+        <v>105350</v>
+      </c>
+      <c r="D19" s="19">
         <f>IF(A19&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A19),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E19" s="20" t="e">
+        <v>630000</v>
+      </c>
+      <c r="E19" s="20">
         <f>IF(A19&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A19),
     "")</f>
-        <v>#VALUE!</v>
+        <v>260200</v>
       </c>
       <c r="F19" s="32">
         <v>1091950</v>
@@ -16901,37 +16943,37 @@
       <c r="A20" s="11">
         <v>46209</v>
       </c>
-      <c r="B20" s="14" t="e">
+      <c r="B20" s="14">
         <f>IF(A20&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A20),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C20" s="15" t="e">
+        <v>188380</v>
+      </c>
+      <c r="C20" s="15">
         <f>IF(A20&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A20),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D20" s="15" t="e">
+        <v>105350</v>
+      </c>
+      <c r="D20" s="15">
         <f>IF(A20&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A20),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E20" s="16" t="e">
+        <v>630000</v>
+      </c>
+      <c r="E20" s="16">
         <f>IF(A20&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A20),
     "")</f>
-        <v>#VALUE!</v>
+        <v>260200</v>
       </c>
       <c r="F20" s="29">
         <v>1091950</v>
@@ -16951,37 +16993,37 @@
       <c r="A21" s="17">
         <v>46209</v>
       </c>
-      <c r="B21" s="18" t="e">
+      <c r="B21" s="18">
         <f>IF(A21&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A21),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C21" s="19" t="e">
+        <v>188380</v>
+      </c>
+      <c r="C21" s="19">
         <f>IF(A21&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A21),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D21" s="19" t="e">
+        <v>105350</v>
+      </c>
+      <c r="D21" s="19">
         <f>IF(A21&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A21),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E21" s="20" t="e">
+        <v>630000</v>
+      </c>
+      <c r="E21" s="20">
         <f>IF(A21&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A21),
     "")</f>
-        <v>#VALUE!</v>
+        <v>260200</v>
       </c>
       <c r="F21" s="32">
         <v>1093850</v>
@@ -17004,37 +17046,37 @@
       <c r="A22" s="11">
         <v>46211</v>
       </c>
-      <c r="B22" s="14" t="e">
+      <c r="B22" s="14">
         <f>IF(A22&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A22),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C22" s="15" t="e">
+        <v>188380</v>
+      </c>
+      <c r="C22" s="15">
         <f>IF(A22&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A22),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D22" s="15" t="e">
+        <v>105350</v>
+      </c>
+      <c r="D22" s="15">
         <f>IF(A22&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A22),
     "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E22" s="16" t="e">
+        <v>630000</v>
+      </c>
+      <c r="E22" s="16">
         <f>IF(A22&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A22),
     "")</f>
-        <v>#VALUE!</v>
+        <v>260200</v>
       </c>
       <c r="F22" s="29">
         <v>1093330</v>
@@ -17053,166 +17095,210 @@
       </c>
     </row>
     <row r="23" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="17"/>
-      <c r="B23" s="18" t="str">
+      <c r="A23" s="17">
+        <v>46213</v>
+      </c>
+      <c r="B23" s="18">
         <f>IF(A23&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A23),
     "")</f>
-        <v/>
-      </c>
-      <c r="C23" s="19" t="str">
+        <v>188380</v>
+      </c>
+      <c r="C23" s="19">
         <f>IF(A23&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A23),
     "")</f>
-        <v/>
-      </c>
-      <c r="D23" s="19" t="str">
+        <v>105350</v>
+      </c>
+      <c r="D23" s="19">
         <f>IF(A23&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A23),
     "")</f>
-        <v/>
-      </c>
-      <c r="E23" s="20" t="str">
+        <v>630000</v>
+      </c>
+      <c r="E23" s="20">
         <f>IF(A23&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A23),
     "")</f>
-        <v/>
-      </c>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="32"/>
+        <v>260200</v>
+      </c>
+      <c r="F23" s="32">
+        <v>1093330</v>
+      </c>
+      <c r="G23" s="32">
+        <v>30950</v>
+      </c>
+      <c r="H23" s="32">
+        <v>587230</v>
+      </c>
+      <c r="I23" s="32">
+        <v>508482.14426753257</v>
+      </c>
       <c r="J23" s="35"/>
       <c r="P23" s="9"/>
     </row>
     <row r="24" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="11"/>
-      <c r="B24" s="14" t="str">
+      <c r="A24" s="11">
+        <v>46213</v>
+      </c>
+      <c r="B24" s="14">
         <f>IF(A24&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A24),
     "")</f>
-        <v/>
-      </c>
-      <c r="C24" s="15" t="str">
+        <v>188380</v>
+      </c>
+      <c r="C24" s="15">
         <f>IF(A24&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A24),
     "")</f>
-        <v/>
-      </c>
-      <c r="D24" s="15" t="str">
+        <v>105350</v>
+      </c>
+      <c r="D24" s="15">
         <f>IF(A24&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A24),
     "")</f>
-        <v/>
-      </c>
-      <c r="E24" s="16" t="str">
+        <v>630000</v>
+      </c>
+      <c r="E24" s="16">
         <f>IF(A24&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A24),
     "")</f>
-        <v/>
-      </c>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="34"/>
+        <v>260200</v>
+      </c>
+      <c r="F24" s="29">
+        <v>1099030</v>
+      </c>
+      <c r="G24" s="29">
+        <v>950</v>
+      </c>
+      <c r="H24" s="29">
+        <v>622930</v>
+      </c>
+      <c r="I24" s="29">
+        <v>544182.14426753251</v>
+      </c>
+      <c r="J24" s="34" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="25" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="17"/>
-      <c r="B25" s="18" t="str">
+      <c r="A25" s="17">
+        <v>46216</v>
+      </c>
+      <c r="B25" s="18">
         <f>IF(A25&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A25),
     "")</f>
-        <v/>
-      </c>
-      <c r="C25" s="19" t="str">
+        <v>188380</v>
+      </c>
+      <c r="C25" s="19">
         <f>IF(A25&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A25),
     "")</f>
-        <v/>
-      </c>
-      <c r="D25" s="19" t="str">
+        <v>105350</v>
+      </c>
+      <c r="D25" s="19">
         <f>IF(A25&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A25),
     "")</f>
-        <v/>
-      </c>
-      <c r="E25" s="20" t="str">
+        <v>630000</v>
+      </c>
+      <c r="E25" s="20">
         <f>IF(A25&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A25),
     "")</f>
-        <v/>
-      </c>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
+        <v>260200</v>
+      </c>
+      <c r="F25" s="32">
+        <v>1099030</v>
+      </c>
+      <c r="G25" s="32">
+        <v>13350</v>
+      </c>
+      <c r="H25" s="32">
+        <v>610530</v>
+      </c>
+      <c r="I25" s="32">
+        <v>534182.59257359686</v>
+      </c>
       <c r="J25" s="35"/>
       <c r="P25" s="9"/>
     </row>
     <row r="26" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="11"/>
-      <c r="B26" s="14" t="str">
+      <c r="A26" s="11">
+        <v>46216</v>
+      </c>
+      <c r="B26" s="14">
         <f>IF(A26&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Capital Injection",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A26),
     "")</f>
-        <v/>
-      </c>
-      <c r="C26" s="15" t="str">
+        <v>188380</v>
+      </c>
+      <c r="C26" s="15">
         <f>IF(A26&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Izra Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A26),
     "")</f>
-        <v/>
-      </c>
-      <c r="D26" s="15" t="str">
+        <v>105350</v>
+      </c>
+      <c r="D26" s="15">
         <f>IF(A26&lt;&gt;"",
     SUMIFS([28]InvestingJournal!$F:$F,
            [28]InvestingJournal!$C:$C,"Loan Advance",
            [28]InvestingJournal!$A:$A,"&lt;="&amp;A26),
     "")</f>
-        <v/>
-      </c>
-      <c r="E26" s="16" t="str">
+        <v>630000</v>
+      </c>
+      <c r="E26" s="16">
         <f>IF(A26&lt;&gt;"",
     SUMIFS([28]FinancingJournal!$E:$E,
            [28]FinancingJournal!$C:$C,"Borrowing",
            [28]FinancingJournal!$A:$A,"&lt;="&amp;A26),
     "")</f>
-        <v/>
-      </c>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="34"/>
+        <v>260200</v>
+      </c>
+      <c r="F26" s="29">
+        <v>1082530</v>
+      </c>
+      <c r="G26" s="29">
+        <v>-3150</v>
+      </c>
+      <c r="H26" s="29">
+        <v>610530</v>
+      </c>
+      <c r="I26" s="29">
+        <v>534182.59257359686</v>
+      </c>
+      <c r="J26" s="34" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="27" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="17"/>
@@ -18038,7 +18124,7 @@
   <cols>
     <col min="2" max="2" width="31" customWidth="1"/>
     <col min="3" max="3" width="18.140625" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" style="73" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" style="64" customWidth="1"/>
     <col min="5" max="6" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -18050,7 +18136,7 @@
       <c r="C2" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="70" t="s">
+      <c r="D2" s="61" t="s">
         <v>71</v>
       </c>
       <c r="E2" s="12" t="s">
@@ -18068,7 +18154,7 @@
       <c r="C3" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="71">
+      <c r="D3" s="62">
         <v>2100</v>
       </c>
       <c r="E3" s="11" t="s">
@@ -18086,7 +18172,7 @@
         <v>40</v>
       </c>
       <c r="C4" s="17"/>
-      <c r="D4" s="72">
+      <c r="D4" s="63">
         <v>500</v>
       </c>
       <c r="E4" s="17" t="s">
@@ -18104,7 +18190,7 @@
         <v>41</v>
       </c>
       <c r="C5" s="11"/>
-      <c r="D5" s="71">
+      <c r="D5" s="62">
         <f>100*2</f>
         <v>200</v>
       </c>
@@ -18125,7 +18211,7 @@
       <c r="C6" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="72">
+      <c r="D6" s="63">
         <v>1400</v>
       </c>
       <c r="E6" s="17" t="s">
@@ -18143,7 +18229,7 @@
         <v>43</v>
       </c>
       <c r="C7" s="11"/>
-      <c r="D7" s="71">
+      <c r="D7" s="62">
         <v>400</v>
       </c>
       <c r="E7" s="11" t="s">
@@ -18163,7 +18249,7 @@
       <c r="C8" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="D8" s="72">
+      <c r="D8" s="63">
         <v>1400</v>
       </c>
       <c r="E8" s="17" t="s">
@@ -18183,7 +18269,7 @@
       <c r="C9" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="71">
+      <c r="D9" s="62">
         <v>2100</v>
       </c>
       <c r="E9" s="11" t="s">
@@ -18203,7 +18289,7 @@
       <c r="C10" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="72">
+      <c r="D10" s="63">
         <v>700</v>
       </c>
       <c r="E10" s="17" t="s">
@@ -18223,7 +18309,7 @@
       <c r="C11" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="71">
+      <c r="D11" s="62">
         <v>1400</v>
       </c>
       <c r="E11" s="11" t="s">
@@ -18243,7 +18329,7 @@
       <c r="C12" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="D12" s="72">
+      <c r="D12" s="63">
         <v>3000</v>
       </c>
       <c r="E12" s="17" t="s">
@@ -18263,7 +18349,7 @@
       <c r="C13" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="71">
+      <c r="D13" s="62">
         <v>1400</v>
       </c>
       <c r="E13" s="11" t="s">
@@ -18281,7 +18367,7 @@
         <v>50</v>
       </c>
       <c r="C14" s="17"/>
-      <c r="D14" s="72">
+      <c r="D14" s="63">
         <v>100</v>
       </c>
       <c r="E14" s="17" t="s">
@@ -18301,7 +18387,7 @@
       <c r="C15" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="D15" s="71">
+      <c r="D15" s="62">
         <v>700</v>
       </c>
       <c r="E15" s="11" t="s">
@@ -18319,7 +18405,7 @@
         <v>52</v>
       </c>
       <c r="C16" s="17"/>
-      <c r="D16" s="72">
+      <c r="D16" s="63">
         <v>180</v>
       </c>
       <c r="E16" s="17" t="s">
@@ -18337,7 +18423,7 @@
         <v>53</v>
       </c>
       <c r="C17" s="11"/>
-      <c r="D17" s="71">
+      <c r="D17" s="62">
         <v>180</v>
       </c>
       <c r="E17" s="11" t="s">
@@ -18357,7 +18443,7 @@
       <c r="C18" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="72">
+      <c r="D18" s="63">
         <v>2100</v>
       </c>
       <c r="E18" s="17" t="s">
@@ -18375,7 +18461,7 @@
         <v>55</v>
       </c>
       <c r="C19" s="11"/>
-      <c r="D19" s="71">
+      <c r="D19" s="62">
         <v>150</v>
       </c>
       <c r="E19" s="11" t="s">
@@ -18395,7 +18481,7 @@
       <c r="C20" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="72">
+      <c r="D20" s="63">
         <v>1400</v>
       </c>
       <c r="E20" s="17" t="s">
@@ -18415,7 +18501,7 @@
       <c r="C21" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="D21" s="71">
+      <c r="D21" s="62">
         <v>12600</v>
       </c>
       <c r="E21" s="11" t="s">
@@ -18433,7 +18519,7 @@
         <v>58</v>
       </c>
       <c r="C22" s="17"/>
-      <c r="D22" s="72">
+      <c r="D22" s="63">
         <v>200</v>
       </c>
       <c r="E22" s="17" t="s">
@@ -18453,7 +18539,7 @@
       <c r="C23" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="D23" s="71">
+      <c r="D23" s="62">
         <v>1400</v>
       </c>
       <c r="E23" s="11" t="s">
@@ -18473,7 +18559,7 @@
       <c r="C24" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D24" s="72">
+      <c r="D24" s="63">
         <v>700</v>
       </c>
       <c r="E24" s="17" t="s">
@@ -18491,7 +18577,7 @@
         <v>61</v>
       </c>
       <c r="C25" s="11"/>
-      <c r="D25" s="71"/>
+      <c r="D25" s="62"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
     </row>
@@ -18505,7 +18591,7 @@
       <c r="C26" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D26" s="72">
+      <c r="D26" s="63">
         <v>1400</v>
       </c>
       <c r="E26" s="17" t="s">
@@ -18525,7 +18611,7 @@
       <c r="C27" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="D27" s="71">
+      <c r="D27" s="62">
         <v>1400</v>
       </c>
       <c r="E27" s="11" t="s">
@@ -18543,7 +18629,7 @@
         <v>89</v>
       </c>
       <c r="C28" s="17"/>
-      <c r="D28" s="72"/>
+      <c r="D28" s="63"/>
       <c r="E28" s="17"/>
       <c r="F28" s="17"/>
     </row>
@@ -18555,7 +18641,7 @@
         <v>90</v>
       </c>
       <c r="C29" s="11"/>
-      <c r="D29" s="71"/>
+      <c r="D29" s="62"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
     </row>
@@ -18567,7 +18653,7 @@
         <v>91</v>
       </c>
       <c r="C30" s="17"/>
-      <c r="D30" s="72"/>
+      <c r="D30" s="63"/>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
     </row>

--- a/NBFC-MF/LoanPortfolio.xlsx
+++ b/NBFC-MF/LoanPortfolio.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3600" windowWidth="15360" windowHeight="4410"/>
+    <workbookView xWindow="0" yWindow="3600" windowWidth="15360" windowHeight="4410" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="7" r:id="rId1"/>
@@ -46,13 +46,15 @@
     <externalReference r:id="rId35"/>
     <externalReference r:id="rId36"/>
     <externalReference r:id="rId37"/>
+    <externalReference r:id="rId38"/>
+    <externalReference r:id="rId39"/>
   </externalReferences>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="122">
   <si>
     <t>Code</t>
   </si>
@@ -394,6 +396,30 @@
   </si>
   <si>
     <t>candle expense 300</t>
+  </si>
+  <si>
+    <t>grocery expense 2800</t>
+  </si>
+  <si>
+    <t>pratima 209 issued loan 5000</t>
+  </si>
+  <si>
+    <t>interest expense 3500</t>
+  </si>
+  <si>
+    <t>aboong deposit 10000 ; gold loan 20000 to ibeyaima</t>
+  </si>
+  <si>
+    <t>sudhana210  loan 20000</t>
+  </si>
+  <si>
+    <t>bomcha and angom marup 18500</t>
+  </si>
+  <si>
+    <t>fish and veg 500+650</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Anjala 211loan 20000; ranjana212 loan 20000</t>
   </si>
 </sst>
 </file>
@@ -1251,22 +1277,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>6</v>
+            <v>8</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>15400</v>
+            <v>12600</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>13697.569400122526</v>
+            <v>11424.319854722999</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>6302.4305998774744</v>
+            <v>8575.6801452770014</v>
           </cell>
         </row>
         <row r="16">
@@ -1290,6 +1316,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Loan1"/>
+      <sheetName val="210"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -1320,22 +1347,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>14</v>
+            <v>17</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>4200</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>4037.031116629747</v>
+            <v>9.1336005425546318E-10</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>15962.968883370253</v>
+            <v>19999.999999999087</v>
           </cell>
         </row>
         <row r="16">
@@ -1346,6 +1373,63 @@
         <row r="17">
           <cell r="K17">
             <v>46269</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="K2" t="str">
+            <v>L20000W17-Sudhana-N210</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="K3" t="str">
+            <v>Sudhana</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="K7">
+            <v>20000</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="K9">
+            <v>1400</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="K10">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>22400</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="K14">
+            <v>19001.031241588931</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="K15">
+            <v>998.96875841106885</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="K16">
+            <v>46255</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="K17">
+            <v>46374</v>
           </cell>
         </row>
       </sheetData>
@@ -1447,22 +1531,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>3</v>
+            <v>9</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>9800</v>
+            <v>5600</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>8471.2997110135693</v>
+            <v>5126.6976567527154</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>1528.7002889864307</v>
+            <v>4873.3023432472846</v>
           </cell>
         </row>
         <row r="16">
@@ -1632,22 +1716,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>5</v>
+            <v>7</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>21000</v>
+            <v>15000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>18745.312366590952</v>
+            <v>13769.437260492452</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>11254.687633409048</v>
+            <v>16230.562739507548</v>
           </cell>
         </row>
         <row r="16">
@@ -1702,22 +1786,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>72</v>
+            <v>86</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>4800</v>
+            <v>3400</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>4452.0495824872778</v>
+            <v>3221.4357981349976</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>5547.9504175127222</v>
+            <v>6778.5642018650024</v>
           </cell>
         </row>
         <row r="16">
@@ -1759,22 +1843,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>65</v>
+            <v>79</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>5500</v>
+            <v>4100</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>5047.5569965601198</v>
+            <v>3843.4386264349664</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>4952.4430034398802</v>
+            <v>6156.5613735650331</v>
           </cell>
         </row>
         <row r="16">
@@ -2013,22 +2097,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>6</v>
+            <v>8</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>15400</v>
+            <v>12600</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>13697.569400122526</v>
+            <v>11424.319854722999</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>6302.4305998774744</v>
+            <v>8575.6801452770014</v>
           </cell>
         </row>
         <row r="16">
@@ -2082,22 +2166,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>10</v>
+            <v>12</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>14700</v>
+            <v>10500</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>13588.487859238874</v>
+            <v>9896.78385192102</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>16411.512140761126</v>
+            <v>20103.21614807898</v>
           </cell>
         </row>
         <row r="16">
@@ -2397,6 +2481,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Loan1"/>
+      <sheetName val="209"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -2427,22 +2512,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>61</v>
+            <v>71</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>5900</v>
+            <v>4900</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>5382.0725484424574</v>
+            <v>4537.9176811721318</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>4617.9274515575426</v>
+            <v>5462.0823188278682</v>
           </cell>
         </row>
         <row r="16">
@@ -2453,6 +2538,63 @@
         <row r="17">
           <cell r="K17">
             <v>46298</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="K2" t="str">
+            <v>L5000D60-Pratima-N209</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="K3" t="str">
+            <v>Pratima</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="K7">
+            <v>5000</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="K9">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="K10">
+            <v>60</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>5400</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="K14">
+            <v>4579.041797209431</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="K15">
+            <v>420.95820279056898</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="K16">
+            <v>46246</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="K17">
+            <v>46366</v>
           </cell>
         </row>
       </sheetData>
@@ -2496,22 +2638,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>9</v>
+            <v>11</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>11200</v>
+            <v>8400</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>10253.395313505431</v>
+            <v>7840.638844742849</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>9746.6046864945693</v>
+            <v>12159.361155257151</v>
           </cell>
         </row>
         <row r="16">
@@ -2565,22 +2707,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>8</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>6300</v>
+            <v>4900</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>5712.1599273614993</v>
+            <v>4529.4959530796459</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>4287.8400726385007</v>
+            <v>5470.5040469203541</v>
           </cell>
         </row>
         <row r="16">
@@ -2634,22 +2776,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>6</v>
+            <v>8</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>23100</v>
+            <v>18900</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>20546.354100183748</v>
+            <v>17136.479782084447</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>9453.6458998162525</v>
+            <v>12863.520217915553</v>
           </cell>
         </row>
         <row r="16">
@@ -2703,22 +2845,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>6</v>
+            <v>7</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>7700</v>
+            <v>7000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>6848.7847000612628</v>
+            <v>6286.1135316433047</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>3151.2152999387372</v>
+            <v>3713.8864683566953</v>
           </cell>
         </row>
         <row r="16">
@@ -2772,22 +2914,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>6</v>
+            <v>8</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>15400</v>
+            <v>12600</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>13697.569400122526</v>
+            <v>11424.319854722999</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>6302.4305998774744</v>
+            <v>8575.6801452770014</v>
           </cell>
         </row>
         <row r="16">
@@ -2841,22 +2983,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>6</v>
+            <v>8</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>15400</v>
+            <v>12600</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>13697.569400122526</v>
+            <v>11424.319854722999</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>6302.4305998774744</v>
+            <v>8575.6801452770014</v>
           </cell>
         </row>
         <row r="16">
@@ -2910,22 +3052,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>2</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>105000</v>
+            <v>91000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>89910.157995515663</v>
+            <v>79411.625030625364</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>10089.842004484337</v>
+            <v>20588.374969374636</v>
           </cell>
         </row>
         <row r="16">
@@ -2979,22 +3121,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>2</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>63000</v>
+            <v>54600</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>53946.09479730943</v>
+            <v>47646.975018375277</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>6053.9052026905701</v>
+            <v>12353.024981624723</v>
           </cell>
         </row>
         <row r="16">
@@ -3048,22 +3190,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>51</v>
+            <v>55</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>34500</v>
+            <v>32500</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>31001.918071958298</v>
+            <v>29380.546280768685</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>18998.081928041702</v>
+            <v>20619.453719231315</v>
           </cell>
         </row>
         <row r="16">
@@ -3117,22 +3259,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>2</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>21000</v>
+            <v>18200</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>17982.031599103153</v>
+            <v>15882.325006125111</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>2017.968400896847</v>
+            <v>4117.674993874889</v>
           </cell>
         </row>
         <row r="16">
@@ -3152,6 +3294,213 @@
 </file>
 
 <file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="205"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2" t="str">
+            <v>L100000W17-Sunita_Group-N205</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="K3" t="str">
+            <v>Sunita_Group</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="K7">
+            <v>100000</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="K9">
+            <v>7000</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="K10">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>105000</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="K14">
+            <v>89910.157995515663</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="K15">
+            <v>10089.842004484337</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="K16">
+            <v>46244</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="K17">
+            <v>46363</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="207"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2" t="str">
+            <v>L20000D80-Shantibala-N207</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="K3" t="str">
+            <v>Shantibala</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="K7">
+            <v>20000</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="K9">
+            <v>300</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="K10">
+            <v>80</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>21000</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="K14">
+            <v>17886.991816415415</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="K15">
+            <v>2113.0081835845849</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="K16">
+            <v>46242</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="K17">
+            <v>46362</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="208"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2" t="str">
+            <v>L20000W17-Wangkheimayum_Thoibisana-N208</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="K3" t="str">
+            <v>Wangkheimayum_Thoibisana</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="K7">
+            <v>20000</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="K9">
+            <v>1400</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="K10">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>21000</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="K14">
+            <v>17982.031599103153</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="K15">
+            <v>2017.968400896847</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="K16">
+            <v>46248</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="K17">
+            <v>46367</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3427,9 +3776,20 @@
             <v>3000</v>
           </cell>
         </row>
+        <row r="25">
+          <cell r="A25">
+            <v>46248</v>
+          </cell>
+          <cell r="C25" t="str">
+            <v>Borrowing</v>
+          </cell>
+          <cell r="E25">
+            <v>10000</v>
+          </cell>
+        </row>
         <row r="31">
           <cell r="E31">
-            <v>661880</v>
+            <v>671880</v>
           </cell>
         </row>
       </sheetData>
@@ -3555,12 +3915,23 @@
             <v>3000</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="A12">
+            <v>46248</v>
+          </cell>
+          <cell r="C12" t="str">
+            <v>Loan Advance</v>
+          </cell>
+          <cell r="F12">
+            <v>20000</v>
+          </cell>
+        </row>
         <row r="17">
           <cell r="A17" t="str">
             <v>TOTAL</v>
           </cell>
           <cell r="F17">
-            <v>767000</v>
+            <v>787000</v>
           </cell>
         </row>
       </sheetData>
@@ -3570,32 +3941,32 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="205"/>
+      <sheetName val="211"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
           <cell r="K2" t="str">
-            <v>L100000W17-Sunita_Group-N205</v>
+            <v>L20000W17-Salam_Anjala-N211</v>
           </cell>
         </row>
         <row r="3">
           <cell r="K3" t="str">
-            <v>Sunita_Group</v>
+            <v>Salam_Anjala</v>
           </cell>
         </row>
         <row r="7">
           <cell r="K7">
-            <v>100000</v>
+            <v>20000</v>
           </cell>
         </row>
         <row r="9">
           <cell r="K9">
-            <v>7000</v>
+            <v>1400</v>
           </cell>
         </row>
         <row r="10">
@@ -3610,12 +3981,12 @@
         </row>
         <row r="13">
           <cell r="K13">
-            <v>119000</v>
+            <v>23800</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>119000</v>
+            <v>23800</v>
           </cell>
         </row>
         <row r="15">
@@ -3639,91 +4010,22 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="207"/>
+      <sheetName val="212"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
           <cell r="K2" t="str">
-            <v>L20000D80-Shantibala-N207</v>
+            <v>L20000W17-Konsam_Ranjana-N212</v>
           </cell>
         </row>
         <row r="3">
           <cell r="K3" t="str">
-            <v>Shantibala</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="K7">
-            <v>20000</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="K9">
-            <v>300</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="K10">
-            <v>80</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="K12">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="K13">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="K14">
-            <v>24000</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="K15">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="K16" t="str">
-            <v/>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="K17" t="str">
-            <v/>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="208"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2" t="str">
-            <v>L20000W17-Wangkheimayum_Thoibisana-N208</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="K3" t="str">
-            <v>Wangkheimayum_Thoibisana</v>
+            <v>Konsam_Ranjana</v>
           </cell>
         </row>
         <row r="7">
@@ -3871,22 +4173,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>53</v>
+            <v>64</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>26800</v>
+            <v>22400</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>24155.002294956197</v>
+            <v>20526.305336742687</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>15844.997705043803</v>
+            <v>19473.694663257313</v>
           </cell>
         </row>
         <row r="16">
@@ -3928,22 +4230,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>1</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>22400</v>
+            <v>19600</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>19001.031241588931</v>
+            <v>16942.599422027139</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>998.96875841106885</v>
+            <v>3057.4005779728614</v>
           </cell>
         </row>
         <row r="16">
@@ -3997,22 +4299,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>95</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>5000</v>
+            <v>4000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>4803.13010252807</v>
+            <v>3872.1386840566906</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>15196.86989747193</v>
+            <v>16127.86131594331</v>
           </cell>
         </row>
         <row r="16">
@@ -4124,22 +4426,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>6</v>
+            <v>8</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>138600</v>
+            <v>113400</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>123278.12460110265</v>
+            <v>102818.8786925069</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>56721.875398897348</v>
+            <v>77181.1213074931</v>
           </cell>
         </row>
         <row r="16">
@@ -4251,22 +4553,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>4</v>
+            <v>6</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>27300</v>
+            <v>23100</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>23823.487509187638</v>
+            <v>20546.354100183748</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>6176.5124908123616</v>
+            <v>9453.6458998162525</v>
           </cell>
         </row>
         <row r="16">
@@ -4447,22 +4749,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>2</v>
+            <v>9</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>11600</v>
+            <v>10200</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>9722.813926576051</v>
+            <v>8725.3031755911798</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>277.18607342394898</v>
+            <v>1274.6968244088202</v>
           </cell>
         </row>
         <row r="16">
@@ -4777,7 +5079,7 @@
       <c r="J1" s="82"/>
       <c r="K1" s="83">
         <f>SUM(J5:J1000)</f>
-        <v>843300</v>
+        <v>790000</v>
       </c>
       <c r="L1" s="84"/>
       <c r="N1" s="78" t="s">
@@ -4786,7 +5088,7 @@
       <c r="O1" s="10"/>
       <c r="P1" s="78">
         <f>SUM(P5:P1000)</f>
-        <v>65300</v>
+        <v>67400</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4799,7 +5101,7 @@
       <c r="J2" s="82"/>
       <c r="K2" s="83">
         <f>SUM(K5:K1000)</f>
-        <v>762360.34486046841</v>
+        <v>704659.79450026399</v>
       </c>
       <c r="L2" s="84"/>
       <c r="M2" s="2"/>
@@ -5011,7 +5313,7 @@
       </c>
       <c r="G7" s="19">
         <f t="shared" ref="G7:G17" si="0">IF(H7,H7-I7,"")</f>
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H7" s="62">
         <f>[3]Loan1!$K$10</f>
@@ -5019,19 +5321,19 @@
       </c>
       <c r="I7" s="62">
         <f>[3]Loan1!$K$12</f>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J7" s="15">
         <f>[3]Loan1!$K$13</f>
-        <v>34500</v>
+        <v>32500</v>
       </c>
       <c r="K7" s="15">
         <f>[3]Loan1!$K$14</f>
-        <v>31001.918071958298</v>
+        <v>29380.546280768685</v>
       </c>
       <c r="L7" s="64">
         <f>[3]Loan1!$K$15</f>
-        <v>18998.081928041702</v>
+        <v>20619.453719231315</v>
       </c>
       <c r="M7" s="65">
         <f>[3]Loan1!$K$16</f>
@@ -5135,7 +5437,7 @@
       </c>
       <c r="G9" s="19">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H9" s="62">
         <f>[5]Loan1!$K$10</f>
@@ -5143,19 +5445,19 @@
       </c>
       <c r="I9" s="62">
         <f>[5]Loan1!$K$12</f>
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J9" s="15">
         <f>[5]Loan1!$K$13</f>
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="K9" s="15">
         <f>[5]Loan1!$K$14</f>
-        <v>4803.13010252807</v>
+        <v>3872.1386840566906</v>
       </c>
       <c r="L9" s="64">
         <f>[5]Loan1!$K$15</f>
-        <v>15196.86989747193</v>
+        <v>16127.86131594331</v>
       </c>
       <c r="M9" s="65">
         <f>[5]Loan1!$K$16</f>
@@ -5476,125 +5778,123 @@
       </c>
     </row>
     <row r="15" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="62">
+      <c r="A15" s="41">
         <f t="shared" si="1"/>
         <v>173</v>
       </c>
-      <c r="B15" s="62" t="str">
+      <c r="B15" s="41" t="str">
         <f>[11]Loan1!$K$3</f>
         <v>Sudhana</v>
       </c>
-      <c r="C15" s="62" t="s">
+      <c r="C15" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="63" t="str">
+      <c r="D15" s="67" t="str">
         <f>[11]Loan1!$K$2</f>
         <v>L20000W17-Sudhana-NLoan1</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="68">
         <f>[11]Loan1!$K$7</f>
         <v>20000</v>
       </c>
-      <c r="F15" s="62">
+      <c r="F15" s="41">
         <f>[11]Loan1!$K$9</f>
         <v>1400</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="41">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="H15" s="62">
+        <v>0</v>
+      </c>
+      <c r="H15" s="41">
         <f>[11]Loan1!$K$10</f>
         <v>17</v>
       </c>
-      <c r="I15" s="62">
+      <c r="I15" s="41">
         <f>[11]Loan1!$K$12</f>
-        <v>14</v>
-      </c>
-      <c r="J15" s="15">
+        <v>17</v>
+      </c>
+      <c r="J15" s="68">
         <f>[11]Loan1!$K$13</f>
-        <v>4200</v>
-      </c>
-      <c r="K15" s="15">
+        <v>0</v>
+      </c>
+      <c r="K15" s="68">
         <f>[11]Loan1!$K$14</f>
-        <v>4037.031116629747</v>
-      </c>
-      <c r="L15" s="64">
+        <v>9.1336005425546318E-10</v>
+      </c>
+      <c r="L15" s="69">
         <f>[11]Loan1!$K$15</f>
-        <v>15962.968883370253</v>
-      </c>
-      <c r="M15" s="65">
+        <v>19999.999999999087</v>
+      </c>
+      <c r="M15" s="70">
         <f>[11]Loan1!$K$16</f>
         <v>46150</v>
       </c>
-      <c r="N15" s="66">
+      <c r="N15" s="71">
         <f>[11]Loan1!$K$17</f>
         <v>46269</v>
       </c>
-      <c r="P15" s="43">
-        <v>1400</v>
-      </c>
+      <c r="O15" s="42"/>
+      <c r="P15" s="45"/>
       <c r="R15" s="43"/>
     </row>
     <row r="16" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19">
+      <c r="A16" s="41">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
-      <c r="B16" s="19" t="str">
+      <c r="B16" s="41" t="str">
         <f>[12]Loan1!$K$3</f>
         <v>Bidyarani</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="72" t="str">
+      <c r="D16" s="67" t="str">
         <f>[12]Loan1!$K$2</f>
         <v>L20000W17-Bidyarani-NLoan1</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="68">
         <f>[12]Loan1!$K$7</f>
         <v>20000</v>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="41">
         <f>[12]Loan1!$K$9</f>
         <v>1400</v>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="19">
+      <c r="H16" s="41">
         <f>[12]Loan1!$K$10</f>
         <v>17</v>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="41">
         <f>[12]Loan1!$K$12</f>
         <v>17</v>
       </c>
-      <c r="J16" s="18">
+      <c r="J16" s="68">
         <f>[12]Loan1!$K$13</f>
         <v>0</v>
       </c>
-      <c r="K16" s="18">
+      <c r="K16" s="68">
         <f>[12]Loan1!$K$14</f>
         <v>9.1336005425546318E-10</v>
       </c>
-      <c r="L16" s="73">
+      <c r="L16" s="69">
         <f>[12]Loan1!$K$15</f>
         <v>19999.999999999087</v>
       </c>
-      <c r="M16" s="74">
+      <c r="M16" s="70">
         <f>[12]Loan1!$K$16</f>
         <v>46150</v>
       </c>
-      <c r="N16" s="75">
+      <c r="N16" s="71">
         <f>[12]Loan1!$K$17</f>
         <v>46269</v>
       </c>
-      <c r="P16" s="43">
-        <v>1400</v>
-      </c>
+      <c r="O16" s="42"/>
+      <c r="P16" s="45"/>
       <c r="R16" s="43"/>
     </row>
     <row r="17" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5688,7 +5988,7 @@
       </c>
       <c r="G18" s="19">
         <f t="shared" ref="G18:G21" si="2">IF(H18,H18-I18,"")</f>
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="H18" s="19">
         <f>[14]Loan1!$K$10</f>
@@ -5696,19 +5996,19 @@
       </c>
       <c r="I18" s="19">
         <f>[14]Loan1!$K$12</f>
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="J18" s="18">
         <f>[14]Loan1!$K$13</f>
-        <v>4800</v>
+        <v>3400</v>
       </c>
       <c r="K18" s="18">
         <f>[14]Loan1!$K$14</f>
-        <v>4452.0495824872778</v>
+        <v>3221.4357981349976</v>
       </c>
       <c r="L18" s="73">
         <f>[14]Loan1!$K$15</f>
-        <v>5547.9504175127222</v>
+        <v>6778.5642018650024</v>
       </c>
       <c r="M18" s="74">
         <f>[14]Loan1!$K$16</f>
@@ -5874,7 +6174,7 @@
       </c>
       <c r="G21" s="19">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H21" s="62">
         <f>[17]Loan1!$K$10</f>
@@ -5882,19 +6182,19 @@
       </c>
       <c r="I21" s="62">
         <f>[17]Loan1!$K$12</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J21" s="15">
         <f>[17]Loan1!$K$13</f>
-        <v>14700</v>
+        <v>10500</v>
       </c>
       <c r="K21" s="15">
         <f>[17]Loan1!$K$14</f>
-        <v>13588.487859238874</v>
+        <v>9896.78385192102</v>
       </c>
       <c r="L21" s="64">
         <f>[17]Loan1!$K$15</f>
-        <v>16411.512140761126</v>
+        <v>20103.21614807898</v>
       </c>
       <c r="M21" s="65">
         <f>[17]Loan1!$K$16</f>
@@ -6123,7 +6423,7 @@
       </c>
       <c r="G25" s="19">
         <f t="shared" si="3"/>
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="H25" s="62">
         <f>[14]Loan2!$K$10</f>
@@ -6131,19 +6431,19 @@
       </c>
       <c r="I25" s="62">
         <f>[14]Loan2!$K$12</f>
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="J25" s="15">
         <f>[14]Loan2!$K$13</f>
-        <v>5500</v>
+        <v>4100</v>
       </c>
       <c r="K25" s="15">
         <f>[14]Loan2!$K$14</f>
-        <v>5047.5569965601198</v>
+        <v>3843.4386264349664</v>
       </c>
       <c r="L25" s="64">
         <f>[14]Loan2!$K$15</f>
-        <v>4952.4430034398802</v>
+        <v>6156.5613735650331</v>
       </c>
       <c r="M25" s="65">
         <f>[14]Loan2!$K$16</f>
@@ -6190,7 +6490,7 @@
       </c>
       <c r="G26" s="19">
         <f t="shared" ref="G26:G89" si="4">IF(H26,H26-I26,"")</f>
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="H26" s="19">
         <f>[21]Loan1!$K$10</f>
@@ -6198,19 +6498,19 @@
       </c>
       <c r="I26" s="19">
         <f>[21]Loan1!$K$12</f>
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="J26" s="18">
         <f>[21]Loan1!$K$13</f>
-        <v>5900</v>
+        <v>4900</v>
       </c>
       <c r="K26" s="18">
         <f>[21]Loan1!$K$14</f>
-        <v>5382.0725484424574</v>
+        <v>4537.9176811721318</v>
       </c>
       <c r="L26" s="73">
         <f>[21]Loan1!$K$15</f>
-        <v>4617.9274515575426</v>
+        <v>5462.0823188278682</v>
       </c>
       <c r="M26" s="74">
         <f>[21]Loan1!$K$16</f>
@@ -6257,7 +6557,7 @@
       </c>
       <c r="G27" s="19">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H27" s="62">
         <f>[22]Loan1!$K$10</f>
@@ -6265,19 +6565,19 @@
       </c>
       <c r="I27" s="62">
         <f>[22]Loan1!$K$12</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J27" s="15">
         <f>[22]Loan1!$K$13</f>
-        <v>11200</v>
+        <v>8400</v>
       </c>
       <c r="K27" s="15">
         <f>[22]Loan1!$K$14</f>
-        <v>10253.395313505431</v>
+        <v>7840.638844742849</v>
       </c>
       <c r="L27" s="64">
         <f>[22]Loan1!$K$15</f>
-        <v>9746.6046864945693</v>
+        <v>12159.361155257151</v>
       </c>
       <c r="M27" s="65">
         <f>[22]Loan1!$K$16</f>
@@ -6323,7 +6623,7 @@
       </c>
       <c r="G28" s="19">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H28" s="19">
         <f>[23]Loan1!$K$10</f>
@@ -6331,19 +6631,19 @@
       </c>
       <c r="I28" s="19">
         <f>[23]Loan1!$K$12</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J28" s="18">
         <f>[23]Loan1!$K$13</f>
-        <v>6300</v>
+        <v>4900</v>
       </c>
       <c r="K28" s="18">
         <f>[23]Loan1!$K$14</f>
-        <v>5712.1599273614993</v>
+        <v>4529.4959530796459</v>
       </c>
       <c r="L28" s="73">
         <f>[23]Loan1!$K$15</f>
-        <v>4287.8400726385007</v>
+        <v>5470.5040469203541</v>
       </c>
       <c r="M28" s="74">
         <f>[23]Loan1!$K$16</f>
@@ -6384,7 +6684,7 @@
       </c>
       <c r="G29" s="19">
         <f t="shared" si="4"/>
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="H29" s="62">
         <f>'[4]188'!$K$10</f>
@@ -6392,19 +6692,19 @@
       </c>
       <c r="I29" s="62">
         <f>'[4]188'!$K$12</f>
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="J29" s="15">
         <f>'[4]188'!$K$13</f>
-        <v>26800</v>
+        <v>22400</v>
       </c>
       <c r="K29" s="15">
         <f>'[4]188'!$K$14</f>
-        <v>24155.002294956197</v>
+        <v>20526.305336742687</v>
       </c>
       <c r="L29" s="64">
         <f>'[4]188'!$K$15</f>
-        <v>15844.997705043803</v>
+        <v>19473.694663257313</v>
       </c>
       <c r="M29" s="65">
         <f>'[4]188'!$K$16</f>
@@ -6511,7 +6811,7 @@
       </c>
       <c r="G31" s="19">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H31" s="62">
         <f>'[12]190'!$K$10</f>
@@ -6519,19 +6819,19 @@
       </c>
       <c r="I31" s="62">
         <f>'[12]190'!$K$12</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J31" s="15">
         <f>'[12]190'!$K$13</f>
-        <v>9800</v>
+        <v>5600</v>
       </c>
       <c r="K31" s="15">
         <f>'[12]190'!$K$14</f>
-        <v>8471.2997110135693</v>
+        <v>5126.6976567527154</v>
       </c>
       <c r="L31" s="64">
         <f>'[12]190'!$K$15</f>
-        <v>1528.7002889864307</v>
+        <v>4873.3023432472846</v>
       </c>
       <c r="M31" s="65">
         <f>'[12]190'!$K$16</f>
@@ -6572,7 +6872,7 @@
       </c>
       <c r="G32" s="19">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H32" s="19">
         <f>'[24]191'!$K$10</f>
@@ -6580,19 +6880,19 @@
       </c>
       <c r="I32" s="19">
         <f>'[24]191'!$K$12</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J32" s="18">
         <f>'[24]191'!$K$13</f>
-        <v>23100</v>
+        <v>18900</v>
       </c>
       <c r="K32" s="18">
         <f>'[24]191'!$K$14</f>
-        <v>20546.354100183748</v>
+        <v>17136.479782084447</v>
       </c>
       <c r="L32" s="73">
         <f>'[24]191'!$K$15</f>
-        <v>9453.6458998162525</v>
+        <v>12863.520217915553</v>
       </c>
       <c r="M32" s="74">
         <f>'[24]191'!$K$16</f>
@@ -6636,7 +6936,7 @@
       </c>
       <c r="G33" s="19">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H33" s="62">
         <f>'[25]192'!$K$10</f>
@@ -6644,19 +6944,19 @@
       </c>
       <c r="I33" s="62">
         <f>'[25]192'!$K$12</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J33" s="15">
         <f>'[25]192'!$K$13</f>
-        <v>7700</v>
+        <v>7000</v>
       </c>
       <c r="K33" s="15">
         <f>'[25]192'!$K$14</f>
-        <v>6848.7847000612628</v>
+        <v>6286.1135316433047</v>
       </c>
       <c r="L33" s="64">
         <f>'[25]192'!$K$15</f>
-        <v>3151.2152999387372</v>
+        <v>3713.8864683566953</v>
       </c>
       <c r="M33" s="65">
         <f>'[25]192'!$K$16</f>
@@ -6697,7 +6997,7 @@
       </c>
       <c r="G34" s="19">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H34" s="19">
         <f>'[26]193'!$K$10</f>
@@ -6705,19 +7005,19 @@
       </c>
       <c r="I34" s="19">
         <f>'[26]193'!$K$12</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J34" s="18">
         <f>'[26]193'!$K$13</f>
-        <v>15400</v>
+        <v>12600</v>
       </c>
       <c r="K34" s="18">
         <f>'[26]193'!$K$14</f>
-        <v>13697.569400122526</v>
+        <v>11424.319854722999</v>
       </c>
       <c r="L34" s="73">
         <f>'[26]193'!$K$15</f>
-        <v>6302.4305998774744</v>
+        <v>8575.6801452770014</v>
       </c>
       <c r="M34" s="74">
         <f>'[26]193'!$K$16</f>
@@ -6758,7 +7058,7 @@
       </c>
       <c r="G35" s="19">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H35" s="62">
         <f>'[27]194'!$K$10</f>
@@ -6766,19 +7066,19 @@
       </c>
       <c r="I35" s="62">
         <f>'[27]194'!$K$12</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J35" s="15">
         <f>'[27]194'!$K$13</f>
-        <v>15400</v>
+        <v>12600</v>
       </c>
       <c r="K35" s="15">
         <f>'[27]194'!$K$14</f>
-        <v>13697.569400122526</v>
+        <v>11424.319854722999</v>
       </c>
       <c r="L35" s="64">
         <f>'[27]194'!$K$15</f>
-        <v>6302.4305998774744</v>
+        <v>8575.6801452770014</v>
       </c>
       <c r="M35" s="65">
         <f>'[27]194'!$K$16</f>
@@ -6822,7 +7122,7 @@
       </c>
       <c r="G36" s="19">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H36" s="19">
         <f>'[6]195'!$K$10</f>
@@ -6830,19 +7130,19 @@
       </c>
       <c r="I36" s="19">
         <f>'[6]195'!$K$12</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J36" s="18">
         <f>'[6]195'!$K$13</f>
-        <v>138600</v>
+        <v>113400</v>
       </c>
       <c r="K36" s="18">
         <f>'[6]195'!$K$14</f>
-        <v>123278.12460110265</v>
+        <v>102818.8786925069</v>
       </c>
       <c r="L36" s="73">
         <f>'[6]195'!$K$15</f>
-        <v>56721.875398897348</v>
+        <v>77181.1213074931</v>
       </c>
       <c r="M36" s="74">
         <f>'[6]195'!$K$16</f>
@@ -6943,7 +7243,7 @@
       </c>
       <c r="G38" s="19">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H38" s="19">
         <f>'[16]197'!$K$10</f>
@@ -6951,19 +7251,19 @@
       </c>
       <c r="I38" s="19">
         <f>'[16]197'!$K$12</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J38" s="18">
         <f>'[16]197'!$K$13</f>
-        <v>15400</v>
+        <v>12600</v>
       </c>
       <c r="K38" s="18">
         <f>'[16]197'!$K$14</f>
-        <v>13697.569400122526</v>
+        <v>11424.319854722999</v>
       </c>
       <c r="L38" s="73">
         <f>'[16]197'!$K$15</f>
-        <v>6302.4305998774744</v>
+        <v>8575.6801452770014</v>
       </c>
       <c r="M38" s="74">
         <f>'[16]197'!$K$16</f>
@@ -7003,7 +7303,7 @@
       </c>
       <c r="G39" s="19">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H39" s="62">
         <f>'[10]198'!$K$10</f>
@@ -7011,19 +7311,19 @@
       </c>
       <c r="I39" s="62">
         <f>'[10]198'!$K$12</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J39" s="15">
         <f>'[10]198'!$K$13</f>
-        <v>15400</v>
+        <v>12600</v>
       </c>
       <c r="K39" s="15">
         <f>'[10]198'!$K$14</f>
-        <v>13697.569400122526</v>
+        <v>11424.319854722999</v>
       </c>
       <c r="L39" s="64">
         <f>'[10]198'!$K$15</f>
-        <v>6302.4305998774744</v>
+        <v>8575.6801452770014</v>
       </c>
       <c r="M39" s="65">
         <f>'[10]198'!$K$16</f>
@@ -7063,7 +7363,7 @@
       </c>
       <c r="G40" s="19">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H40" s="19">
         <f>'[13]199'!$K$10</f>
@@ -7071,19 +7371,19 @@
       </c>
       <c r="I40" s="19">
         <f>'[13]199'!$K$12</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J40" s="18">
         <f>'[13]199'!$K$13</f>
-        <v>21000</v>
+        <v>15000</v>
       </c>
       <c r="K40" s="18">
         <f>'[13]199'!$K$14</f>
-        <v>18745.312366590952</v>
+        <v>13769.437260492452</v>
       </c>
       <c r="L40" s="73">
         <f>'[13]199'!$K$15</f>
-        <v>11254.687633409048</v>
+        <v>16230.562739507548</v>
       </c>
       <c r="M40" s="74">
         <f>'[13]199'!$K$16</f>
@@ -7123,7 +7423,7 @@
       </c>
       <c r="G41" s="19">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H41" s="62">
         <f>'[7]200'!$K$10</f>
@@ -7131,19 +7431,19 @@
       </c>
       <c r="I41" s="62">
         <f>'[7]200'!$K$12</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J41" s="15">
         <f>'[7]200'!$K$13</f>
-        <v>27300</v>
+        <v>23100</v>
       </c>
       <c r="K41" s="15">
         <f>'[7]200'!$K$14</f>
-        <v>23823.487509187638</v>
+        <v>20546.354100183748</v>
       </c>
       <c r="L41" s="64">
         <f>'[7]200'!$K$15</f>
-        <v>6176.5124908123616</v>
+        <v>9453.6458998162525</v>
       </c>
       <c r="M41" s="65">
         <f>'[7]200'!$K$16</f>
@@ -7183,7 +7483,7 @@
       </c>
       <c r="G42" s="19">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H42" s="19">
         <f>'[28]195'!$K$10</f>
@@ -7191,19 +7491,19 @@
       </c>
       <c r="I42" s="19">
         <f>'[28]195'!$K$12</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J42" s="18">
         <f>'[28]195'!$K$13</f>
-        <v>105000</v>
+        <v>91000</v>
       </c>
       <c r="K42" s="18">
         <f>'[28]195'!$K$14</f>
-        <v>89910.157995515663</v>
+        <v>79411.625030625364</v>
       </c>
       <c r="L42" s="73">
         <f>'[28]195'!$K$15</f>
-        <v>10089.842004484337</v>
+        <v>20588.374969374636</v>
       </c>
       <c r="M42" s="74">
         <f>'[28]195'!$K$16</f>
@@ -7243,7 +7543,7 @@
       </c>
       <c r="G43" s="19">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H43" s="62">
         <f>[29]Loan1!$K$10</f>
@@ -7251,19 +7551,19 @@
       </c>
       <c r="I43" s="62">
         <f>[29]Loan1!$K$12</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J43" s="15">
         <f>[29]Loan1!$K$13</f>
-        <v>63000</v>
+        <v>54600</v>
       </c>
       <c r="K43" s="15">
         <f>[29]Loan1!$K$14</f>
-        <v>53946.09479730943</v>
+        <v>47646.975018375277</v>
       </c>
       <c r="L43" s="64">
         <f>[29]Loan1!$K$15</f>
-        <v>6053.9052026905701</v>
+        <v>12353.024981624723</v>
       </c>
       <c r="M43" s="65">
         <f>[29]Loan1!$K$16</f>
@@ -7303,7 +7603,7 @@
       </c>
       <c r="G44" s="19">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H44" s="36">
         <f>'[30]203'!$K$10</f>
@@ -7311,19 +7611,19 @@
       </c>
       <c r="I44" s="36">
         <f>'[30]203'!$K$12</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J44" s="39">
         <f>'[30]203'!$K$13</f>
-        <v>21000</v>
+        <v>18200</v>
       </c>
       <c r="K44" s="39">
         <f>'[30]203'!$K$14</f>
-        <v>17982.031599103153</v>
+        <v>15882.325006125111</v>
       </c>
       <c r="L44" s="40">
         <f>'[30]203'!$K$15</f>
-        <v>2017.968400896847</v>
+        <v>4117.674993874889</v>
       </c>
       <c r="M44" s="20">
         <f>'[30]203'!$K$16</f>
@@ -7363,7 +7663,7 @@
       </c>
       <c r="G45" s="19">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H45" s="33">
         <f>'[4]204'!$K$10</f>
@@ -7371,19 +7671,19 @@
       </c>
       <c r="I45" s="33">
         <f>'[4]204'!$K$12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J45" s="35">
         <f>'[4]204'!$K$13</f>
-        <v>22400</v>
+        <v>19600</v>
       </c>
       <c r="K45" s="35">
         <f>'[4]204'!$K$14</f>
-        <v>19001.031241588931</v>
+        <v>16942.599422027139</v>
       </c>
       <c r="L45" s="37">
         <f>'[4]204'!$K$15</f>
-        <v>998.96875841106885</v>
+        <v>3057.4005779728614</v>
       </c>
       <c r="M45" s="22">
         <f>'[4]204'!$K$16</f>
@@ -7403,55 +7703,55 @@
         <v>205</v>
       </c>
       <c r="B46" s="36" t="str">
-        <f>'[32]205'!$K$3</f>
+        <f>'[31]205'!$K$3</f>
         <v>Sunita_Group</v>
       </c>
       <c r="C46" s="36" t="s">
         <v>6</v>
       </c>
       <c r="D46" s="38" t="str">
-        <f>'[32]205'!$K$2</f>
+        <f>'[31]205'!$K$2</f>
         <v>L100000W17-Sunita_Group-N205</v>
       </c>
       <c r="E46" s="39">
-        <f>'[32]205'!$K$7</f>
+        <f>'[31]205'!$K$7</f>
         <v>100000</v>
       </c>
       <c r="F46" s="36">
-        <f>'[32]205'!$K$9</f>
+        <f>'[31]205'!$K$9</f>
         <v>7000</v>
       </c>
       <c r="G46" s="19">
         <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="H46" s="36">
+        <f>'[31]205'!$K$10</f>
         <v>17</v>
       </c>
-      <c r="H46" s="36">
-        <f>'[32]205'!$K$10</f>
-        <v>17</v>
-      </c>
       <c r="I46" s="36">
-        <f>'[32]205'!$K$12</f>
-        <v>0</v>
+        <f>'[31]205'!$K$12</f>
+        <v>2</v>
       </c>
       <c r="J46" s="39">
-        <f>'[32]205'!$K$13</f>
-        <v>119000</v>
+        <f>'[31]205'!$K$13</f>
+        <v>105000</v>
       </c>
       <c r="K46" s="39">
-        <f>'[32]205'!$K$14</f>
-        <v>119000</v>
+        <f>'[31]205'!$K$14</f>
+        <v>89910.157995515663</v>
       </c>
       <c r="L46" s="40">
-        <f>'[32]205'!$K$15</f>
-        <v>0</v>
-      </c>
-      <c r="M46" s="20" t="str">
-        <f>'[32]205'!$K$16</f>
-        <v/>
-      </c>
-      <c r="N46" s="21" t="str">
-        <f>'[32]205'!$K$17</f>
-        <v/>
+        <f>'[31]205'!$K$15</f>
+        <v>10089.842004484337</v>
+      </c>
+      <c r="M46" s="20">
+        <f>'[31]205'!$K$16</f>
+        <v>46244</v>
+      </c>
+      <c r="N46" s="21">
+        <f>'[31]205'!$K$17</f>
+        <v>46363</v>
       </c>
       <c r="P46" s="43">
         <v>7000</v>
@@ -7483,7 +7783,7 @@
       </c>
       <c r="G47" s="19">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H47" s="33">
         <f>'[9]206'!$K$10</f>
@@ -7491,19 +7791,19 @@
       </c>
       <c r="I47" s="33">
         <f>'[9]206'!$K$12</f>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J47" s="35">
         <f>'[9]206'!$K$13</f>
-        <v>11600</v>
+        <v>10200</v>
       </c>
       <c r="K47" s="35">
         <f>'[9]206'!$K$14</f>
-        <v>9722.813926576051</v>
+        <v>8725.3031755911798</v>
       </c>
       <c r="L47" s="37">
         <f>'[9]206'!$K$15</f>
-        <v>277.18607342394898</v>
+        <v>1274.6968244088202</v>
       </c>
       <c r="M47" s="22">
         <f>'[9]206'!$K$16</f>
@@ -7523,55 +7823,55 @@
         <v>207</v>
       </c>
       <c r="B48" s="36" t="str">
-        <f>'[33]207'!$K$3</f>
+        <f>'[32]207'!$K$3</f>
         <v>Shantibala</v>
       </c>
       <c r="C48" s="36" t="s">
         <v>6</v>
       </c>
       <c r="D48" s="38" t="str">
-        <f>'[33]207'!$K$2</f>
+        <f>'[32]207'!$K$2</f>
         <v>L20000D80-Shantibala-N207</v>
       </c>
       <c r="E48" s="39">
-        <f>'[33]207'!$K$7</f>
+        <f>'[32]207'!$K$7</f>
         <v>20000</v>
       </c>
       <c r="F48" s="36">
-        <f>'[33]207'!$K$9</f>
+        <f>'[32]207'!$K$9</f>
         <v>300</v>
       </c>
       <c r="G48" s="19">
         <f t="shared" si="4"/>
+        <v>70</v>
+      </c>
+      <c r="H48" s="36">
+        <f>'[32]207'!$K$10</f>
         <v>80</v>
       </c>
-      <c r="H48" s="36">
-        <f>'[33]207'!$K$10</f>
-        <v>80</v>
-      </c>
       <c r="I48" s="36">
-        <f>'[33]207'!$K$12</f>
-        <v>0</v>
+        <f>'[32]207'!$K$12</f>
+        <v>10</v>
       </c>
       <c r="J48" s="39">
-        <f>'[33]207'!$K$13</f>
-        <v>24000</v>
+        <f>'[32]207'!$K$13</f>
+        <v>21000</v>
       </c>
       <c r="K48" s="39">
-        <f>'[33]207'!$K$14</f>
-        <v>24000</v>
+        <f>'[32]207'!$K$14</f>
+        <v>17886.991816415415</v>
       </c>
       <c r="L48" s="40">
-        <f>'[33]207'!$K$15</f>
-        <v>0</v>
-      </c>
-      <c r="M48" s="20" t="str">
-        <f>'[33]207'!$K$16</f>
-        <v/>
-      </c>
-      <c r="N48" s="21" t="str">
-        <f>'[33]207'!$K$17</f>
-        <v/>
+        <f>'[32]207'!$K$15</f>
+        <v>2113.0081835845849</v>
+      </c>
+      <c r="M48" s="20">
+        <f>'[32]207'!$K$16</f>
+        <v>46242</v>
+      </c>
+      <c r="N48" s="21">
+        <f>'[32]207'!$K$17</f>
+        <v>46362</v>
       </c>
       <c r="P48" s="43">
         <v>2100</v>
@@ -7583,55 +7883,55 @@
         <v>208</v>
       </c>
       <c r="B49" s="33" t="str">
-        <f>'[34]208'!$K$3</f>
+        <f>'[33]208'!$K$3</f>
         <v>Wangkheimayum_Thoibisana</v>
       </c>
       <c r="C49" s="33" t="s">
         <v>6</v>
       </c>
       <c r="D49" s="34" t="str">
-        <f>'[34]208'!$K$2</f>
+        <f>'[33]208'!$K$2</f>
         <v>L20000W17-Wangkheimayum_Thoibisana-N208</v>
       </c>
       <c r="E49" s="35">
-        <f>'[34]208'!$K$7</f>
+        <f>'[33]208'!$K$7</f>
         <v>20000</v>
       </c>
       <c r="F49" s="33">
-        <f>'[34]208'!$K$9</f>
+        <f>'[33]208'!$K$9</f>
         <v>1400</v>
       </c>
       <c r="G49" s="19">
         <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="H49" s="33">
+        <f>'[33]208'!$K$10</f>
         <v>17</v>
       </c>
-      <c r="H49" s="33">
-        <f>'[34]208'!$K$10</f>
-        <v>17</v>
-      </c>
       <c r="I49" s="33">
-        <f>'[34]208'!$K$12</f>
-        <v>0</v>
+        <f>'[33]208'!$K$12</f>
+        <v>2</v>
       </c>
       <c r="J49" s="35">
-        <f>'[34]208'!$K$13</f>
-        <v>23800</v>
+        <f>'[33]208'!$K$13</f>
+        <v>21000</v>
       </c>
       <c r="K49" s="35">
-        <f>'[34]208'!$K$14</f>
-        <v>23800</v>
+        <f>'[33]208'!$K$14</f>
+        <v>17982.031599103153</v>
       </c>
       <c r="L49" s="37">
-        <f>'[34]208'!$K$15</f>
-        <v>0</v>
-      </c>
-      <c r="M49" s="22" t="str">
-        <f>'[34]208'!$K$16</f>
-        <v/>
-      </c>
-      <c r="N49" s="23" t="str">
-        <f>'[34]208'!$K$17</f>
-        <v/>
+        <f>'[33]208'!$K$15</f>
+        <v>2017.968400896847</v>
+      </c>
+      <c r="M49" s="22">
+        <f>'[33]208'!$K$16</f>
+        <v>46248</v>
+      </c>
+      <c r="N49" s="23">
+        <f>'[33]208'!$K$17</f>
+        <v>46367</v>
       </c>
       <c r="P49" s="43">
         <v>1400</v>
@@ -7642,88 +7942,240 @@
         <f t="shared" si="1"/>
         <v>209</v>
       </c>
-      <c r="B50" s="36"/>
-      <c r="C50" s="36"/>
-      <c r="D50" s="38"/>
-      <c r="E50" s="39"/>
-      <c r="F50" s="36"/>
-      <c r="G50" s="19" t="str">
+      <c r="B50" s="36" t="str">
+        <f>'[21]209'!$K$3</f>
+        <v>Pratima</v>
+      </c>
+      <c r="C50" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" s="38" t="str">
+        <f>'[21]209'!$K$2</f>
+        <v>L5000D60-Pratima-N209</v>
+      </c>
+      <c r="E50" s="39">
+        <f>'[21]209'!$K$7</f>
+        <v>5000</v>
+      </c>
+      <c r="F50" s="36">
+        <f>'[21]209'!$K$9</f>
+        <v>100</v>
+      </c>
+      <c r="G50" s="19">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H50" s="36"/>
-      <c r="I50" s="36"/>
-      <c r="J50" s="39"/>
-      <c r="K50" s="39"/>
-      <c r="L50" s="40"/>
-      <c r="M50" s="20"/>
-      <c r="N50" s="21"/>
+        <v>54</v>
+      </c>
+      <c r="H50" s="36">
+        <f>'[21]209'!$K$10</f>
+        <v>60</v>
+      </c>
+      <c r="I50" s="36">
+        <f>'[21]209'!$K$12</f>
+        <v>6</v>
+      </c>
+      <c r="J50" s="39">
+        <f>'[21]209'!$K$13</f>
+        <v>5400</v>
+      </c>
+      <c r="K50" s="39">
+        <f>'[21]209'!$K$14</f>
+        <v>4579.041797209431</v>
+      </c>
+      <c r="L50" s="40">
+        <f>'[21]209'!$K$15</f>
+        <v>420.95820279056898</v>
+      </c>
+      <c r="M50" s="20">
+        <f>'[21]209'!$K$16</f>
+        <v>46246</v>
+      </c>
+      <c r="N50" s="21">
+        <f>'[21]209'!$K$17</f>
+        <v>46366</v>
+      </c>
+      <c r="P50" s="43">
+        <v>700</v>
+      </c>
     </row>
     <row r="51" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="33">
         <f t="shared" si="1"/>
         <v>210</v>
       </c>
-      <c r="B51" s="33"/>
-      <c r="C51" s="33"/>
-      <c r="D51" s="34"/>
-      <c r="E51" s="35"/>
-      <c r="F51" s="33"/>
-      <c r="G51" s="19" t="str">
+      <c r="B51" s="33" t="str">
+        <f>'[11]210'!$K$3</f>
+        <v>Sudhana</v>
+      </c>
+      <c r="C51" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" s="34" t="str">
+        <f>'[11]210'!$K$2</f>
+        <v>L20000W17-Sudhana-N210</v>
+      </c>
+      <c r="E51" s="35">
+        <f>'[11]210'!$K$7</f>
+        <v>20000</v>
+      </c>
+      <c r="F51" s="33">
+        <f>'[11]210'!$K$9</f>
+        <v>1400</v>
+      </c>
+      <c r="G51" s="19">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H51" s="33"/>
-      <c r="I51" s="33"/>
-      <c r="J51" s="35"/>
-      <c r="K51" s="35"/>
-      <c r="L51" s="37"/>
-      <c r="M51" s="22"/>
-      <c r="N51" s="23"/>
+        <v>16</v>
+      </c>
+      <c r="H51" s="33">
+        <f>'[11]210'!$K$10</f>
+        <v>17</v>
+      </c>
+      <c r="I51" s="33">
+        <f>'[11]210'!$K$12</f>
+        <v>1</v>
+      </c>
+      <c r="J51" s="35">
+        <f>'[11]210'!$K$13</f>
+        <v>22400</v>
+      </c>
+      <c r="K51" s="35">
+        <f>'[11]210'!$K$14</f>
+        <v>19001.031241588931</v>
+      </c>
+      <c r="L51" s="37">
+        <f>'[11]210'!$K$15</f>
+        <v>998.96875841106885</v>
+      </c>
+      <c r="M51" s="22">
+        <f>'[11]210'!$K$16</f>
+        <v>46255</v>
+      </c>
+      <c r="N51" s="23">
+        <f>'[11]210'!$K$17</f>
+        <v>46374</v>
+      </c>
+      <c r="P51" s="43">
+        <v>1400</v>
+      </c>
     </row>
     <row r="52" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="36">
         <f t="shared" si="1"/>
         <v>211</v>
       </c>
-      <c r="B52" s="36"/>
-      <c r="C52" s="36"/>
-      <c r="D52" s="38"/>
-      <c r="E52" s="39"/>
-      <c r="F52" s="36"/>
-      <c r="G52" s="19" t="str">
+      <c r="B52" s="36" t="str">
+        <f>'[35]211'!$K$3</f>
+        <v>Salam_Anjala</v>
+      </c>
+      <c r="C52" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" s="38" t="str">
+        <f>'[35]211'!$K$2</f>
+        <v>L20000W17-Salam_Anjala-N211</v>
+      </c>
+      <c r="E52" s="39">
+        <f>'[35]211'!$K$7</f>
+        <v>20000</v>
+      </c>
+      <c r="F52" s="36">
+        <f>'[35]211'!$K$9</f>
+        <v>1400</v>
+      </c>
+      <c r="G52" s="19">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H52" s="36"/>
-      <c r="I52" s="36"/>
-      <c r="J52" s="39"/>
-      <c r="K52" s="39"/>
-      <c r="L52" s="40"/>
-      <c r="M52" s="20"/>
-      <c r="N52" s="21"/>
+        <v>17</v>
+      </c>
+      <c r="H52" s="36">
+        <f>'[35]211'!$K$10</f>
+        <v>17</v>
+      </c>
+      <c r="I52" s="36">
+        <f>'[35]211'!$K$12</f>
+        <v>0</v>
+      </c>
+      <c r="J52" s="39">
+        <f>'[35]211'!$K$13</f>
+        <v>23800</v>
+      </c>
+      <c r="K52" s="39">
+        <f>'[35]211'!$K$14</f>
+        <v>23800</v>
+      </c>
+      <c r="L52" s="40">
+        <f>'[35]211'!$K$15</f>
+        <v>0</v>
+      </c>
+      <c r="M52" s="20" t="str">
+        <f>'[35]211'!$K$16</f>
+        <v/>
+      </c>
+      <c r="N52" s="21" t="str">
+        <f>'[35]211'!$K$17</f>
+        <v/>
+      </c>
+      <c r="P52" s="43">
+        <v>1400</v>
+      </c>
     </row>
     <row r="53" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="33">
         <f t="shared" si="1"/>
         <v>212</v>
       </c>
-      <c r="B53" s="33"/>
-      <c r="C53" s="33"/>
-      <c r="D53" s="34"/>
-      <c r="E53" s="35"/>
-      <c r="F53" s="33"/>
-      <c r="G53" s="19" t="str">
+      <c r="B53" s="33" t="str">
+        <f>'[36]212'!$K$3</f>
+        <v>Konsam_Ranjana</v>
+      </c>
+      <c r="C53" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="D53" s="34" t="str">
+        <f>'[36]212'!$K$2</f>
+        <v>L20000W17-Konsam_Ranjana-N212</v>
+      </c>
+      <c r="E53" s="35">
+        <f>'[36]212'!$K$7</f>
+        <v>20000</v>
+      </c>
+      <c r="F53" s="33">
+        <f>'[36]212'!$K$9</f>
+        <v>1400</v>
+      </c>
+      <c r="G53" s="19">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H53" s="33"/>
-      <c r="I53" s="33"/>
-      <c r="J53" s="35"/>
-      <c r="K53" s="35"/>
-      <c r="L53" s="37"/>
-      <c r="M53" s="22"/>
-      <c r="N53" s="23"/>
+        <v>17</v>
+      </c>
+      <c r="H53" s="33">
+        <f>'[36]212'!$K$10</f>
+        <v>17</v>
+      </c>
+      <c r="I53" s="33">
+        <f>'[36]212'!$K$12</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="35">
+        <f>'[36]212'!$K$13</f>
+        <v>23800</v>
+      </c>
+      <c r="K53" s="35">
+        <f>'[36]212'!$K$14</f>
+        <v>23800</v>
+      </c>
+      <c r="L53" s="37">
+        <f>'[36]212'!$K$15</f>
+        <v>0</v>
+      </c>
+      <c r="M53" s="22" t="str">
+        <f>'[36]212'!$K$16</f>
+        <v/>
+      </c>
+      <c r="N53" s="23" t="str">
+        <f>'[36]212'!$K$17</f>
+        <v/>
+      </c>
+      <c r="P53" s="43">
+        <v>1400</v>
+      </c>
     </row>
     <row r="54" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="36">
@@ -16952,7 +17404,7 @@
       <c r="D474" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="10c4oH6xUuFc+oCzJ9bMYbhA0wtcEZIg6Rrkwa6B73gxq/9cQrHq75PfOjrWzT7WE0QzhmVFQ53zRLFWoypR1w==" saltValue="CHXdYTblCt9ijpRexnsQyA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="tYMlp7NE01OHioxjijj3u4QN6UkVOWZKsD9sXulls46RhpmXslnE7jkq/oMQiOygT7XN9ZnfK/vVaa6voE+tjg==" saltValue="/AjAvHmEBVnfIAxwujpt8A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="7">
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="N1:N2"/>
@@ -17026,37 +17478,37 @@
       </c>
       <c r="B2" s="14">
         <f>IF(A2&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A2),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A2),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C2" s="15">
         <f>IF(A2&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A2),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A2),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D2" s="15">
         <f>IF(A2&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A2),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A2),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E2" s="15">
         <f>IF(A2&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A2)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A2)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A2),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A2),
     "")</f>
         <v>100200</v>
       </c>
@@ -17082,37 +17534,37 @@
       </c>
       <c r="B3" s="17">
         <f>IF(A3&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A3),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A3),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C3" s="18">
         <f>IF(A3&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A3),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A3),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D3" s="18">
         <f>IF(A3&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A3),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A3),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E3" s="18">
         <f>IF(A3&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A3)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A3)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A3),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A3),
     "")</f>
         <v>100200</v>
       </c>
@@ -17137,37 +17589,37 @@
       </c>
       <c r="B4" s="14">
         <f>IF(A4&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A4),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A4),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C4" s="15">
         <f>IF(A4&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A4),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A4),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D4" s="15">
         <f>IF(A4&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A4),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A4),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E4" s="15">
         <f>IF(A4&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A4)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A4)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A4),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A4),
     "")</f>
         <v>100200</v>
       </c>
@@ -17193,37 +17645,37 @@
       </c>
       <c r="B5" s="17">
         <f>IF(A5&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A5),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A5),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C5" s="18">
         <f>IF(A5&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A5),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A5),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D5" s="18">
         <f>IF(A5&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A5),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A5),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E5" s="18">
         <f>IF(A5&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A5)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A5)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A5),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A5),
     "")</f>
         <v>100200</v>
       </c>
@@ -17248,37 +17700,37 @@
       </c>
       <c r="B6" s="14">
         <f>IF(A6&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A6),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A6),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C6" s="15">
         <f>IF(A6&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A6),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A6),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D6" s="15">
         <f>IF(A6&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A6),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A6),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E6" s="15">
         <f>IF(A6&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A6)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A6)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A6),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A6),
     "")</f>
         <v>100200</v>
       </c>
@@ -17304,37 +17756,37 @@
       </c>
       <c r="B7" s="17">
         <f>IF(A7&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A7),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A7),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C7" s="18">
         <f>IF(A7&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A7),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A7),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D7" s="18">
         <f>IF(A7&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A7),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A7),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E7" s="18">
         <f>IF(A7&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A7)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A7)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A7),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A7),
     "")</f>
         <v>100200</v>
       </c>
@@ -17361,37 +17813,37 @@
       </c>
       <c r="B8" s="14">
         <f>IF(A8&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A8),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A8),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C8" s="15">
         <f>IF(A8&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A8),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A8),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D8" s="15">
         <f>IF(A8&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A8),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A8),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E8" s="15">
         <f>IF(A8&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A8)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A8)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A8),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A8),
     "")</f>
         <v>138200</v>
       </c>
@@ -17415,37 +17867,37 @@
       </c>
       <c r="B9" s="17">
         <f>IF(A9&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A9),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A9),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C9" s="18">
         <f>IF(A9&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A9),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A9),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D9" s="18">
         <f>IF(A9&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A9),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A9),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E9" s="18">
         <f>IF(A9&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A9)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A9)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A9),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A9),
     "")</f>
         <v>138200</v>
       </c>
@@ -17472,37 +17924,37 @@
       </c>
       <c r="B10" s="14">
         <f>IF(A10&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A10),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A10),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C10" s="15">
         <f>IF(A10&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A10),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A10),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D10" s="15">
         <f>IF(A10&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A10),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A10),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E10" s="15">
         <f>IF(A10&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A10)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A10)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A10),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A10),
     "")</f>
         <v>138200</v>
       </c>
@@ -17528,37 +17980,37 @@
       </c>
       <c r="B11" s="17">
         <f>IF(A11&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A11),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A11),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C11" s="18">
         <f>IF(A11&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A11),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A11),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D11" s="18">
         <f>IF(A11&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A11),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A11),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E11" s="18">
         <f>IF(A11&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A11)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A11)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A11),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A11),
     "")</f>
         <v>138200</v>
       </c>
@@ -17583,37 +18035,37 @@
       </c>
       <c r="B12" s="14">
         <f>IF(A12&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A12),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A12),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C12" s="15">
         <f>IF(A12&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A12),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A12),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D12" s="15">
         <f>IF(A12&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A12),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A12),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E12" s="15">
         <f>IF(A12&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A12)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A12)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A12),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A12),
     "")</f>
         <v>138200</v>
       </c>
@@ -17639,37 +18091,37 @@
       </c>
       <c r="B13" s="17">
         <f>IF(A13&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A13),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A13),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C13" s="18">
         <f>IF(A13&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A13),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A13),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D13" s="18">
         <f>IF(A13&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A13),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A13),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E13" s="18">
         <f>IF(A13&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A13)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A13)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A13),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A13),
     "")</f>
         <v>138200</v>
       </c>
@@ -17694,37 +18146,37 @@
       </c>
       <c r="B14" s="14">
         <f>IF(A14&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A14),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A14),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C14" s="15">
         <f>IF(A14&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A14),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A14),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D14" s="15">
         <f>IF(A14&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A14),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A14),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E14" s="15">
         <f>IF(A14&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A14)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A14)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A14),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A14),
     "")</f>
         <v>138200</v>
       </c>
@@ -17750,37 +18202,37 @@
       </c>
       <c r="B15" s="17">
         <f>IF(A15&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A15),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A15),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C15" s="18">
         <f>IF(A15&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A15),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A15),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D15" s="18">
         <f>IF(A15&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A15),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A15),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E15" s="18">
         <f>IF(A15&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A15)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A15)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A15),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A15),
     "")</f>
         <v>138200</v>
       </c>
@@ -17805,37 +18257,37 @@
       </c>
       <c r="B16" s="14">
         <f>IF(A16&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A16),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A16),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C16" s="15">
         <f>IF(A16&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A16),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A16),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D16" s="15">
         <f>IF(A16&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A16),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A16),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E16" s="15">
         <f>IF(A16&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A16)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A16)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A16),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A16),
     "")</f>
         <v>298200</v>
       </c>
@@ -17861,37 +18313,37 @@
       </c>
       <c r="B17" s="17">
         <f>IF(A17&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A17),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A17),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C17" s="18">
         <f>IF(A17&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A17),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A17),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D17" s="18">
         <f>IF(A17&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A17),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A17),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E17" s="18">
         <f>IF(A17&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A17)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A17)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A17),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A17),
     "")</f>
         <v>298200</v>
       </c>
@@ -17918,37 +18370,37 @@
       </c>
       <c r="B18" s="14">
         <f>IF(A18&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A18),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A18),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C18" s="15">
         <f>IF(A18&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A18),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A18),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D18" s="15">
         <f>IF(A18&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A18),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A18),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E18" s="15">
         <f>IF(A18&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A18)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A18)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A18),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A18),
     "")</f>
         <v>298200</v>
       </c>
@@ -17974,37 +18426,37 @@
       </c>
       <c r="B19" s="17">
         <f>IF(A19&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A19),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A19),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C19" s="18">
         <f>IF(A19&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A19),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A19),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D19" s="18">
         <f>IF(A19&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A19),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A19),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E19" s="18">
         <f>IF(A19&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A19)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A19)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A19),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A19),
     "")</f>
         <v>298200</v>
       </c>
@@ -18029,37 +18481,37 @@
       </c>
       <c r="B20" s="14">
         <f>IF(A20&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A20),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A20),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C20" s="15">
         <f>IF(A20&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A20),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A20),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D20" s="15">
         <f>IF(A20&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A20),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A20),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E20" s="15">
         <f>IF(A20&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A20)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A20)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A20),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A20),
     "")</f>
         <v>298200</v>
       </c>
@@ -18085,37 +18537,37 @@
       </c>
       <c r="B21" s="17">
         <f>IF(A21&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A21),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A21),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C21" s="18">
         <f>IF(A21&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A21),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A21),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D21" s="18">
         <f>IF(A21&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A21),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A21),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E21" s="18">
         <f>IF(A21&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A21)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A21)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A21),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A21),
     "")</f>
         <v>298200</v>
       </c>
@@ -18140,37 +18592,37 @@
       </c>
       <c r="B22" s="14">
         <f>IF(A22&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A22),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A22),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C22" s="15">
         <f>IF(A22&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A22),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A22),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D22" s="15">
         <f>IF(A22&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A22),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A22),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E22" s="15">
         <f>IF(A22&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A22)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A22)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A22),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A22),
     "")</f>
         <v>298200</v>
       </c>
@@ -18196,37 +18648,37 @@
       </c>
       <c r="B23" s="17">
         <f>IF(A23&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A23),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A23),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C23" s="18">
         <f>IF(A23&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A23),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A23),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D23" s="18">
         <f>IF(A23&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A23),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A23),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E23" s="18">
         <f>IF(A23&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A23)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A23)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A23),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A23),
     "")</f>
         <v>298200</v>
       </c>
@@ -18253,37 +18705,37 @@
       </c>
       <c r="B24" s="14">
         <f>IF(A24&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A24),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A24),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C24" s="15">
         <f>IF(A24&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A24),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A24),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D24" s="15">
         <f>IF(A24&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A24),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A24),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E24" s="15">
         <f>IF(A24&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A24)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A24)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A24),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A24),
     "")</f>
         <v>298200</v>
       </c>
@@ -18307,37 +18759,37 @@
       </c>
       <c r="B25" s="17">
         <f>IF(A25&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A25),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A25),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C25" s="18">
         <f>IF(A25&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A25),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A25),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D25" s="18">
         <f>IF(A25&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A25),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A25),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E25" s="18">
         <f>IF(A25&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A25)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A25)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A25),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A25),
     "")</f>
         <v>298200</v>
       </c>
@@ -18364,37 +18816,37 @@
       </c>
       <c r="B26" s="14">
         <f>IF(A26&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A26),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A26),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C26" s="15">
         <f>IF(A26&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A26),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A26),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D26" s="15">
         <f>IF(A26&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A26),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A26),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E26" s="15">
         <f>IF(A26&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A26)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A26)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A26),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A26),
     "")</f>
         <v>298200</v>
       </c>
@@ -18420,37 +18872,37 @@
       </c>
       <c r="B27" s="17">
         <f>IF(A27&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A27),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A27),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C27" s="18">
         <f>IF(A27&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A27),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A27),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D27" s="18">
         <f>IF(A27&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A27),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A27),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E27" s="18">
         <f>IF(A27&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A27)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A27)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A27),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A27),
     "")</f>
         <v>298200</v>
       </c>
@@ -18477,37 +18929,37 @@
       </c>
       <c r="B28" s="14">
         <f>IF(A28&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A28),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A28),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C28" s="15">
         <f>IF(A28&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A28),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A28),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D28" s="15">
         <f>IF(A28&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A28),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A28),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E28" s="15">
         <f>IF(A28&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A28)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A28)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A28),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A28),
     "")</f>
         <v>390700</v>
       </c>
@@ -18533,37 +18985,37 @@
       </c>
       <c r="B29" s="17">
         <f>IF(A29&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A29),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A29),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C29" s="18">
         <f>IF(A29&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A29),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A29),
     "")</f>
         <v>105350</v>
       </c>
       <c r="D29" s="18">
         <f>IF(A29&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A29),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A29),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E29" s="18">
         <f>IF(A29&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A29)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A29)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A29),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A29),
     "")</f>
         <v>390700</v>
       </c>
@@ -18590,9 +19042,9 @@
       </c>
       <c r="B30" s="14">
         <f>IF(A30&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A30),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A30),
     "")</f>
         <v>188380</v>
       </c>
@@ -18601,9 +19053,9 @@
       </c>
       <c r="D30" s="15">
         <f>IF(A30&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A30),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A30),
     "")</f>
         <v>630000</v>
       </c>
@@ -18632,9 +19084,9 @@
       </c>
       <c r="B31" s="17">
         <f>IF(A31&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A31),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A31),
     "")</f>
         <v>188380</v>
       </c>
@@ -18643,9 +19095,9 @@
       </c>
       <c r="D31" s="18">
         <f>IF(A31&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A31),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A31),
     "")</f>
         <v>630000</v>
       </c>
@@ -18675,25 +19127,25 @@
       </c>
       <c r="B32" s="14">
         <f>IF(A32&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A32),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A32),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C32" s="15">
         <f>IF(A32&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A32),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A32),
     "")</f>
         <v>120000</v>
       </c>
       <c r="D32" s="15">
         <f>IF(A32&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A32),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A32),
     "")</f>
         <v>630000</v>
       </c>
@@ -18722,37 +19174,37 @@
       </c>
       <c r="B33" s="17">
         <f>IF(A33&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A33),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A33),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C33" s="18">
         <f>IF(A33&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A33),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A33),
     "")</f>
         <v>120000</v>
       </c>
       <c r="D33" s="18">
         <f>IF(A33&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A33),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A33),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E33" s="18">
         <f>IF(A33&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A33)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A33)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A33),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A33),
     "")</f>
         <v>450500</v>
       </c>
@@ -18779,37 +19231,37 @@
       </c>
       <c r="B34" s="14">
         <f>IF(A34&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A34),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A34),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C34" s="15">
         <f>IF(A34&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A34),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A34),
     "")</f>
         <v>120000</v>
       </c>
       <c r="D34" s="15">
         <f>IF(A34&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A34),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A34),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E34" s="15">
         <f>IF(A34&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A34)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A34)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A34),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A34),
     "")</f>
         <v>450500</v>
       </c>
@@ -18835,37 +19287,37 @@
       </c>
       <c r="B35" s="17">
         <f>IF(A35&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A35),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A35),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C35" s="18">
         <f>IF(A35&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A35),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A35),
     "")</f>
         <v>120000</v>
       </c>
       <c r="D35" s="18">
         <f>IF(A35&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A35),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A35),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E35" s="18">
         <f>IF(A35&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A35)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A35)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A35),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A35),
     "")</f>
         <v>450500</v>
       </c>
@@ -18892,37 +19344,37 @@
       </c>
       <c r="B36" s="14">
         <f>IF(A36&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A36),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A36),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C36" s="15">
         <f>IF(A36&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A36),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A36),
     "")</f>
         <v>120000</v>
       </c>
       <c r="D36" s="15">
         <f>IF(A36&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A36),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A36),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E36" s="15">
         <f>IF(A36&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A36)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A36)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A36),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A36),
     "")</f>
         <v>450500</v>
       </c>
@@ -18948,9 +19400,9 @@
       </c>
       <c r="B37" s="17">
         <f>IF(A37&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A37),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A37),
     "")</f>
         <v>188380</v>
       </c>
@@ -18959,9 +19411,9 @@
       </c>
       <c r="D37" s="18">
         <f>IF(A37&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A37),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A37),
     "")</f>
         <v>630000</v>
       </c>
@@ -18989,9 +19441,9 @@
       </c>
       <c r="B38" s="14">
         <f>IF(A38&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A38),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A38),
     "")</f>
         <v>188380</v>
       </c>
@@ -19000,9 +19452,9 @@
       </c>
       <c r="D38" s="15">
         <f>IF(A38&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A38),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A38),
     "")</f>
         <v>630000</v>
       </c>
@@ -19031,9 +19483,9 @@
       </c>
       <c r="B39" s="17">
         <f>IF(A39&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A39),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A39),
     "")</f>
         <v>188380</v>
       </c>
@@ -19042,9 +19494,9 @@
       </c>
       <c r="D39" s="18">
         <f>IF(A39&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A39),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A39),
     "")</f>
         <v>630000</v>
       </c>
@@ -19074,9 +19526,9 @@
       </c>
       <c r="B40" s="14">
         <f>IF(A40&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A40),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A40),
     "")</f>
         <v>188380</v>
       </c>
@@ -19085,21 +19537,21 @@
       </c>
       <c r="D40" s="15">
         <f>IF(A40&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A40),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A40),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E40" s="15">
         <f>IF(A40&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A40)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A40)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A40),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A40),
     "")</f>
         <v>473500</v>
       </c>
@@ -19125,41 +19577,41 @@
       </c>
       <c r="B41" s="17">
         <f>IF(A41&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A41),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A41),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C41" s="18">
         <f>IF(A41&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A41)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A41)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A41),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A41),
     "")</f>
         <v>134000</v>
       </c>
       <c r="D41" s="18">
         <f>IF(A41&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A41),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A41),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E41" s="18">
         <f>IF(A41&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A41)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A41)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A41),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A41),
     "")</f>
         <v>473500</v>
       </c>
@@ -19186,41 +19638,41 @@
       </c>
       <c r="B42" s="14">
         <f>IF(A42&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A42),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A42),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C42" s="15">
         <f>IF(A42&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A42)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A42)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A42),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A42),
     "")</f>
         <v>134000</v>
       </c>
       <c r="D42" s="15">
         <f>IF(A42&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A42),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A42),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E42" s="15">
         <f>IF(A42&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A42)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A42)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A42),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A42),
     "")</f>
         <v>473500</v>
       </c>
@@ -19246,41 +19698,41 @@
       </c>
       <c r="B43" s="17">
         <f>IF(A43&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A43),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A43),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C43" s="18">
         <f>IF(A43&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A43)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A43)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A43),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A43),
     "")</f>
         <v>134000</v>
       </c>
       <c r="D43" s="18">
         <f>IF(A43&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A43),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A43),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E43" s="18">
         <f>IF(A43&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A43)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A43)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A43),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A43),
     "")</f>
         <v>473500</v>
       </c>
@@ -19305,41 +19757,41 @@
       </c>
       <c r="B44" s="14">
         <f>IF(A44&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A44),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A44),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C44" s="15">
         <f>IF(A44&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A44)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A44)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A44),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A44),
     "")</f>
         <v>134000</v>
       </c>
       <c r="D44" s="15">
         <f>IF(A44&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A44),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A44),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E44" s="15">
         <f>IF(A44&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A44)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A44)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A44),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A44),
     "")</f>
         <v>473500</v>
       </c>
@@ -19365,9 +19817,9 @@
       </c>
       <c r="B45" s="17">
         <f>IF(A45&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A45),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A45),
     "")</f>
         <v>188380</v>
       </c>
@@ -19376,21 +19828,21 @@
       </c>
       <c r="D45" s="18">
         <f>IF(A45&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A45),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A45),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E45" s="18">
         <f>IF(A45&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A45)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A45)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A45),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A45),
     "")</f>
         <v>473500</v>
       </c>
@@ -19415,9 +19867,9 @@
       </c>
       <c r="B46" s="14">
         <f>IF(A46&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A46),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A46),
     "")</f>
         <v>188380</v>
       </c>
@@ -19426,21 +19878,21 @@
       </c>
       <c r="D46" s="15">
         <f>IF(A46&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A46),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A46),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E46" s="15">
         <f>IF(A46&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A46)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A46)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A46),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A46),
     "")</f>
         <v>473500</v>
       </c>
@@ -19466,41 +19918,41 @@
       </c>
       <c r="B47" s="17">
         <f>IF(A47&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A47),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A47),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C47" s="18">
         <f>IF(A47&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A47)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A47)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A47),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A47),
     "")</f>
         <v>137000</v>
       </c>
       <c r="D47" s="18">
         <f>IF(A47&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A47),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A47),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E47" s="18">
         <f>IF(A47&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A47)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A47)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A47),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A47),
     "")</f>
         <v>473500</v>
       </c>
@@ -19527,41 +19979,41 @@
       </c>
       <c r="B48" s="14">
         <f>IF(A48&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A48),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A48),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C48" s="15">
         <f>IF(A48&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A48)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A48)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A48),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A48),
     "")</f>
         <v>137000</v>
       </c>
       <c r="D48" s="15">
         <f>IF(A48&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A48),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A48),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E48" s="15">
         <f>IF(A48&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A48)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A48)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A48),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A48),
     "")</f>
         <v>473500</v>
       </c>
@@ -19585,41 +20037,41 @@
       </c>
       <c r="B49" s="17">
         <f>IF(A49&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A49),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A49),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C49" s="18">
         <f>IF(A49&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A49)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A49)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A49),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A49),
     "")</f>
         <v>137000</v>
       </c>
       <c r="D49" s="18">
         <f>IF(A49&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A49),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A49),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E49" s="18">
         <f>IF(A49&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A49)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A49)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A49),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A49),
     "")</f>
         <v>473500</v>
       </c>
@@ -19646,41 +20098,41 @@
       </c>
       <c r="B50" s="14">
         <f>IF(A50&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A50),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A50),
     "")</f>
         <v>188380</v>
       </c>
       <c r="C50" s="15">
         <f>IF(A50&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A50)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A50)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A50),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A50),
     "")</f>
         <v>137000</v>
       </c>
       <c r="D50" s="15">
         <f>IF(A50&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A50),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A50),
     "")</f>
         <v>630000</v>
       </c>
       <c r="E50" s="15">
         <f>IF(A50&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A50)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A50)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A50),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A50),
     "")</f>
         <v>473500</v>
       </c>
@@ -19701,529 +20153,617 @@
       </c>
     </row>
     <row r="51" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="16"/>
-      <c r="B51" s="17" t="str">
+      <c r="A51" s="16">
+        <v>46245</v>
+      </c>
+      <c r="B51" s="17">
         <f>IF(A51&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A51),
-    "")</f>
-        <v/>
-      </c>
-      <c r="C51" s="18" t="str">
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A51),
+    "")</f>
+        <v>188380</v>
+      </c>
+      <c r="C51" s="18">
         <f>IF(A51&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A51)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A51)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A51),
-    "")</f>
-        <v/>
-      </c>
-      <c r="D51" s="18" t="str">
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A51),
+    "")</f>
+        <v>137000</v>
+      </c>
+      <c r="D51" s="18">
         <f>IF(A51&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A51),
-    "")</f>
-        <v/>
-      </c>
-      <c r="E51" s="18" t="str">
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A51),
+    "")</f>
+        <v>630000</v>
+      </c>
+      <c r="E51" s="18">
         <f>IF(A51&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A51)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A51)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A51),
-    "")</f>
-        <v/>
-      </c>
-      <c r="F51" s="29"/>
-      <c r="G51" s="29"/>
-      <c r="H51" s="29"/>
-      <c r="I51" s="29"/>
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A51),
+    "")</f>
+        <v>473500</v>
+      </c>
+      <c r="F51" s="29">
+        <v>1131126</v>
+      </c>
+      <c r="G51" s="29">
+        <v>23926</v>
+      </c>
+      <c r="H51" s="29">
+        <v>813700</v>
+      </c>
+      <c r="I51" s="29">
+        <v>717042.55683881603</v>
+      </c>
       <c r="J51" s="32"/>
       <c r="P51" s="9"/>
     </row>
     <row r="52" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="11"/>
-      <c r="B52" s="14" t="str">
+      <c r="A52" s="11">
+        <v>46245</v>
+      </c>
+      <c r="B52" s="14">
         <f>IF(A52&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A52),
-    "")</f>
-        <v/>
-      </c>
-      <c r="C52" s="15" t="str">
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A52),
+    "")</f>
+        <v>188380</v>
+      </c>
+      <c r="C52" s="15">
         <f>IF(A52&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A52)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A52)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A52),
-    "")</f>
-        <v/>
-      </c>
-      <c r="D52" s="15" t="str">
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A52),
+    "")</f>
+        <v>137000</v>
+      </c>
+      <c r="D52" s="15">
         <f>IF(A52&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A52),
-    "")</f>
-        <v/>
-      </c>
-      <c r="E52" s="15" t="str">
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A52),
+    "")</f>
+        <v>630000</v>
+      </c>
+      <c r="E52" s="15">
         <f>IF(A52&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A52)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A52)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A52),
-    "")</f>
-        <v/>
-      </c>
-      <c r="F52" s="26"/>
-      <c r="G52" s="26"/>
-      <c r="H52" s="26"/>
-      <c r="I52" s="26"/>
-      <c r="J52" s="31"/>
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A52),
+    "")</f>
+        <v>473500</v>
+      </c>
+      <c r="F52" s="26">
+        <v>1128326</v>
+      </c>
+      <c r="G52" s="26">
+        <v>21126</v>
+      </c>
+      <c r="H52" s="26">
+        <v>813700</v>
+      </c>
+      <c r="I52" s="26">
+        <v>717042.55683881603</v>
+      </c>
+      <c r="J52" s="31" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="53" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="16"/>
-      <c r="B53" s="17" t="str">
+      <c r="A53" s="16">
+        <v>46245</v>
+      </c>
+      <c r="B53" s="17">
         <f>IF(A53&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A53),
-    "")</f>
-        <v/>
-      </c>
-      <c r="C53" s="18" t="str">
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A53),
+    "")</f>
+        <v>188380</v>
+      </c>
+      <c r="C53" s="18">
         <f>IF(A53&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A53)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A53)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A53),
-    "")</f>
-        <v/>
-      </c>
-      <c r="D53" s="18" t="str">
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A53),
+    "")</f>
+        <v>137000</v>
+      </c>
+      <c r="D53" s="18">
         <f>IF(A53&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A53),
-    "")</f>
-        <v/>
-      </c>
-      <c r="E53" s="18" t="str">
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A53),
+    "")</f>
+        <v>630000</v>
+      </c>
+      <c r="E53" s="18">
         <f>IF(A53&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A53)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A53)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A53),
-    "")</f>
-        <v/>
-      </c>
-      <c r="F53" s="29"/>
-      <c r="G53" s="29"/>
-      <c r="H53" s="29"/>
-      <c r="I53" s="29"/>
-      <c r="J53" s="32"/>
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A53),
+    "")</f>
+        <v>473500</v>
+      </c>
+      <c r="F53" s="29">
+        <v>1129326</v>
+      </c>
+      <c r="G53" s="29">
+        <v>16126</v>
+      </c>
+      <c r="H53" s="29">
+        <v>819700</v>
+      </c>
+      <c r="I53" s="29">
+        <v>723042.55683881603</v>
+      </c>
+      <c r="J53" s="32" t="s">
+        <v>115</v>
+      </c>
       <c r="P53" s="9"/>
     </row>
     <row r="54" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="11"/>
-      <c r="B54" s="14" t="str">
+      <c r="A54" s="11">
+        <v>46248</v>
+      </c>
+      <c r="B54" s="14">
         <f>IF(A54&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A54),
-    "")</f>
-        <v/>
-      </c>
-      <c r="C54" s="15" t="str">
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A54),
+    "")</f>
+        <v>188380</v>
+      </c>
+      <c r="C54" s="15">
         <f>IF(A54&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A54)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A54)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A54),
-    "")</f>
-        <v/>
-      </c>
-      <c r="D54" s="15" t="str">
-        <f>IF(A54&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A54),
-    "")</f>
-        <v/>
-      </c>
-      <c r="E54" s="15" t="str">
-        <f>IF(A54&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A54)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A54),
+    "")</f>
+        <v>137000</v>
+      </c>
+      <c r="D54" s="15">
+        <v>630000</v>
+      </c>
+      <c r="E54" s="15">
+        <v>473500</v>
+      </c>
+      <c r="F54" s="26">
+        <v>1129326</v>
+      </c>
+      <c r="G54" s="26">
+        <v>55226</v>
+      </c>
+      <c r="H54" s="26">
+        <v>780600</v>
+      </c>
+      <c r="I54" s="26">
+        <v>686340.76040076779</v>
+      </c>
+      <c r="J54" s="31"/>
+    </row>
+    <row r="55" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="16">
+        <v>46248</v>
+      </c>
+      <c r="B55" s="17">
+        <f>IF(A55&lt;&gt;"",
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A55),
+    "")</f>
+        <v>188380</v>
+      </c>
+      <c r="C55" s="18">
+        <f>IF(A55&lt;&gt;"",
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A55)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A54),
-    "")</f>
-        <v/>
-      </c>
-      <c r="F54" s="26"/>
-      <c r="G54" s="26"/>
-      <c r="H54" s="26"/>
-      <c r="I54" s="26"/>
-      <c r="J54" s="31"/>
-    </row>
-    <row r="55" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="16"/>
-      <c r="B55" s="17" t="str">
-        <f>IF(A55&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A55),
-    "")</f>
-        <v/>
-      </c>
-      <c r="C55" s="18" t="str">
-        <f>IF(A55&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A55)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A55),
+    "")</f>
+        <v>137000</v>
+      </c>
+      <c r="D55" s="18">
+        <v>630000</v>
+      </c>
+      <c r="E55" s="18">
+        <v>473500</v>
+      </c>
+      <c r="F55" s="29">
+        <v>1125826</v>
+      </c>
+      <c r="G55" s="29">
+        <v>51726</v>
+      </c>
+      <c r="H55" s="29">
+        <v>780600</v>
+      </c>
+      <c r="I55" s="29">
+        <v>686340.76040076779</v>
+      </c>
+      <c r="J55" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="P55" s="9"/>
+    </row>
+    <row r="56" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="11">
+        <v>46248</v>
+      </c>
+      <c r="B56" s="14">
+        <f>IF(A56&lt;&gt;"",
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A56),
+    "")</f>
+        <v>188380</v>
+      </c>
+      <c r="C56" s="15">
+        <f>IF(A56&lt;&gt;"",
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A56)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A55),
-    "")</f>
-        <v/>
-      </c>
-      <c r="D55" s="18" t="str">
-        <f>IF(A55&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A55),
-    "")</f>
-        <v/>
-      </c>
-      <c r="E55" s="18" t="str">
-        <f>IF(A55&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A55)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A56),
+    "")</f>
+        <v>137000</v>
+      </c>
+      <c r="D56" s="15">
+        <f>IF(A56&lt;&gt;"",
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A56),
+    "")</f>
+        <v>650000</v>
+      </c>
+      <c r="E56" s="15">
+        <f>IF(A56&lt;&gt;"",
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A56)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A55),
-    "")</f>
-        <v/>
-      </c>
-      <c r="F55" s="29"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="29"/>
-      <c r="I55" s="29"/>
-      <c r="J55" s="32"/>
-      <c r="P55" s="9"/>
-    </row>
-    <row r="56" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="11"/>
-      <c r="B56" s="14" t="str">
-        <f>IF(A56&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A56),
-    "")</f>
-        <v/>
-      </c>
-      <c r="C56" s="15" t="str">
-        <f>IF(A56&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A56)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A56),
+    "")</f>
+        <v>483500</v>
+      </c>
+      <c r="F56" s="26">
+        <v>1125826</v>
+      </c>
+      <c r="G56" s="26">
+        <v>41726</v>
+      </c>
+      <c r="H56" s="26">
+        <v>780600</v>
+      </c>
+      <c r="I56" s="26">
+        <v>686340.76040076779</v>
+      </c>
+      <c r="J56" s="31" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="16">
+        <v>46248</v>
+      </c>
+      <c r="B57" s="17">
+        <f>IF(A57&lt;&gt;"",
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A57),
+    "")</f>
+        <v>188380</v>
+      </c>
+      <c r="C57" s="18">
+        <f>IF(A57&lt;&gt;"",
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A57)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A56),
-    "")</f>
-        <v/>
-      </c>
-      <c r="D56" s="15" t="str">
-        <f>IF(A56&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A56),
-    "")</f>
-        <v/>
-      </c>
-      <c r="E56" s="15" t="str">
-        <f>IF(A56&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A56)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A57),
+    "")</f>
+        <v>137000</v>
+      </c>
+      <c r="D57" s="18">
+        <f>IF(A57&lt;&gt;"",
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A57),
+    "")</f>
+        <v>650000</v>
+      </c>
+      <c r="E57" s="18">
+        <f>IF(A57&lt;&gt;"",
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A57)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A56),
-    "")</f>
-        <v/>
-      </c>
-      <c r="F56" s="26"/>
-      <c r="G56" s="26"/>
-      <c r="H56" s="26"/>
-      <c r="I56" s="26"/>
-      <c r="J56" s="31"/>
-    </row>
-    <row r="57" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="16"/>
-      <c r="B57" s="17" t="str">
-        <f>IF(A57&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A57),
-    "")</f>
-        <v/>
-      </c>
-      <c r="C57" s="18" t="str">
-        <f>IF(A57&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A57)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A57),
+    "")</f>
+        <v>483500</v>
+      </c>
+      <c r="F57" s="29">
+        <v>1129626</v>
+      </c>
+      <c r="G57" s="29">
+        <v>21726</v>
+      </c>
+      <c r="H57" s="29">
+        <v>804400</v>
+      </c>
+      <c r="I57" s="29">
+        <v>710142.92313490203</v>
+      </c>
+      <c r="J57" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="P57" s="9"/>
+    </row>
+    <row r="58" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="11">
+        <v>46255</v>
+      </c>
+      <c r="B58" s="14">
+        <f>IF(A58&lt;&gt;"",
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A58),
+    "")</f>
+        <v>188380</v>
+      </c>
+      <c r="C58" s="15">
+        <f>IF(A58&lt;&gt;"",
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A58)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A57),
-    "")</f>
-        <v/>
-      </c>
-      <c r="D57" s="18" t="str">
-        <f>IF(A57&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A57),
-    "")</f>
-        <v/>
-      </c>
-      <c r="E57" s="18" t="str">
-        <f>IF(A57&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A57)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A58),
+    "")</f>
+        <v>137000</v>
+      </c>
+      <c r="D58" s="15">
+        <f>IF(A58&lt;&gt;"",
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A58),
+    "")</f>
+        <v>650000</v>
+      </c>
+      <c r="E58" s="15">
+        <f>IF(A58&lt;&gt;"",
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A58)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A57),
-    "")</f>
-        <v/>
-      </c>
-      <c r="F57" s="29"/>
-      <c r="G57" s="29"/>
-      <c r="H57" s="29"/>
-      <c r="I57" s="29"/>
-      <c r="J57" s="32"/>
-      <c r="P57" s="9"/>
-    </row>
-    <row r="58" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="11"/>
-      <c r="B58" s="14" t="str">
-        <f>IF(A58&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A58),
-    "")</f>
-        <v/>
-      </c>
-      <c r="C58" s="15" t="str">
-        <f>IF(A58&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A58)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A58),
+    "")</f>
+        <v>483500</v>
+      </c>
+      <c r="F58" s="26">
+        <v>1111126</v>
+      </c>
+      <c r="G58" s="26">
+        <v>65226</v>
+      </c>
+      <c r="H58" s="26">
+        <v>742400</v>
+      </c>
+      <c r="I58" s="26">
+        <v>657059.79450026399</v>
+      </c>
+      <c r="J58" s="31" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="16">
+        <v>46255</v>
+      </c>
+      <c r="B59" s="17">
+        <f>IF(A59&lt;&gt;"",
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A59),
+    "")</f>
+        <v>188380</v>
+      </c>
+      <c r="C59" s="18">
+        <f>IF(A59&lt;&gt;"",
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A59)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A58),
-    "")</f>
-        <v/>
-      </c>
-      <c r="D58" s="15" t="str">
-        <f>IF(A58&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A58),
-    "")</f>
-        <v/>
-      </c>
-      <c r="E58" s="15" t="str">
-        <f>IF(A58&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A58)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A59),
+    "")</f>
+        <v>137000</v>
+      </c>
+      <c r="D59" s="18">
+        <f>IF(A59&lt;&gt;"",
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A59),
+    "")</f>
+        <v>650000</v>
+      </c>
+      <c r="E59" s="18">
+        <f>IF(A59&lt;&gt;"",
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A59)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A58),
-    "")</f>
-        <v/>
-      </c>
-      <c r="F58" s="26"/>
-      <c r="G58" s="26"/>
-      <c r="H58" s="26"/>
-      <c r="I58" s="26"/>
-      <c r="J58" s="31"/>
-    </row>
-    <row r="59" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="16"/>
-      <c r="B59" s="17" t="str">
-        <f>IF(A59&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A59),
-    "")</f>
-        <v/>
-      </c>
-      <c r="C59" s="18" t="str">
-        <f>IF(A59&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A59)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A59),
+    "")</f>
+        <v>483500</v>
+      </c>
+      <c r="F59" s="29">
+        <v>1109976</v>
+      </c>
+      <c r="G59" s="29">
+        <v>64076</v>
+      </c>
+      <c r="H59" s="29">
+        <v>742400</v>
+      </c>
+      <c r="I59" s="29">
+        <v>657059.79450026399</v>
+      </c>
+      <c r="J59" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="P59" s="9"/>
+    </row>
+    <row r="60" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="11">
+        <v>46255</v>
+      </c>
+      <c r="B60" s="14">
+        <f>IF(A60&lt;&gt;"",
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A60),
+    "")</f>
+        <v>188380</v>
+      </c>
+      <c r="C60" s="15">
+        <f>IF(A60&lt;&gt;"",
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A60)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A59),
-    "")</f>
-        <v/>
-      </c>
-      <c r="D59" s="18" t="str">
-        <f>IF(A59&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A59),
-    "")</f>
-        <v/>
-      </c>
-      <c r="E59" s="18" t="str">
-        <f>IF(A59&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A59)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A60),
+    "")</f>
+        <v>137000</v>
+      </c>
+      <c r="D60" s="15">
+        <f>IF(A60&lt;&gt;"",
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A60),
+    "")</f>
+        <v>650000</v>
+      </c>
+      <c r="E60" s="15">
+        <f>IF(A60&lt;&gt;"",
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A60)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A59),
-    "")</f>
-        <v/>
-      </c>
-      <c r="F59" s="29"/>
-      <c r="G59" s="29"/>
-      <c r="H59" s="29"/>
-      <c r="I59" s="29"/>
-      <c r="J59" s="32"/>
-      <c r="P59" s="9"/>
-    </row>
-    <row r="60" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="11"/>
-      <c r="B60" s="14" t="str">
-        <f>IF(A60&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A60),
-    "")</f>
-        <v/>
-      </c>
-      <c r="C60" s="15" t="str">
-        <f>IF(A60&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A60)
-    +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A60),
-    "")</f>
-        <v/>
-      </c>
-      <c r="D60" s="15" t="str">
-        <f>IF(A60&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A60),
-    "")</f>
-        <v/>
-      </c>
-      <c r="E60" s="15" t="str">
-        <f>IF(A60&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A60)
-    +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A60),
-    "")</f>
-        <v/>
-      </c>
-      <c r="F60" s="26"/>
-      <c r="G60" s="26"/>
-      <c r="H60" s="26"/>
-      <c r="I60" s="26"/>
-      <c r="J60" s="31"/>
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A60),
+    "")</f>
+        <v>483500</v>
+      </c>
+      <c r="F60" s="26">
+        <v>1117576</v>
+      </c>
+      <c r="G60" s="26">
+        <v>24076</v>
+      </c>
+      <c r="H60" s="26">
+        <v>790000</v>
+      </c>
+      <c r="I60" s="26">
+        <v>704659.79450026399</v>
+      </c>
+      <c r="J60" s="31" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="61" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="16"/>
       <c r="B61" s="17" t="str">
         <f>IF(A61&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A61),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A61),
     "")</f>
         <v/>
       </c>
       <c r="C61" s="18" t="str">
         <f>IF(A61&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A61)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A61)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A61),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A61),
     "")</f>
         <v/>
       </c>
       <c r="D61" s="18" t="str">
         <f>IF(A61&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A61),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A61),
     "")</f>
         <v/>
       </c>
       <c r="E61" s="18" t="str">
         <f>IF(A61&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A61)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A61)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A61),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A61),
     "")</f>
         <v/>
       </c>
@@ -20238,41 +20778,41 @@
       <c r="A62" s="11"/>
       <c r="B62" s="14" t="str">
         <f>IF(A62&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A62),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A62),
     "")</f>
         <v/>
       </c>
       <c r="C62" s="15" t="str">
         <f>IF(A62&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A62)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A62)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A62),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A62),
     "")</f>
         <v/>
       </c>
       <c r="D62" s="15" t="str">
         <f>IF(A62&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A62),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A62),
     "")</f>
         <v/>
       </c>
       <c r="E62" s="15" t="str">
         <f>IF(A62&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A62)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A62)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A62),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A62),
     "")</f>
         <v/>
       </c>
@@ -20286,41 +20826,41 @@
       <c r="A63" s="16"/>
       <c r="B63" s="17" t="str">
         <f>IF(A63&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A63),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A63),
     "")</f>
         <v/>
       </c>
       <c r="C63" s="18" t="str">
         <f>IF(A63&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A63)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A63)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A63),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A63),
     "")</f>
         <v/>
       </c>
       <c r="D63" s="18" t="str">
         <f>IF(A63&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A63),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A63),
     "")</f>
         <v/>
       </c>
       <c r="E63" s="18" t="str">
         <f>IF(A63&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A63)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A63)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A63),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A63),
     "")</f>
         <v/>
       </c>
@@ -20335,41 +20875,41 @@
       <c r="A64" s="11"/>
       <c r="B64" s="14" t="str">
         <f>IF(A64&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A64),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A64),
     "")</f>
         <v/>
       </c>
       <c r="C64" s="15" t="str">
         <f>IF(A64&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A64)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A64)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A64),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A64),
     "")</f>
         <v/>
       </c>
       <c r="D64" s="15" t="str">
         <f>IF(A64&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A64),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A64),
     "")</f>
         <v/>
       </c>
       <c r="E64" s="15" t="str">
         <f>IF(A64&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A64)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A64)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A64),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A64),
     "")</f>
         <v/>
       </c>
@@ -20383,41 +20923,41 @@
       <c r="A65" s="16"/>
       <c r="B65" s="17" t="str">
         <f>IF(A65&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A65),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A65),
     "")</f>
         <v/>
       </c>
       <c r="C65" s="18" t="str">
         <f>IF(A65&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A65)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A65)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A65),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A65),
     "")</f>
         <v/>
       </c>
       <c r="D65" s="18" t="str">
         <f>IF(A65&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A65),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A65),
     "")</f>
         <v/>
       </c>
       <c r="E65" s="18" t="str">
         <f>IF(A65&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A65)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A65)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A65),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A65),
     "")</f>
         <v/>
       </c>
@@ -20432,41 +20972,41 @@
       <c r="A66" s="11"/>
       <c r="B66" s="14" t="str">
         <f>IF(A66&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A66),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A66),
     "")</f>
         <v/>
       </c>
       <c r="C66" s="15" t="str">
         <f>IF(A66&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A66)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A66)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A66),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A66),
     "")</f>
         <v/>
       </c>
       <c r="D66" s="15" t="str">
         <f>IF(A66&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A66),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A66),
     "")</f>
         <v/>
       </c>
       <c r="E66" s="15" t="str">
         <f>IF(A66&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A66)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A66)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A66),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A66),
     "")</f>
         <v/>
       </c>
@@ -20480,41 +21020,41 @@
       <c r="A67" s="16"/>
       <c r="B67" s="17" t="str">
         <f>IF(A67&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A67),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A67),
     "")</f>
         <v/>
       </c>
       <c r="C67" s="18" t="str">
         <f>IF(A67&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A67)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A67)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A67),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A67),
     "")</f>
         <v/>
       </c>
       <c r="D67" s="18" t="str">
         <f>IF(A67&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A67),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A67),
     "")</f>
         <v/>
       </c>
       <c r="E67" s="18" t="str">
         <f>IF(A67&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A67)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A67)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A67),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A67),
     "")</f>
         <v/>
       </c>
@@ -20529,41 +21069,41 @@
       <c r="A68" s="11"/>
       <c r="B68" s="14" t="str">
         <f>IF(A68&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A68),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A68),
     "")</f>
         <v/>
       </c>
       <c r="C68" s="15" t="str">
         <f>IF(A68&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A68)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A68)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A68),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A68),
     "")</f>
         <v/>
       </c>
       <c r="D68" s="15" t="str">
         <f>IF(A68&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A68),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A68),
     "")</f>
         <v/>
       </c>
       <c r="E68" s="15" t="str">
         <f>IF(A68&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A68)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A68)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A68),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A68),
     "")</f>
         <v/>
       </c>
@@ -20577,41 +21117,41 @@
       <c r="A69" s="16"/>
       <c r="B69" s="17" t="str">
         <f>IF(A69&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A69),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A69),
     "")</f>
         <v/>
       </c>
       <c r="C69" s="18" t="str">
         <f>IF(A69&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A69)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A69)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A69),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A69),
     "")</f>
         <v/>
       </c>
       <c r="D69" s="18" t="str">
         <f>IF(A69&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A69),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A69),
     "")</f>
         <v/>
       </c>
       <c r="E69" s="18" t="str">
         <f>IF(A69&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A69)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A69)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A69),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A69),
     "")</f>
         <v/>
       </c>
@@ -20626,41 +21166,41 @@
       <c r="A70" s="11"/>
       <c r="B70" s="14" t="str">
         <f>IF(A70&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A70),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A70),
     "")</f>
         <v/>
       </c>
       <c r="C70" s="15" t="str">
         <f>IF(A70&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A70)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A70)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A70),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A70),
     "")</f>
         <v/>
       </c>
       <c r="D70" s="15" t="str">
         <f>IF(A70&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A70),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A70),
     "")</f>
         <v/>
       </c>
       <c r="E70" s="15" t="str">
         <f>IF(A70&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A70)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A70)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A70),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A70),
     "")</f>
         <v/>
       </c>
@@ -20674,41 +21214,41 @@
       <c r="A71" s="16"/>
       <c r="B71" s="17" t="str">
         <f>IF(A71&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A71),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A71),
     "")</f>
         <v/>
       </c>
       <c r="C71" s="18" t="str">
         <f>IF(A71&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A71)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A71)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A71),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A71),
     "")</f>
         <v/>
       </c>
       <c r="D71" s="18" t="str">
         <f>IF(A71&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A71),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A71),
     "")</f>
         <v/>
       </c>
       <c r="E71" s="18" t="str">
         <f>IF(A71&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A71)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A71)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A71),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A71),
     "")</f>
         <v/>
       </c>
@@ -20723,41 +21263,41 @@
       <c r="A72" s="11"/>
       <c r="B72" s="14" t="str">
         <f>IF(A72&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A72),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A72),
     "")</f>
         <v/>
       </c>
       <c r="C72" s="15" t="str">
         <f>IF(A72&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A72)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A72)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A72),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A72),
     "")</f>
         <v/>
       </c>
       <c r="D72" s="15" t="str">
         <f>IF(A72&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A72),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A72),
     "")</f>
         <v/>
       </c>
       <c r="E72" s="15" t="str">
         <f>IF(A72&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A72)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A72)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A72),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A72),
     "")</f>
         <v/>
       </c>
@@ -20771,41 +21311,41 @@
       <c r="A73" s="16"/>
       <c r="B73" s="17" t="str">
         <f>IF(A73&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A73),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A73),
     "")</f>
         <v/>
       </c>
       <c r="C73" s="18" t="str">
         <f>IF(A73&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A73)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A73)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A73),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A73),
     "")</f>
         <v/>
       </c>
       <c r="D73" s="18" t="str">
         <f>IF(A73&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A73),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A73),
     "")</f>
         <v/>
       </c>
       <c r="E73" s="18" t="str">
         <f>IF(A73&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A73)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A73)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A73),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A73),
     "")</f>
         <v/>
       </c>
@@ -20820,41 +21360,41 @@
       <c r="A74" s="11"/>
       <c r="B74" s="14" t="str">
         <f>IF(A74&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A74),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A74),
     "")</f>
         <v/>
       </c>
       <c r="C74" s="15" t="str">
         <f>IF(A74&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A74)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A74)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A74),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A74),
     "")</f>
         <v/>
       </c>
       <c r="D74" s="15" t="str">
         <f>IF(A74&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A74),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A74),
     "")</f>
         <v/>
       </c>
       <c r="E74" s="15" t="str">
         <f>IF(A74&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A74)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A74)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A74),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A74),
     "")</f>
         <v/>
       </c>
@@ -20868,41 +21408,41 @@
       <c r="A75" s="16"/>
       <c r="B75" s="17" t="str">
         <f>IF(A75&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A75),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A75),
     "")</f>
         <v/>
       </c>
       <c r="C75" s="18" t="str">
         <f>IF(A75&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A75)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A75)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A75),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A75),
     "")</f>
         <v/>
       </c>
       <c r="D75" s="18" t="str">
         <f>IF(A75&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A75),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A75),
     "")</f>
         <v/>
       </c>
       <c r="E75" s="18" t="str">
         <f>IF(A75&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A75)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A75)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A75),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A75),
     "")</f>
         <v/>
       </c>
@@ -20917,41 +21457,41 @@
       <c r="A76" s="11"/>
       <c r="B76" s="14" t="str">
         <f>IF(A76&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A76),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A76),
     "")</f>
         <v/>
       </c>
       <c r="C76" s="15" t="str">
         <f>IF(A76&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A76)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A76)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A76),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A76),
     "")</f>
         <v/>
       </c>
       <c r="D76" s="15" t="str">
         <f>IF(A76&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A76),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A76),
     "")</f>
         <v/>
       </c>
       <c r="E76" s="15" t="str">
         <f>IF(A76&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A76)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A76)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A76),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A76),
     "")</f>
         <v/>
       </c>
@@ -20965,41 +21505,41 @@
       <c r="A77" s="16"/>
       <c r="B77" s="17" t="str">
         <f>IF(A77&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A77),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A77),
     "")</f>
         <v/>
       </c>
       <c r="C77" s="18" t="str">
         <f>IF(A77&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A77)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A77)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A77),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A77),
     "")</f>
         <v/>
       </c>
       <c r="D77" s="18" t="str">
         <f>IF(A77&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A77),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A77),
     "")</f>
         <v/>
       </c>
       <c r="E77" s="18" t="str">
         <f>IF(A77&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A77)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A77)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A77),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A77),
     "")</f>
         <v/>
       </c>
@@ -21014,41 +21554,41 @@
       <c r="A78" s="11"/>
       <c r="B78" s="14" t="str">
         <f>IF(A78&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A78),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A78),
     "")</f>
         <v/>
       </c>
       <c r="C78" s="15" t="str">
         <f>IF(A78&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A78)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A78)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A78),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A78),
     "")</f>
         <v/>
       </c>
       <c r="D78" s="15" t="str">
         <f>IF(A78&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A78),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A78),
     "")</f>
         <v/>
       </c>
       <c r="E78" s="15" t="str">
         <f>IF(A78&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A78)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A78)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A78),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A78),
     "")</f>
         <v/>
       </c>
@@ -21062,41 +21602,41 @@
       <c r="A79" s="16"/>
       <c r="B79" s="17" t="str">
         <f>IF(A79&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A79),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A79),
     "")</f>
         <v/>
       </c>
       <c r="C79" s="18" t="str">
         <f>IF(A79&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A79)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A79)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A79),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A79),
     "")</f>
         <v/>
       </c>
       <c r="D79" s="18" t="str">
         <f>IF(A79&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A79),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A79),
     "")</f>
         <v/>
       </c>
       <c r="E79" s="18" t="str">
         <f>IF(A79&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A79)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A79)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A79),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A79),
     "")</f>
         <v/>
       </c>
@@ -21111,41 +21651,41 @@
       <c r="A80" s="11"/>
       <c r="B80" s="14" t="str">
         <f>IF(A80&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A80),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A80),
     "")</f>
         <v/>
       </c>
       <c r="C80" s="15" t="str">
         <f>IF(A80&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A80)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A80)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A80),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A80),
     "")</f>
         <v/>
       </c>
       <c r="D80" s="15" t="str">
         <f>IF(A80&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A80),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A80),
     "")</f>
         <v/>
       </c>
       <c r="E80" s="15" t="str">
         <f>IF(A80&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A80)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A80)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A80),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A80),
     "")</f>
         <v/>
       </c>
@@ -21159,41 +21699,41 @@
       <c r="A81" s="16"/>
       <c r="B81" s="17" t="str">
         <f>IF(A81&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A81),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A81),
     "")</f>
         <v/>
       </c>
       <c r="C81" s="18" t="str">
         <f>IF(A81&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A81)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A81)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A81),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A81),
     "")</f>
         <v/>
       </c>
       <c r="D81" s="18" t="str">
         <f>IF(A81&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A81),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A81),
     "")</f>
         <v/>
       </c>
       <c r="E81" s="18" t="str">
         <f>IF(A81&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A81)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A81)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A81),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A81),
     "")</f>
         <v/>
       </c>
@@ -21208,41 +21748,41 @@
       <c r="A82" s="11"/>
       <c r="B82" s="14" t="str">
         <f>IF(A82&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A82),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A82),
     "")</f>
         <v/>
       </c>
       <c r="C82" s="15" t="str">
         <f>IF(A82&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A82)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A82)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A82),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A82),
     "")</f>
         <v/>
       </c>
       <c r="D82" s="15" t="str">
         <f>IF(A82&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A82),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A82),
     "")</f>
         <v/>
       </c>
       <c r="E82" s="15" t="str">
         <f>IF(A82&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A82)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A82)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A82),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A82),
     "")</f>
         <v/>
       </c>
@@ -21256,41 +21796,41 @@
       <c r="A83" s="16"/>
       <c r="B83" s="17" t="str">
         <f>IF(A83&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A83),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A83),
     "")</f>
         <v/>
       </c>
       <c r="C83" s="18" t="str">
         <f>IF(A83&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A83)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A83)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A83),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A83),
     "")</f>
         <v/>
       </c>
       <c r="D83" s="18" t="str">
         <f>IF(A83&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A83),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A83),
     "")</f>
         <v/>
       </c>
       <c r="E83" s="18" t="str">
         <f>IF(A83&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A83)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A83)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A83),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A83),
     "")</f>
         <v/>
       </c>
@@ -21305,41 +21845,41 @@
       <c r="A84" s="11"/>
       <c r="B84" s="14" t="str">
         <f>IF(A84&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A84),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A84),
     "")</f>
         <v/>
       </c>
       <c r="C84" s="15" t="str">
         <f>IF(A84&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A84)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A84)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A84),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A84),
     "")</f>
         <v/>
       </c>
       <c r="D84" s="15" t="str">
         <f>IF(A84&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A84),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A84),
     "")</f>
         <v/>
       </c>
       <c r="E84" s="15" t="str">
         <f>IF(A84&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A84)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A84)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A84),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A84),
     "")</f>
         <v/>
       </c>
@@ -21353,41 +21893,41 @@
       <c r="A85" s="16"/>
       <c r="B85" s="17" t="str">
         <f>IF(A85&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A85),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A85),
     "")</f>
         <v/>
       </c>
       <c r="C85" s="18" t="str">
         <f>IF(A85&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A85)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A85)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A85),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A85),
     "")</f>
         <v/>
       </c>
       <c r="D85" s="18" t="str">
         <f>IF(A85&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A85),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A85),
     "")</f>
         <v/>
       </c>
       <c r="E85" s="18" t="str">
         <f>IF(A85&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A85)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A85)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A85),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A85),
     "")</f>
         <v/>
       </c>
@@ -21402,41 +21942,41 @@
       <c r="A86" s="11"/>
       <c r="B86" s="14" t="str">
         <f>IF(A86&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A86),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A86),
     "")</f>
         <v/>
       </c>
       <c r="C86" s="15" t="str">
         <f>IF(A86&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A86)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A86)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A86),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A86),
     "")</f>
         <v/>
       </c>
       <c r="D86" s="15" t="str">
         <f>IF(A86&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A86),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A86),
     "")</f>
         <v/>
       </c>
       <c r="E86" s="15" t="str">
         <f>IF(A86&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A86)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A86)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A86),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A86),
     "")</f>
         <v/>
       </c>
@@ -21450,41 +21990,41 @@
       <c r="A87" s="16"/>
       <c r="B87" s="17" t="str">
         <f>IF(A87&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A87),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A87),
     "")</f>
         <v/>
       </c>
       <c r="C87" s="18" t="str">
         <f>IF(A87&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A87)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A87)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A87),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A87),
     "")</f>
         <v/>
       </c>
       <c r="D87" s="18" t="str">
         <f>IF(A87&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A87),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A87),
     "")</f>
         <v/>
       </c>
       <c r="E87" s="18" t="str">
         <f>IF(A87&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A87)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A87)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A87),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A87),
     "")</f>
         <v/>
       </c>
@@ -21499,41 +22039,41 @@
       <c r="A88" s="11"/>
       <c r="B88" s="14" t="str">
         <f>IF(A88&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A88),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A88),
     "")</f>
         <v/>
       </c>
       <c r="C88" s="15" t="str">
         <f>IF(A88&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A88)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A88)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A88),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A88),
     "")</f>
         <v/>
       </c>
       <c r="D88" s="15" t="str">
         <f>IF(A88&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A88),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A88),
     "")</f>
         <v/>
       </c>
       <c r="E88" s="15" t="str">
         <f>IF(A88&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A88)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A88)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A88),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A88),
     "")</f>
         <v/>
       </c>
@@ -21547,41 +22087,41 @@
       <c r="A89" s="16"/>
       <c r="B89" s="17" t="str">
         <f>IF(A89&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A89),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A89),
     "")</f>
         <v/>
       </c>
       <c r="C89" s="18" t="str">
         <f>IF(A89&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A89)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A89)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A89),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A89),
     "")</f>
         <v/>
       </c>
       <c r="D89" s="18" t="str">
         <f>IF(A89&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A89),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A89),
     "")</f>
         <v/>
       </c>
       <c r="E89" s="18" t="str">
         <f>IF(A89&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A89)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A89)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A89),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A89),
     "")</f>
         <v/>
       </c>
@@ -21596,41 +22136,41 @@
       <c r="A90" s="11"/>
       <c r="B90" s="14" t="str">
         <f>IF(A90&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A90),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A90),
     "")</f>
         <v/>
       </c>
       <c r="C90" s="15" t="str">
         <f>IF(A90&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A90)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A90)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A90),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A90),
     "")</f>
         <v/>
       </c>
       <c r="D90" s="15" t="str">
         <f>IF(A90&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A90),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A90),
     "")</f>
         <v/>
       </c>
       <c r="E90" s="15" t="str">
         <f>IF(A90&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A90)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A90)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A90),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A90),
     "")</f>
         <v/>
       </c>
@@ -21644,41 +22184,41 @@
       <c r="A91" s="16"/>
       <c r="B91" s="17" t="str">
         <f>IF(A91&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A91),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A91),
     "")</f>
         <v/>
       </c>
       <c r="C91" s="18" t="str">
         <f>IF(A91&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A91)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A91)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A91),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A91),
     "")</f>
         <v/>
       </c>
       <c r="D91" s="18" t="str">
         <f>IF(A91&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A91),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A91),
     "")</f>
         <v/>
       </c>
       <c r="E91" s="18" t="str">
         <f>IF(A91&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A91)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A91)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A91),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A91),
     "")</f>
         <v/>
       </c>
@@ -21693,41 +22233,41 @@
       <c r="A92" s="11"/>
       <c r="B92" s="14" t="str">
         <f>IF(A92&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A92),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A92),
     "")</f>
         <v/>
       </c>
       <c r="C92" s="15" t="str">
         <f>IF(A92&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A92)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A92)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A92),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A92),
     "")</f>
         <v/>
       </c>
       <c r="D92" s="15" t="str">
         <f>IF(A92&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A92),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A92),
     "")</f>
         <v/>
       </c>
       <c r="E92" s="15" t="str">
         <f>IF(A92&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A92)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A92)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A92),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A92),
     "")</f>
         <v/>
       </c>
@@ -21741,41 +22281,41 @@
       <c r="A93" s="16"/>
       <c r="B93" s="17" t="str">
         <f>IF(A93&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A93),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A93),
     "")</f>
         <v/>
       </c>
       <c r="C93" s="18" t="str">
         <f>IF(A93&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A93)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A93)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A93),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A93),
     "")</f>
         <v/>
       </c>
       <c r="D93" s="18" t="str">
         <f>IF(A93&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A93),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A93),
     "")</f>
         <v/>
       </c>
       <c r="E93" s="18" t="str">
         <f>IF(A93&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A93)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A93)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A93),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A93),
     "")</f>
         <v/>
       </c>
@@ -21790,41 +22330,41 @@
       <c r="A94" s="11"/>
       <c r="B94" s="14" t="str">
         <f>IF(A94&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A94),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A94),
     "")</f>
         <v/>
       </c>
       <c r="C94" s="15" t="str">
         <f>IF(A94&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A94)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A94)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A94),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A94),
     "")</f>
         <v/>
       </c>
       <c r="D94" s="15" t="str">
         <f>IF(A94&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A94),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A94),
     "")</f>
         <v/>
       </c>
       <c r="E94" s="15" t="str">
         <f>IF(A94&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A94)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A94)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A94),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A94),
     "")</f>
         <v/>
       </c>
@@ -21838,41 +22378,41 @@
       <c r="A95" s="16"/>
       <c r="B95" s="17" t="str">
         <f>IF(A95&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A95),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A95),
     "")</f>
         <v/>
       </c>
       <c r="C95" s="18" t="str">
         <f>IF(A95&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A95)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A95)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A95),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A95),
     "")</f>
         <v/>
       </c>
       <c r="D95" s="18" t="str">
         <f>IF(A95&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A95),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A95),
     "")</f>
         <v/>
       </c>
       <c r="E95" s="18" t="str">
         <f>IF(A95&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A95)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A95)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A95),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A95),
     "")</f>
         <v/>
       </c>
@@ -21887,41 +22427,41 @@
       <c r="A96" s="11"/>
       <c r="B96" s="14" t="str">
         <f>IF(A96&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A96),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A96),
     "")</f>
         <v/>
       </c>
       <c r="C96" s="15" t="str">
         <f>IF(A96&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A96)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A96)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A96),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A96),
     "")</f>
         <v/>
       </c>
       <c r="D96" s="15" t="str">
         <f>IF(A96&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A96),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A96),
     "")</f>
         <v/>
       </c>
       <c r="E96" s="15" t="str">
         <f>IF(A96&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A96)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A96)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A96),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A96),
     "")</f>
         <v/>
       </c>
@@ -21935,41 +22475,41 @@
       <c r="A97" s="16"/>
       <c r="B97" s="17" t="str">
         <f>IF(A97&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A97),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A97),
     "")</f>
         <v/>
       </c>
       <c r="C97" s="18" t="str">
         <f>IF(A97&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A97)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A97)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A97),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A97),
     "")</f>
         <v/>
       </c>
       <c r="D97" s="18" t="str">
         <f>IF(A97&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A97),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A97),
     "")</f>
         <v/>
       </c>
       <c r="E97" s="18" t="str">
         <f>IF(A97&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A97)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A97)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A97),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A97),
     "")</f>
         <v/>
       </c>
@@ -21984,41 +22524,41 @@
       <c r="A98" s="11"/>
       <c r="B98" s="14" t="str">
         <f>IF(A98&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A98),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A98),
     "")</f>
         <v/>
       </c>
       <c r="C98" s="15" t="str">
         <f>IF(A98&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A98)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A98)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A98),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A98),
     "")</f>
         <v/>
       </c>
       <c r="D98" s="15" t="str">
         <f>IF(A98&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A98),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A98),
     "")</f>
         <v/>
       </c>
       <c r="E98" s="15" t="str">
         <f>IF(A98&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A98)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A98)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A98),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A98),
     "")</f>
         <v/>
       </c>
@@ -22032,41 +22572,41 @@
       <c r="A99" s="16"/>
       <c r="B99" s="17" t="str">
         <f>IF(A99&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A99),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A99),
     "")</f>
         <v/>
       </c>
       <c r="C99" s="18" t="str">
         <f>IF(A99&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A99)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A99)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A99),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A99),
     "")</f>
         <v/>
       </c>
       <c r="D99" s="18" t="str">
         <f>IF(A99&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A99),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A99),
     "")</f>
         <v/>
       </c>
       <c r="E99" s="18" t="str">
         <f>IF(A99&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A99)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A99)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A99),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A99),
     "")</f>
         <v/>
       </c>
@@ -22081,41 +22621,41 @@
       <c r="A100" s="11"/>
       <c r="B100" s="14" t="str">
         <f>IF(A100&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A100),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A100),
     "")</f>
         <v/>
       </c>
       <c r="C100" s="15" t="str">
         <f>IF(A100&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A100)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A100)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A100),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A100),
     "")</f>
         <v/>
       </c>
       <c r="D100" s="15" t="str">
         <f>IF(A100&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A100),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A100),
     "")</f>
         <v/>
       </c>
       <c r="E100" s="15" t="str">
         <f>IF(A100&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A100)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A100)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A100),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A100),
     "")</f>
         <v/>
       </c>
@@ -22129,41 +22669,41 @@
       <c r="A101" s="16"/>
       <c r="B101" s="17" t="str">
         <f>IF(A101&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A101),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A101),
     "")</f>
         <v/>
       </c>
       <c r="C101" s="18" t="str">
         <f>IF(A101&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A101)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A101)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A101),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A101),
     "")</f>
         <v/>
       </c>
       <c r="D101" s="18" t="str">
         <f>IF(A101&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A101),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A101),
     "")</f>
         <v/>
       </c>
       <c r="E101" s="18" t="str">
         <f>IF(A101&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A101)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A101)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A101),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A101),
     "")</f>
         <v/>
       </c>
@@ -22178,41 +22718,41 @@
       <c r="A102" s="11"/>
       <c r="B102" s="14" t="str">
         <f>IF(A102&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A102),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A102),
     "")</f>
         <v/>
       </c>
       <c r="C102" s="15" t="str">
         <f>IF(A102&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A102)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A102)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A102),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A102),
     "")</f>
         <v/>
       </c>
       <c r="D102" s="15" t="str">
         <f>IF(A102&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A102),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A102),
     "")</f>
         <v/>
       </c>
       <c r="E102" s="15" t="str">
         <f>IF(A102&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A102)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A102)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A102),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A102),
     "")</f>
         <v/>
       </c>
@@ -22226,41 +22766,41 @@
       <c r="A103" s="16"/>
       <c r="B103" s="17" t="str">
         <f>IF(A103&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A103),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A103),
     "")</f>
         <v/>
       </c>
       <c r="C103" s="18" t="str">
         <f>IF(A103&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A103)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A103)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A103),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A103),
     "")</f>
         <v/>
       </c>
       <c r="D103" s="18" t="str">
         <f>IF(A103&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A103),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A103),
     "")</f>
         <v/>
       </c>
       <c r="E103" s="18" t="str">
         <f>IF(A103&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A103)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A103)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A103),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A103),
     "")</f>
         <v/>
       </c>
@@ -22275,41 +22815,41 @@
       <c r="A104" s="11"/>
       <c r="B104" s="14" t="str">
         <f>IF(A104&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A104),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A104),
     "")</f>
         <v/>
       </c>
       <c r="C104" s="15" t="str">
         <f>IF(A104&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A104)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A104)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A104),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A104),
     "")</f>
         <v/>
       </c>
       <c r="D104" s="15" t="str">
         <f>IF(A104&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A104),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A104),
     "")</f>
         <v/>
       </c>
       <c r="E104" s="15" t="str">
         <f>IF(A104&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A104)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A104)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A104),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A104),
     "")</f>
         <v/>
       </c>
@@ -22323,41 +22863,41 @@
       <c r="A105" s="16"/>
       <c r="B105" s="17" t="str">
         <f>IF(A105&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A105),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A105),
     "")</f>
         <v/>
       </c>
       <c r="C105" s="18" t="str">
         <f>IF(A105&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A105)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A105)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A105),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A105),
     "")</f>
         <v/>
       </c>
       <c r="D105" s="18" t="str">
         <f>IF(A105&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A105),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A105),
     "")</f>
         <v/>
       </c>
       <c r="E105" s="18" t="str">
         <f>IF(A105&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A105)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A105)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A105),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A105),
     "")</f>
         <v/>
       </c>
@@ -22372,41 +22912,41 @@
       <c r="A106" s="11"/>
       <c r="B106" s="14" t="str">
         <f>IF(A106&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A106),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A106),
     "")</f>
         <v/>
       </c>
       <c r="C106" s="15" t="str">
         <f>IF(A106&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A106)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A106)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A106),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A106),
     "")</f>
         <v/>
       </c>
       <c r="D106" s="15" t="str">
         <f>IF(A106&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A106),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A106),
     "")</f>
         <v/>
       </c>
       <c r="E106" s="15" t="str">
         <f>IF(A106&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A106)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A106)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A106),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A106),
     "")</f>
         <v/>
       </c>
@@ -22420,41 +22960,41 @@
       <c r="A107" s="16"/>
       <c r="B107" s="17" t="str">
         <f>IF(A107&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A107),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A107),
     "")</f>
         <v/>
       </c>
       <c r="C107" s="18" t="str">
         <f>IF(A107&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A107)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A107)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A107),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A107),
     "")</f>
         <v/>
       </c>
       <c r="D107" s="18" t="str">
         <f>IF(A107&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A107),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A107),
     "")</f>
         <v/>
       </c>
       <c r="E107" s="18" t="str">
         <f>IF(A107&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A107)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A107)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A107),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A107),
     "")</f>
         <v/>
       </c>
@@ -22469,41 +23009,41 @@
       <c r="A108" s="11"/>
       <c r="B108" s="14" t="str">
         <f>IF(A108&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A108),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A108),
     "")</f>
         <v/>
       </c>
       <c r="C108" s="15" t="str">
         <f>IF(A108&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A108)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A108)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A108),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A108),
     "")</f>
         <v/>
       </c>
       <c r="D108" s="15" t="str">
         <f>IF(A108&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A108),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A108),
     "")</f>
         <v/>
       </c>
       <c r="E108" s="15" t="str">
         <f>IF(A108&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A108)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A108)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A108),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A108),
     "")</f>
         <v/>
       </c>
@@ -22517,41 +23057,41 @@
       <c r="A109" s="16"/>
       <c r="B109" s="17" t="str">
         <f>IF(A109&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A109),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A109),
     "")</f>
         <v/>
       </c>
       <c r="C109" s="18" t="str">
         <f>IF(A109&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A109)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A109)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A109),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A109),
     "")</f>
         <v/>
       </c>
       <c r="D109" s="18" t="str">
         <f>IF(A109&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A109),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A109),
     "")</f>
         <v/>
       </c>
       <c r="E109" s="18" t="str">
         <f>IF(A109&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A109)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A109)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A109),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A109),
     "")</f>
         <v/>
       </c>
@@ -22566,41 +23106,41 @@
       <c r="A110" s="11"/>
       <c r="B110" s="14" t="str">
         <f>IF(A110&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A110),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A110),
     "")</f>
         <v/>
       </c>
       <c r="C110" s="15" t="str">
         <f>IF(A110&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A110)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A110)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A110),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A110),
     "")</f>
         <v/>
       </c>
       <c r="D110" s="15" t="str">
         <f>IF(A110&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A110),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A110),
     "")</f>
         <v/>
       </c>
       <c r="E110" s="15" t="str">
         <f>IF(A110&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A110)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A110)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A110),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A110),
     "")</f>
         <v/>
       </c>
@@ -22614,41 +23154,41 @@
       <c r="A111" s="16"/>
       <c r="B111" s="17" t="str">
         <f>IF(A111&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Capital Injection",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A111),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Capital Injection",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A111),
     "")</f>
         <v/>
       </c>
       <c r="C111" s="18" t="str">
         <f>IF(A111&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Izra Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A111)
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Izra Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A111)
     +
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Investment to Unit",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A111),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Investment to Unit",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A111),
     "")</f>
         <v/>
       </c>
       <c r="D111" s="18" t="str">
         <f>IF(A111&lt;&gt;"",
-    SUMIFS([31]InvestingJournal!$F:$F,
-           [31]InvestingJournal!$C:$C,"Loan Advance",
-           [31]InvestingJournal!$A:$A,"&lt;="&amp;A111),
+    SUMIFS([34]InvestingJournal!$F:$F,
+           [34]InvestingJournal!$C:$C,"Loan Advance",
+           [34]InvestingJournal!$A:$A,"&lt;="&amp;A111),
     "")</f>
         <v/>
       </c>
       <c r="E111" s="18" t="str">
         <f>IF(A111&lt;&gt;"",
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Borrowing",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A111)
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Borrowing",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A111)
     +
-    SUMIFS([31]FinancingJournal!$E:$E,
-           [31]FinancingJournal!$C:$C,"Withdrawal",
-           [31]FinancingJournal!$A:$A,"&lt;="&amp;A111),
+    SUMIFS([34]FinancingJournal!$E:$E,
+           [34]FinancingJournal!$C:$C,"Withdrawal",
+           [34]FinancingJournal!$A:$A,"&lt;="&amp;A111),
     "")</f>
         <v/>
       </c>
@@ -22660,7 +23200,7 @@
       <c r="P111" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="pACmxmtkz7DID0/3BpUYEp59aYzu7loptOcK2mkTNwJi+eru9MAZxpt3oUaN/Pfi9MdsFG+qO4uJBRfbrenhgg==" saltValue="vqcHVdw6pSYNaBL55KDTcg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="SzpsEc9zrwywAWxZeoF5LE1Ik3LGLKMsFQuZ3Jqn51/GNeThmSawB0y1MA1DbyZBI5HGAN3yKm9EzOvoVyVD4g==" saltValue="Iumo3Otk/rY14P/xLqPb+A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
